--- a/scripts/data/publications.xlsx
+++ b/scripts/data/publications.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilakolpashnikova/Dropbox/Mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34C2746F-C844-ED4F-B4F2-56678D310D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E1D1F0-F2C6-964D-A3AB-C35C53BF2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1880" windowWidth="28040" windowHeight="17180" xr2:uid="{1AE54D6A-986F-F746-921F-6A2F1439D6A6}"/>
+    <workbookView xWindow="44000" yWindow="1140" windowWidth="28040" windowHeight="17180" xr2:uid="{1AE54D6A-986F-F746-921F-6A2F1439D6A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="629">
   <si>
     <t>Evolution of Semantic Similarity—A Survey</t>
   </si>
@@ -1658,12 +1657,347 @@
   <si>
     <t>International Conference on Frontiers of Intelligent Computing: Theory and …</t>
   </si>
+  <si>
+    <t>Smart fog: Fog computing framework for unsupervised clustering analytics in wearable internet of things</t>
+  </si>
+  <si>
+    <t>D Borthakur, H Dubey, N Constant, L Mahler, K Mankodiya</t>
+  </si>
+  <si>
+    <t>2017 IEEE Global Conference on Signal and Information Processing (GlobalSIP …</t>
+  </si>
+  <si>
+    <t>Fog computing in medical internet-of-things: architecture, implementation, and applications</t>
+  </si>
+  <si>
+    <t>H Dubey, A Monteiro, N Constant, M Abtahi, D Borthakur, L Mahler, Y Sun, ...</t>
+  </si>
+  <si>
+    <t>Handbook of large-scale distributed computing in smart healthcare, 281-321</t>
+  </si>
+  <si>
+    <t>Fog-assisted wiot: A smart fog gateway for end-to-end analytics in wearable internet of things</t>
+  </si>
+  <si>
+    <t>N Constant, D Borthakur, M Abtahi, H Dubey, K Mankodiya</t>
+  </si>
+  <si>
+    <t>arXiv preprint arXiv:1701.08680</t>
+  </si>
+  <si>
+    <t>Fog assisted cloud computing in era of big data and internet-of-things: systems, architectures, and applications</t>
+  </si>
+  <si>
+    <t>RK Barik, H Dubey, C Misra, D Borthakur, N Constant, SA Sasane, ...</t>
+  </si>
+  <si>
+    <t>Cloud computing for optimization: foundations, applications, and challenges …</t>
+  </si>
+  <si>
+    <t>Yoga pose estimation using angle-based feature extraction</t>
+  </si>
+  <si>
+    <t>D Borthakur, A Paul, D Kapil, MJ Saikia</t>
+  </si>
+  <si>
+    <t>Healthcare 11 (24), 3133</t>
+  </si>
+  <si>
+    <t>Associations between police lethal force errors, measures of diurnal and reactive cortisol, and mental health</t>
+  </si>
+  <si>
+    <t>JF Chan, PM Di Nota, K Planche, D Borthakur, JP Andersen</t>
+  </si>
+  <si>
+    <t>Psychoneuroendocrinology 142, 105789</t>
+  </si>
+  <si>
+    <t>SmartEAR: Smartwatch-based unsupervised learning for multi-modal signal analysis in opportunistic sensing framework</t>
+  </si>
+  <si>
+    <t>D Borthakur, A Peltier, H Dubey, JV Gyllinsky, K Mankodiya</t>
+  </si>
+  <si>
+    <t>Proceedings of the 2018 IEEE/ACM International Conference on Connected …</t>
+  </si>
+  <si>
+    <t>Using breath-like cues for guided breathing</t>
+  </si>
+  <si>
+    <t>G Marentakis, D Borthakur, P Batchelor, JP Andersen, V Grace</t>
+  </si>
+  <si>
+    <t>Extended Abstracts of the 2021 CHI Conference on Human Factors in Computing …</t>
+  </si>
+  <si>
+    <t>A machine learning approach to classify working memory load from optical neuroimaging data</t>
+  </si>
+  <si>
+    <t>MJ Saikia, S Kuanar, D Borthakur, M Vinti, T Tendhar</t>
+  </si>
+  <si>
+    <t>Optical Techniques in Neurosurgery, Neurophotonics, and Optogenetics 11629 …</t>
+  </si>
+  <si>
+    <t>Fuzzy C-means clustering and sonification of HRV features</t>
+  </si>
+  <si>
+    <t>D Borthakur, V Grace, P Batchelor, H Dubey, K Mankodiya</t>
+  </si>
+  <si>
+    <t>2019 IEEE/ACM International Conference on Connected Health: Applications …</t>
+  </si>
+  <si>
+    <t>Inequity aversion toward AI counterparts</t>
+  </si>
+  <si>
+    <t>D Borthakur, P Diep, JE Plaks</t>
+  </si>
+  <si>
+    <t>Scientific Reports 15 (1), 37916</t>
+  </si>
+  <si>
+    <t>Machine learning approach for music familiarity classification with single-channel eeg</t>
+  </si>
+  <si>
+    <t>N Kim, D Borthakur, MJ Saikia</t>
+  </si>
+  <si>
+    <t>2024 46th Annual International Conference of the IEEE Engineering in …</t>
+  </si>
+  <si>
+    <t>Empowering bystanders: a psychological and institutional model for intervention in academic bullying</t>
+  </si>
+  <si>
+    <t>D Borthakur, L Crockett, J Mihalchan, J Swann, MJ Saikia</t>
+  </si>
+  <si>
+    <t>Frontiers in Psychology 16, 1650438</t>
+  </si>
+  <si>
+    <t>Cardiorespiratory optimized guided-breathing for post-stress recovery in a group setting</t>
+  </si>
+  <si>
+    <t>D Borthakur</t>
+  </si>
+  <si>
+    <t>Quantifying the Effects of Motor Tasks on Corticokinematic Coherence in Parkinson's Disease</t>
+  </si>
+  <si>
+    <t>University of Rhode Island</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence (AI) in Patient–Healthcare Relationships: Psychosocial Perspective</t>
+  </si>
+  <si>
+    <t>MJ Saikia, D Borthakur</t>
+  </si>
+  <si>
+    <t>IEEE Access</t>
+  </si>
+  <si>
+    <t>Personality Influences on Inequity Aversion Toward Human and AI Counterparts</t>
+  </si>
+  <si>
+    <t>D Borthakur, H Ahmad, JE Plaks</t>
+  </si>
+  <si>
+    <t>Identifying Proposers’ Behavioral Patterns in Human-AI Economic Interactions</t>
+  </si>
+  <si>
+    <t>2025 IEEE International Conference on Future Machine Learning and Data …</t>
+  </si>
+  <si>
+    <t>Assamese Society Through the Lens of Cultural Neuroscience</t>
+  </si>
+  <si>
+    <t>ALOK https://www.alokassamesejournal.com/current-issue 16 (16), 82-88</t>
+  </si>
+  <si>
+    <t>“Prosodic Finder” – A web application</t>
+  </si>
+  <si>
+    <t>DBS Mahanta</t>
+  </si>
+  <si>
+    <t>Conference: 37th International Conference of Linguistics Society of India …</t>
+  </si>
+  <si>
+    <t>Automating Detection of Drug-Related Harms on Social Media: Machine Learning Framework</t>
+  </si>
+  <si>
+    <t>Journal of Medical Internet Research 25, e43630</t>
+  </si>
+  <si>
+    <t>Comparison of Moderated and Unmoderated Remote Usability Sessions for Web-Based Simulation Software: A Randomized Controlled Trial</t>
+  </si>
+  <si>
+    <t>Simulating the Evolution of Homeless Populations in Canada Using Modified Deep Q-Learning (MDQL) and Modified Neural Fitted Q-Iteration (MNFQ) Algorithms</t>
+  </si>
+  <si>
+    <t>Green Communication Protocol with Geolocation</t>
+  </si>
+  <si>
+    <t>G Srivastava, A Fisher, R Bryce, J Crichigno</t>
+  </si>
+  <si>
+    <t>2019 IEEE 89th Vehicular Technology Conference (VTC2019-Spring), 1-6</t>
+  </si>
+  <si>
+    <r>
+      <t>15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="24"/>
+        <color rgb="FF660099"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>*</t>
+    </r>
+  </si>
+  <si>
+    <t>Predicting the Resource Needs and Outcomes of Computationally Intensive Biological Simulations</t>
+  </si>
+  <si>
+    <t>2020 Spring Simulation Conference (SpringSim), 1-12</t>
+  </si>
+  <si>
+    <t>TentNet: Deep Learning Tent Detection Algorithm Using A Synthetic Training Approach</t>
+  </si>
+  <si>
+    <t>Investigating the Implications of COVID-19 for the Rural and Remote Population of Northern Ontario Using a Mathematical Model</t>
+  </si>
+  <si>
+    <t>BEAUT: An ExplainaBle Deep LEarning Model for Agent-Based PopUlations With Poor DaTa</t>
+  </si>
+  <si>
+    <t>PLOS ONE 19 (6), e0303646</t>
+  </si>
+  <si>
+    <t>How Many Costly Simulations Do we Need to Create Accurate Metamodels? A Case Study on Predicting HIV Viral Load in Response to Clinically Relevant Intervention Scenarios</t>
+  </si>
+  <si>
+    <t>International Workshop on Health Intelligence, 273-288</t>
+  </si>
+  <si>
+    <t>HEAL-Summ: A Lightweight and Ethical Framework for Accessible Summarization of Health Information</t>
+  </si>
+  <si>
+    <t>MQTTg: An Android Implementation</t>
+  </si>
+  <si>
+    <t>A Fisher, G Srivastava, R Bryce</t>
+  </si>
+  <si>
+    <t>2019 42nd International Conference on Telecommunications and Signal …</t>
+  </si>
+  <si>
+    <t>Facilitating Learning Outcome Assessment- Development of New Datasets and Analysis of Pre-Trained Language Models</t>
+  </si>
+  <si>
+    <t>An Ethical Visualization of the NorthCOVID-19 Model</t>
+  </si>
+  <si>
+    <t>Development of Simulation and Machine Learning Solutions for Social Issues</t>
+  </si>
+  <si>
+    <t>A Fisher</t>
+  </si>
+  <si>
+    <t>Proportion of Preterm birth and associated factors among mothers who gave birth in Debretabor town health institutions, northwest, Ethiopia</t>
+  </si>
+  <si>
+    <t>DG Mekonen, AE Yismaw, TS Nigussie, WM Ambaw</t>
+  </si>
+  <si>
+    <t>BMC research notes 12 (1), 2</t>
+  </si>
+  <si>
+    <t>Prevalence of post partum modern family planning utilization and associated factors among postpartum mothers in Debre Tabor town, North West Ethiopia, 2018</t>
+  </si>
+  <si>
+    <t>EB Taye, DG Mekonen, TZ Debele</t>
+  </si>
+  <si>
+    <t>BMC research notes 12 (1), 430</t>
+  </si>
+  <si>
+    <t>Repeat induced abortion and associated factors among women seeking abortion care services at Debre Markos town health institutions, Amhara regional state, Ethiopia, 2017</t>
+  </si>
+  <si>
+    <t>MI Waktola, DG Mekonen, TS Nigussie, EA Cherkose, AT Abate</t>
+  </si>
+  <si>
+    <t>BMC research notes 13 (1), 44</t>
+  </si>
+  <si>
+    <t>“I became a person again”: Social inclusion and participation experiences of Ethiopian women post-obstetric fistula surgical repair</t>
+  </si>
+  <si>
+    <t>TZ Debele, D Macdonald, HM Aldersey, Z Mengistu, DG Mekonnen, ...</t>
+  </si>
+  <si>
+    <t>Plos one 19 (7), e0307021</t>
+  </si>
+  <si>
+    <t>Predictors of competency on delivery care service among final year undergraduate midwifery students in higher education institutions of Ethiopia, 2019: A cross sectional study</t>
+  </si>
+  <si>
+    <t>DN Gessesse, BW Yirdaw, DG Mekonen</t>
+  </si>
+  <si>
+    <t>Clinical Epidemiology and Global Health 11, 100730</t>
+  </si>
+  <si>
+    <t>Supporting women after obstetric fistula surgery to enhance their social participation and inclusion</t>
+  </si>
+  <si>
+    <t>T Debele, HM Aldersey, D Macdonald, Z Mengistu, DG Mekonnen, ...</t>
+  </si>
+  <si>
+    <t>International journal of environmental research and public health 21 (9), 1201</t>
+  </si>
+  <si>
+    <t>“It is challenging to face the judgmental gazes”: women with physical disability and perinatal care-seeking in rural Ethiopia: a qualitative case study</t>
+  </si>
+  <si>
+    <t>DG Mekonen, E Snelgrove-Clarke, C Donnelly, EH Engeda, T Debele, ...</t>
+  </si>
+  <si>
+    <t>Disability and Rehabilitation, 1-17</t>
+  </si>
+  <si>
+    <t>Perinatal care experiences of women living with disability in Africa: a qualitative systematic review protocol</t>
+  </si>
+  <si>
+    <t>DG Mekonen, E Snelgrove-Clarke, D Macdonald, C Donnelly, E Engeda</t>
+  </si>
+  <si>
+    <t>JBI Evidence Synthesis 23 (4), 772-780</t>
+  </si>
+  <si>
+    <t>Knowledge of Postpartum Women About Modern Contraceptive Methods and Attitudes Towards its Utilization in Debre Tabor Town, Northwest Ethiopia: A Community-Based Cross …</t>
+  </si>
+  <si>
+    <t>EB Taye, DG Mekonnen, TZ Debele</t>
+  </si>
+  <si>
+    <t>Ethiopian Journal of Health and Biomedical Sciences 13 (1), 57-69</t>
+  </si>
+  <si>
+    <t>Proportion of preterm birth and associated factors among mothers who gave birth in Debretabor town health institutions, northwest, Ethiopia.</t>
+  </si>
+  <si>
+    <t>DGM Dawit Gebeyehu Mekonen, AEY Ayenew Engida Yismaw, ...</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1703,6 +2037,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1725,13 +2065,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2067,7 +2408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F586DF-5126-0C41-93C9-DC8AF5D22C1E}">
-  <dimension ref="A1:C560"/>
+  <dimension ref="A1:C709"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86.83203125" customWidth="1"/>
@@ -6685,18 +7026,1683 @@
       <c r="B560" s="3"/>
       <c r="C560" s="4"/>
     </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A561" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B561" s="3">
+        <v>133</v>
+      </c>
+      <c r="C561" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A562" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B562" s="3"/>
+      <c r="C562" s="4"/>
+    </row>
+    <row r="563" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A563" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B563" s="3"/>
+      <c r="C563" s="4"/>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A564" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="B564" s="3">
+        <v>132</v>
+      </c>
+      <c r="C564" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A565" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B565" s="3"/>
+      <c r="C565" s="4"/>
+    </row>
+    <row r="566" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A566" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B566" s="3"/>
+      <c r="C566" s="4"/>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A567" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="B567" s="3">
+        <v>102</v>
+      </c>
+      <c r="C567" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A568" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B568" s="3"/>
+      <c r="C568" s="4"/>
+    </row>
+    <row r="569" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A569" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B569" s="3"/>
+      <c r="C569" s="4"/>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A570" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="B570" s="3">
+        <v>89</v>
+      </c>
+      <c r="C570" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A571" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B571" s="3"/>
+      <c r="C571" s="4"/>
+    </row>
+    <row r="572" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A572" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B572" s="3"/>
+      <c r="C572" s="4"/>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A573" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B573" s="3">
+        <v>40</v>
+      </c>
+      <c r="C573" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A574" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B574" s="3"/>
+      <c r="C574" s="4"/>
+    </row>
+    <row r="575" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A575" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B575" s="3"/>
+      <c r="C575" s="4"/>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A576" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="B576" s="3">
+        <v>17</v>
+      </c>
+      <c r="C576" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A577" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B577" s="3"/>
+      <c r="C577" s="4"/>
+    </row>
+    <row r="578" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A578" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B578" s="3"/>
+      <c r="C578" s="4"/>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A579" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="B579" s="3">
+        <v>13</v>
+      </c>
+      <c r="C579" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A580" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="B580" s="3"/>
+      <c r="C580" s="4"/>
+    </row>
+    <row r="581" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A581" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B581" s="3"/>
+      <c r="C581" s="4"/>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A582" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="B582" s="3">
+        <v>12</v>
+      </c>
+      <c r="C582" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A583" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B583" s="3"/>
+      <c r="C583" s="4"/>
+    </row>
+    <row r="584" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A584" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B584" s="3"/>
+      <c r="C584" s="4"/>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A585" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="B585" s="3">
+        <v>11</v>
+      </c>
+      <c r="C585" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A586" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B586" s="3"/>
+      <c r="C586" s="4"/>
+    </row>
+    <row r="587" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A587" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B587" s="3"/>
+      <c r="C587" s="4"/>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A588" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="B588" s="3">
+        <v>7</v>
+      </c>
+      <c r="C588" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A589" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B589" s="3"/>
+      <c r="C589" s="4"/>
+    </row>
+    <row r="590" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A590" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B590" s="3"/>
+      <c r="C590" s="4"/>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A591" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="B591" s="3">
+        <v>6</v>
+      </c>
+      <c r="C591" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A592" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B592" s="3"/>
+      <c r="C592" s="4"/>
+    </row>
+    <row r="593" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A593" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B593" s="3"/>
+      <c r="C593" s="4"/>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A594" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="B594" s="3">
+        <v>5</v>
+      </c>
+      <c r="C594" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A595" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B595" s="3"/>
+      <c r="C595" s="4"/>
+    </row>
+    <row r="596" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A596" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B596" s="3"/>
+      <c r="C596" s="4"/>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A597" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="B597" s="3">
+        <v>4</v>
+      </c>
+      <c r="C597" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A598" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B598" s="3"/>
+      <c r="C598" s="4"/>
+    </row>
+    <row r="599" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A599" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B599" s="3"/>
+      <c r="C599" s="4"/>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A600" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B600" s="3">
+        <v>2</v>
+      </c>
+      <c r="C600" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A601" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B601" s="3"/>
+      <c r="C601" s="4"/>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A602" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B602" s="3">
+        <v>2</v>
+      </c>
+      <c r="C602" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A603" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B603" s="3"/>
+      <c r="C603" s="4"/>
+    </row>
+    <row r="604" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A604" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B604" s="3"/>
+      <c r="C604" s="4"/>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A605" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B605" s="3">
+        <v>1</v>
+      </c>
+      <c r="C605" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A606" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B606" s="3"/>
+      <c r="C606" s="4"/>
+    </row>
+    <row r="607" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A607" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B607" s="3"/>
+      <c r="C607" s="4"/>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A608" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="B608" s="3"/>
+      <c r="C608" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A609" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B609" s="3"/>
+      <c r="C609" s="4"/>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A610" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="B610" s="3"/>
+      <c r="C610" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A611" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="B611" s="3"/>
+      <c r="C611" s="4"/>
+    </row>
+    <row r="612" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A612" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="B612" s="3"/>
+      <c r="C612" s="4"/>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A613" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="B613" s="3"/>
+      <c r="C613" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A614" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B614" s="3"/>
+      <c r="C614" s="4"/>
+    </row>
+    <row r="615" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A615" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B615" s="3"/>
+      <c r="C615" s="4"/>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A616" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="B616" s="3"/>
+      <c r="C616" s="4">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A617" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="B617" s="3"/>
+      <c r="C617" s="4"/>
+    </row>
+    <row r="618" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A618" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="B618" s="3"/>
+      <c r="C618" s="4"/>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A619" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="B619" s="3">
+        <v>23</v>
+      </c>
+      <c r="C619" s="6">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A620" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B620" s="3"/>
+      <c r="C620" s="6"/>
+    </row>
+    <row r="621" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A621" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="B621" s="3"/>
+      <c r="C621" s="6"/>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A622" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="B622" s="3">
+        <v>18</v>
+      </c>
+      <c r="C622" s="6">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A623" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B623" s="3"/>
+      <c r="C623" s="6"/>
+    </row>
+    <row r="624" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A624" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B624" s="3"/>
+      <c r="C624" s="6"/>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A625" s="1" t="s">
+        <v>579</v>
+      </c>
+      <c r="B625" s="3">
+        <v>18</v>
+      </c>
+      <c r="C625" s="6">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A626" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B626" s="3"/>
+      <c r="C626" s="6"/>
+    </row>
+    <row r="627" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A627" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B627" s="3"/>
+      <c r="C627" s="6"/>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A628" s="1" t="s">
+        <v>580</v>
+      </c>
+      <c r="B628" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="C628" s="6">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A629" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B629" s="5"/>
+      <c r="C629" s="6"/>
+    </row>
+    <row r="630" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A630" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B630" s="5"/>
+      <c r="C630" s="6"/>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A631" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B631" s="3">
+        <v>14</v>
+      </c>
+      <c r="C631" s="6">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A632" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B632" s="3"/>
+      <c r="C632" s="6"/>
+    </row>
+    <row r="633" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A633" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="B633" s="3"/>
+      <c r="C633" s="6"/>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A634" s="1" t="s">
+        <v>586</v>
+      </c>
+      <c r="B634" s="3">
+        <v>12</v>
+      </c>
+      <c r="C634" s="6">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A635" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B635" s="3"/>
+      <c r="C635" s="6"/>
+    </row>
+    <row r="636" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A636" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B636" s="3"/>
+      <c r="C636" s="6"/>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A637" s="1" t="s">
+        <v>587</v>
+      </c>
+      <c r="B637" s="3">
+        <v>9</v>
+      </c>
+      <c r="C637" s="6">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A638" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B638" s="3"/>
+      <c r="C638" s="6"/>
+    </row>
+    <row r="639" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A639" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B639" s="3"/>
+      <c r="C639" s="6"/>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A640" s="1" t="s">
+        <v>588</v>
+      </c>
+      <c r="B640" s="3">
+        <v>7</v>
+      </c>
+      <c r="C640" s="6">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A641" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B641" s="3"/>
+      <c r="C641" s="6"/>
+    </row>
+    <row r="642" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A642" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B642" s="3"/>
+      <c r="C642" s="6"/>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A643" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B643" s="3">
+        <v>6</v>
+      </c>
+      <c r="C643" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A644" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B644" s="3"/>
+      <c r="C644" s="6"/>
+    </row>
+    <row r="645" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A645" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="B645" s="3"/>
+      <c r="C645" s="6"/>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A646" s="1" t="s">
+        <v>590</v>
+      </c>
+      <c r="B646" s="3">
+        <v>5</v>
+      </c>
+      <c r="C646" s="6">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A647" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B647" s="3"/>
+      <c r="C647" s="6"/>
+    </row>
+    <row r="648" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A648" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B648" s="3"/>
+      <c r="C648" s="6"/>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A649" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="B649" s="3">
+        <v>3</v>
+      </c>
+      <c r="C649" s="6">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A650" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B650" s="3"/>
+      <c r="C650" s="6"/>
+    </row>
+    <row r="651" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A651" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B651" s="3"/>
+      <c r="C651" s="6"/>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A652" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="B652" s="3">
+        <v>2</v>
+      </c>
+      <c r="C652" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A653" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B653" s="3"/>
+      <c r="C653" s="6"/>
+    </row>
+    <row r="654" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A654" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B654" s="3"/>
+      <c r="C654" s="6"/>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A655" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="B655" s="3">
+        <v>2</v>
+      </c>
+      <c r="C655" s="6">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A656" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B656" s="3"/>
+      <c r="C656" s="6"/>
+    </row>
+    <row r="657" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A657" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="B657" s="3"/>
+      <c r="C657" s="6"/>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A658" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="B658" s="3">
+        <v>1</v>
+      </c>
+      <c r="C658" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A659" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B659" s="3"/>
+      <c r="C659" s="6"/>
+    </row>
+    <row r="660" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A660" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B660" s="3"/>
+      <c r="C660" s="6"/>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A661" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="B661" s="3">
+        <v>1</v>
+      </c>
+      <c r="C661" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A662" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B662" s="3"/>
+      <c r="C662" s="6"/>
+    </row>
+    <row r="663" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A663" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B663" s="3"/>
+      <c r="C663" s="6"/>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A664" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B664" s="3"/>
+      <c r="C664" s="6">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A665" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B665" s="3"/>
+      <c r="C665" s="6"/>
+    </row>
+    <row r="666" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A666" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B666" s="3"/>
+      <c r="C666" s="6"/>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A667" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="B667" s="3"/>
+      <c r="C667" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A668" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B668" s="3"/>
+      <c r="C668" s="6"/>
+    </row>
+    <row r="669" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A669" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B669" s="3"/>
+      <c r="C669" s="6"/>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A670" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="B670" s="3"/>
+      <c r="C670" s="6">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="671" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A671" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B671" s="3"/>
+      <c r="C671" s="6"/>
+    </row>
+    <row r="672" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A672" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B672" s="3"/>
+      <c r="C672" s="6"/>
+    </row>
+    <row r="673" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A673" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="B673" s="3"/>
+      <c r="C673" s="6">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="674" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A674" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="B674" s="3"/>
+      <c r="C674" s="6"/>
+    </row>
+    <row r="675" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A675" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B675" s="3"/>
+      <c r="C675" s="6"/>
+    </row>
+    <row r="676" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A676" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B676" s="3"/>
+      <c r="C676" s="6">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="677" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A677" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B677" s="3"/>
+      <c r="C677" s="6"/>
+    </row>
+    <row r="678" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A678" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="B678" s="3"/>
+      <c r="C678" s="6"/>
+    </row>
+    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A679" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="B679" s="3"/>
+      <c r="C679" s="6">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="680" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A680" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B680" s="3"/>
+      <c r="C680" s="6"/>
+    </row>
+    <row r="681" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A681" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B681" s="3">
+        <v>59</v>
+      </c>
+      <c r="C681" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="682" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A682" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B682" s="3"/>
+      <c r="C682" s="4"/>
+    </row>
+    <row r="683" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A683" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B683" s="3"/>
+      <c r="C683" s="4"/>
+    </row>
+    <row r="684" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A684" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B684" s="3">
+        <v>42</v>
+      </c>
+      <c r="C684" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="685" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A685" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B685" s="3"/>
+      <c r="C685" s="4"/>
+    </row>
+    <row r="686" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A686" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B686" s="3"/>
+      <c r="C686" s="4"/>
+    </row>
+    <row r="687" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A687" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B687" s="3">
+        <v>31</v>
+      </c>
+      <c r="C687" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="688" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A688" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B688" s="3"/>
+      <c r="C688" s="4"/>
+    </row>
+    <row r="689" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A689" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B689" s="3"/>
+      <c r="C689" s="4"/>
+    </row>
+    <row r="690" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A690" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B690" s="3">
+        <v>8</v>
+      </c>
+      <c r="C690" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="691" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A691" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B691" s="3"/>
+      <c r="C691" s="4"/>
+    </row>
+    <row r="692" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A692" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B692" s="3"/>
+      <c r="C692" s="4"/>
+    </row>
+    <row r="693" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A693" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B693" s="3">
+        <v>8</v>
+      </c>
+      <c r="C693" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="694" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A694" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B694" s="3"/>
+      <c r="C694" s="4"/>
+    </row>
+    <row r="695" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A695" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B695" s="3"/>
+      <c r="C695" s="4"/>
+    </row>
+    <row r="696" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A696" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B696" s="3">
+        <v>2</v>
+      </c>
+      <c r="C696" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="697" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A697" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B697" s="3"/>
+      <c r="C697" s="4"/>
+    </row>
+    <row r="698" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A698" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B698" s="3"/>
+      <c r="C698" s="4"/>
+    </row>
+    <row r="699" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A699" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B699" s="3"/>
+      <c r="C699" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="700" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A700" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B700" s="3"/>
+      <c r="C700" s="4"/>
+    </row>
+    <row r="701" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A701" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B701" s="3"/>
+      <c r="C701" s="4"/>
+    </row>
+    <row r="702" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A702" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B702" s="3"/>
+      <c r="C702" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="703" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A703" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B703" s="3"/>
+      <c r="C703" s="4"/>
+    </row>
+    <row r="704" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A704" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B704" s="3"/>
+      <c r="C704" s="4"/>
+    </row>
+    <row r="705" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A705" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B705" s="3"/>
+      <c r="C705" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="706" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A706" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B706" s="3"/>
+      <c r="C706" s="4"/>
+    </row>
+    <row r="707" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A707" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B707" s="3"/>
+      <c r="C707" s="4"/>
+    </row>
+    <row r="708" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A708" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="B708" s="3"/>
+      <c r="C708" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="709" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A709" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B709" s="3"/>
+      <c r="C709" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="376">
-    <mergeCell ref="B556:B557"/>
-    <mergeCell ref="C556:C557"/>
-    <mergeCell ref="B558:B560"/>
-    <mergeCell ref="C558:C560"/>
-    <mergeCell ref="B548:B550"/>
-    <mergeCell ref="C548:C550"/>
-    <mergeCell ref="B551:B552"/>
-    <mergeCell ref="C551:C552"/>
-    <mergeCell ref="B553:B555"/>
-    <mergeCell ref="C553:C555"/>
+  <mergeCells count="478">
+    <mergeCell ref="B699:B701"/>
+    <mergeCell ref="C699:C701"/>
+    <mergeCell ref="B702:B704"/>
+    <mergeCell ref="C702:C704"/>
+    <mergeCell ref="B705:B707"/>
+    <mergeCell ref="C705:C707"/>
+    <mergeCell ref="B708:B709"/>
+    <mergeCell ref="C708:C709"/>
+    <mergeCell ref="B684:B686"/>
+    <mergeCell ref="C684:C686"/>
+    <mergeCell ref="B687:B689"/>
+    <mergeCell ref="C687:C689"/>
+    <mergeCell ref="B690:B692"/>
+    <mergeCell ref="C690:C692"/>
+    <mergeCell ref="B693:B695"/>
+    <mergeCell ref="C693:C695"/>
+    <mergeCell ref="B696:B698"/>
+    <mergeCell ref="C696:C698"/>
+    <mergeCell ref="B670:B672"/>
+    <mergeCell ref="C670:C672"/>
+    <mergeCell ref="B673:B675"/>
+    <mergeCell ref="C673:C675"/>
+    <mergeCell ref="B676:B678"/>
+    <mergeCell ref="C676:C678"/>
+    <mergeCell ref="B679:B680"/>
+    <mergeCell ref="C679:C680"/>
+    <mergeCell ref="B681:B683"/>
+    <mergeCell ref="C681:C683"/>
+    <mergeCell ref="B655:B657"/>
+    <mergeCell ref="C655:C657"/>
+    <mergeCell ref="B658:B660"/>
+    <mergeCell ref="C658:C660"/>
+    <mergeCell ref="B661:B663"/>
+    <mergeCell ref="C661:C663"/>
+    <mergeCell ref="B664:B666"/>
+    <mergeCell ref="C664:C666"/>
+    <mergeCell ref="B667:B669"/>
+    <mergeCell ref="C667:C669"/>
+    <mergeCell ref="B640:B642"/>
+    <mergeCell ref="C640:C642"/>
+    <mergeCell ref="B643:B645"/>
+    <mergeCell ref="C643:C645"/>
+    <mergeCell ref="B646:B648"/>
+    <mergeCell ref="C646:C648"/>
+    <mergeCell ref="B649:B651"/>
+    <mergeCell ref="C649:C651"/>
+    <mergeCell ref="B652:B654"/>
+    <mergeCell ref="C652:C654"/>
+    <mergeCell ref="B625:B627"/>
+    <mergeCell ref="C625:C627"/>
+    <mergeCell ref="B628:B630"/>
+    <mergeCell ref="C628:C630"/>
+    <mergeCell ref="B631:B633"/>
+    <mergeCell ref="C631:C633"/>
+    <mergeCell ref="B634:B636"/>
+    <mergeCell ref="C634:C636"/>
+    <mergeCell ref="B637:B639"/>
+    <mergeCell ref="C637:C639"/>
+    <mergeCell ref="B610:B612"/>
+    <mergeCell ref="C610:C612"/>
+    <mergeCell ref="B613:B615"/>
+    <mergeCell ref="C613:C615"/>
+    <mergeCell ref="B616:B618"/>
+    <mergeCell ref="C616:C618"/>
+    <mergeCell ref="B619:B621"/>
+    <mergeCell ref="C619:C621"/>
+    <mergeCell ref="B622:B624"/>
+    <mergeCell ref="C622:C624"/>
+    <mergeCell ref="B597:B599"/>
+    <mergeCell ref="C597:C599"/>
+    <mergeCell ref="B600:B601"/>
+    <mergeCell ref="C600:C601"/>
+    <mergeCell ref="B602:B604"/>
+    <mergeCell ref="C602:C604"/>
+    <mergeCell ref="B605:B607"/>
+    <mergeCell ref="C605:C607"/>
+    <mergeCell ref="B608:B609"/>
+    <mergeCell ref="C608:C609"/>
+    <mergeCell ref="B582:B584"/>
+    <mergeCell ref="C582:C584"/>
+    <mergeCell ref="B585:B587"/>
+    <mergeCell ref="C585:C587"/>
+    <mergeCell ref="B588:B590"/>
+    <mergeCell ref="C588:C590"/>
+    <mergeCell ref="B591:B593"/>
+    <mergeCell ref="C591:C593"/>
+    <mergeCell ref="B594:B596"/>
+    <mergeCell ref="C594:C596"/>
+    <mergeCell ref="B567:B569"/>
+    <mergeCell ref="C567:C569"/>
+    <mergeCell ref="B570:B572"/>
+    <mergeCell ref="C570:C572"/>
+    <mergeCell ref="B573:B575"/>
+    <mergeCell ref="C573:C575"/>
+    <mergeCell ref="B576:B578"/>
+    <mergeCell ref="C576:C578"/>
+    <mergeCell ref="B579:B581"/>
+    <mergeCell ref="C579:C581"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="C4:C6"/>
+    <mergeCell ref="B7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="B561:B563"/>
+    <mergeCell ref="C561:C563"/>
+    <mergeCell ref="B564:B566"/>
+    <mergeCell ref="C564:C566"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="B22:B24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="B25:B27"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="C91:C93"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="C115:C117"/>
+    <mergeCell ref="B100:B102"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="B127:B129"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="C133:C135"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="C124:C126"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="C148:C150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="C151:C153"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="C136:C138"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="C139:C141"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="C142:C144"/>
+    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="C163:C165"/>
+    <mergeCell ref="B166:B168"/>
+    <mergeCell ref="C166:C168"/>
+    <mergeCell ref="B169:B171"/>
+    <mergeCell ref="C169:C171"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="C154:C156"/>
+    <mergeCell ref="B157:B159"/>
+    <mergeCell ref="C157:C159"/>
+    <mergeCell ref="B160:B162"/>
+    <mergeCell ref="C160:C162"/>
+    <mergeCell ref="B181:B183"/>
+    <mergeCell ref="C181:C183"/>
+    <mergeCell ref="B184:B186"/>
+    <mergeCell ref="C184:C186"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="C187:C189"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="C172:C174"/>
+    <mergeCell ref="B175:B177"/>
+    <mergeCell ref="C175:C177"/>
+    <mergeCell ref="B178:B180"/>
+    <mergeCell ref="C178:C180"/>
+    <mergeCell ref="B199:B201"/>
+    <mergeCell ref="C199:C201"/>
+    <mergeCell ref="B202:B204"/>
+    <mergeCell ref="C202:C204"/>
+    <mergeCell ref="B205:B207"/>
+    <mergeCell ref="C205:C207"/>
+    <mergeCell ref="B190:B192"/>
+    <mergeCell ref="C190:C192"/>
+    <mergeCell ref="B193:B195"/>
+    <mergeCell ref="C193:C195"/>
+    <mergeCell ref="B196:B198"/>
+    <mergeCell ref="C196:C198"/>
+    <mergeCell ref="B217:B219"/>
+    <mergeCell ref="C217:C219"/>
+    <mergeCell ref="B220:B222"/>
+    <mergeCell ref="C220:C222"/>
+    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="C223:C225"/>
+    <mergeCell ref="B208:B210"/>
+    <mergeCell ref="C208:C210"/>
+    <mergeCell ref="B211:B213"/>
+    <mergeCell ref="C211:C213"/>
+    <mergeCell ref="B214:B216"/>
+    <mergeCell ref="C214:C216"/>
+    <mergeCell ref="B235:B237"/>
+    <mergeCell ref="C235:C237"/>
+    <mergeCell ref="B238:B240"/>
+    <mergeCell ref="C238:C240"/>
+    <mergeCell ref="B241:B243"/>
+    <mergeCell ref="C241:C243"/>
+    <mergeCell ref="B226:B228"/>
+    <mergeCell ref="C226:C228"/>
+    <mergeCell ref="B229:B231"/>
+    <mergeCell ref="C229:C231"/>
+    <mergeCell ref="B232:B234"/>
+    <mergeCell ref="C232:C234"/>
+    <mergeCell ref="B253:B255"/>
+    <mergeCell ref="C253:C255"/>
+    <mergeCell ref="B256:B258"/>
+    <mergeCell ref="C256:C258"/>
+    <mergeCell ref="B259:B261"/>
+    <mergeCell ref="C259:C261"/>
+    <mergeCell ref="B244:B246"/>
+    <mergeCell ref="C244:C246"/>
+    <mergeCell ref="B247:B249"/>
+    <mergeCell ref="C247:C249"/>
+    <mergeCell ref="B250:B252"/>
+    <mergeCell ref="C250:C252"/>
+    <mergeCell ref="B271:B273"/>
+    <mergeCell ref="C271:C273"/>
+    <mergeCell ref="B274:B276"/>
+    <mergeCell ref="C274:C276"/>
+    <mergeCell ref="B277:B279"/>
+    <mergeCell ref="C277:C279"/>
+    <mergeCell ref="B262:B264"/>
+    <mergeCell ref="C262:C264"/>
+    <mergeCell ref="B265:B267"/>
+    <mergeCell ref="C265:C267"/>
+    <mergeCell ref="B268:B270"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="B289:B291"/>
+    <mergeCell ref="C289:C291"/>
+    <mergeCell ref="B292:B294"/>
+    <mergeCell ref="C292:C294"/>
+    <mergeCell ref="B295:B297"/>
+    <mergeCell ref="C295:C297"/>
+    <mergeCell ref="B280:B282"/>
+    <mergeCell ref="C280:C282"/>
+    <mergeCell ref="B283:B285"/>
+    <mergeCell ref="C283:C285"/>
+    <mergeCell ref="B286:B288"/>
+    <mergeCell ref="C286:C288"/>
+    <mergeCell ref="B307:B309"/>
+    <mergeCell ref="C307:C309"/>
+    <mergeCell ref="B310:B312"/>
+    <mergeCell ref="C310:C312"/>
+    <mergeCell ref="B313:B315"/>
+    <mergeCell ref="C313:C315"/>
+    <mergeCell ref="B298:B300"/>
+    <mergeCell ref="C298:C300"/>
+    <mergeCell ref="B301:B303"/>
+    <mergeCell ref="C301:C303"/>
+    <mergeCell ref="B304:B306"/>
+    <mergeCell ref="C304:C306"/>
+    <mergeCell ref="B325:B327"/>
+    <mergeCell ref="C325:C327"/>
+    <mergeCell ref="B328:B330"/>
+    <mergeCell ref="C328:C330"/>
+    <mergeCell ref="B331:B333"/>
+    <mergeCell ref="C331:C333"/>
+    <mergeCell ref="B316:B318"/>
+    <mergeCell ref="C316:C318"/>
+    <mergeCell ref="B319:B321"/>
+    <mergeCell ref="C319:C321"/>
+    <mergeCell ref="B322:B324"/>
+    <mergeCell ref="C322:C324"/>
+    <mergeCell ref="B343:B345"/>
+    <mergeCell ref="C343:C345"/>
+    <mergeCell ref="B346:B348"/>
+    <mergeCell ref="C346:C348"/>
+    <mergeCell ref="B349:B351"/>
+    <mergeCell ref="C349:C351"/>
+    <mergeCell ref="B334:B336"/>
+    <mergeCell ref="C334:C336"/>
+    <mergeCell ref="B337:B339"/>
+    <mergeCell ref="C337:C339"/>
+    <mergeCell ref="B340:B342"/>
+    <mergeCell ref="C340:C342"/>
+    <mergeCell ref="B361:B363"/>
+    <mergeCell ref="C361:C363"/>
+    <mergeCell ref="B364:B366"/>
+    <mergeCell ref="C364:C366"/>
+    <mergeCell ref="B367:B369"/>
+    <mergeCell ref="C367:C369"/>
+    <mergeCell ref="B352:B354"/>
+    <mergeCell ref="C352:C354"/>
+    <mergeCell ref="B355:B357"/>
+    <mergeCell ref="C355:C357"/>
+    <mergeCell ref="B358:B360"/>
+    <mergeCell ref="C358:C360"/>
+    <mergeCell ref="B379:B381"/>
+    <mergeCell ref="C379:C381"/>
+    <mergeCell ref="B382:B384"/>
+    <mergeCell ref="C382:C384"/>
+    <mergeCell ref="B385:B387"/>
+    <mergeCell ref="C385:C387"/>
+    <mergeCell ref="B370:B372"/>
+    <mergeCell ref="C370:C372"/>
+    <mergeCell ref="B373:B375"/>
+    <mergeCell ref="C373:C375"/>
+    <mergeCell ref="B376:B378"/>
+    <mergeCell ref="C376:C378"/>
+    <mergeCell ref="B397:B399"/>
+    <mergeCell ref="C397:C399"/>
+    <mergeCell ref="B400:B402"/>
+    <mergeCell ref="C400:C402"/>
+    <mergeCell ref="B403:B405"/>
+    <mergeCell ref="C403:C405"/>
+    <mergeCell ref="B388:B390"/>
+    <mergeCell ref="C388:C390"/>
+    <mergeCell ref="B391:B393"/>
+    <mergeCell ref="C391:C393"/>
+    <mergeCell ref="B394:B396"/>
+    <mergeCell ref="C394:C396"/>
+    <mergeCell ref="B415:B417"/>
+    <mergeCell ref="C415:C417"/>
+    <mergeCell ref="B418:B420"/>
+    <mergeCell ref="C418:C420"/>
+    <mergeCell ref="B421:B423"/>
+    <mergeCell ref="C421:C423"/>
+    <mergeCell ref="B406:B408"/>
+    <mergeCell ref="C406:C408"/>
+    <mergeCell ref="B409:B411"/>
+    <mergeCell ref="C409:C411"/>
+    <mergeCell ref="B412:B414"/>
+    <mergeCell ref="C412:C414"/>
+    <mergeCell ref="B433:B435"/>
+    <mergeCell ref="C433:C435"/>
+    <mergeCell ref="B436:B438"/>
+    <mergeCell ref="C436:C438"/>
+    <mergeCell ref="B439:B441"/>
+    <mergeCell ref="C439:C441"/>
+    <mergeCell ref="B424:B426"/>
+    <mergeCell ref="C424:C426"/>
+    <mergeCell ref="B427:B429"/>
+    <mergeCell ref="C427:C429"/>
+    <mergeCell ref="B430:B432"/>
+    <mergeCell ref="C430:C432"/>
+    <mergeCell ref="B450:B452"/>
+    <mergeCell ref="C450:C452"/>
+    <mergeCell ref="B453:B455"/>
+    <mergeCell ref="C453:C455"/>
+    <mergeCell ref="B456:B458"/>
+    <mergeCell ref="C456:C458"/>
+    <mergeCell ref="B442:B444"/>
+    <mergeCell ref="C442:C444"/>
+    <mergeCell ref="B445:B447"/>
+    <mergeCell ref="C445:C447"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="C448:C449"/>
+    <mergeCell ref="B468:B470"/>
+    <mergeCell ref="C468:C470"/>
+    <mergeCell ref="B471:B473"/>
+    <mergeCell ref="C471:C473"/>
+    <mergeCell ref="B474:B476"/>
+    <mergeCell ref="C474:C476"/>
+    <mergeCell ref="B459:B461"/>
+    <mergeCell ref="C459:C461"/>
+    <mergeCell ref="B462:B464"/>
+    <mergeCell ref="C462:C464"/>
+    <mergeCell ref="B465:B467"/>
+    <mergeCell ref="C465:C467"/>
+    <mergeCell ref="B485:B487"/>
+    <mergeCell ref="C485:C487"/>
+    <mergeCell ref="B488:B490"/>
+    <mergeCell ref="C488:C490"/>
+    <mergeCell ref="B491:B493"/>
+    <mergeCell ref="C491:C493"/>
+    <mergeCell ref="B477:B479"/>
+    <mergeCell ref="C477:C479"/>
+    <mergeCell ref="B480:B482"/>
+    <mergeCell ref="C480:C482"/>
+    <mergeCell ref="B483:B484"/>
+    <mergeCell ref="C483:C484"/>
+    <mergeCell ref="B503:B505"/>
+    <mergeCell ref="C503:C505"/>
+    <mergeCell ref="B506:B508"/>
+    <mergeCell ref="C506:C508"/>
+    <mergeCell ref="B509:B511"/>
+    <mergeCell ref="C509:C511"/>
+    <mergeCell ref="B494:B496"/>
+    <mergeCell ref="C494:C496"/>
+    <mergeCell ref="B497:B499"/>
+    <mergeCell ref="C497:C499"/>
+    <mergeCell ref="B500:B502"/>
+    <mergeCell ref="C500:C502"/>
+    <mergeCell ref="B521:B523"/>
+    <mergeCell ref="C521:C523"/>
+    <mergeCell ref="B524:B526"/>
+    <mergeCell ref="C524:C526"/>
+    <mergeCell ref="B527:B529"/>
+    <mergeCell ref="C527:C529"/>
+    <mergeCell ref="B512:B514"/>
+    <mergeCell ref="C512:C514"/>
+    <mergeCell ref="B515:B517"/>
+    <mergeCell ref="C515:C517"/>
+    <mergeCell ref="B518:B520"/>
+    <mergeCell ref="C518:C520"/>
     <mergeCell ref="B539:B541"/>
     <mergeCell ref="C539:C541"/>
     <mergeCell ref="B542:B544"/>
@@ -6709,360 +8715,16 @@
     <mergeCell ref="C533:C535"/>
     <mergeCell ref="B536:B538"/>
     <mergeCell ref="C536:C538"/>
-    <mergeCell ref="B521:B523"/>
-    <mergeCell ref="C521:C523"/>
-    <mergeCell ref="B524:B526"/>
-    <mergeCell ref="C524:C526"/>
-    <mergeCell ref="B527:B529"/>
-    <mergeCell ref="C527:C529"/>
-    <mergeCell ref="B512:B514"/>
-    <mergeCell ref="C512:C514"/>
-    <mergeCell ref="B515:B517"/>
-    <mergeCell ref="C515:C517"/>
-    <mergeCell ref="B518:B520"/>
-    <mergeCell ref="C518:C520"/>
-    <mergeCell ref="B503:B505"/>
-    <mergeCell ref="C503:C505"/>
-    <mergeCell ref="B506:B508"/>
-    <mergeCell ref="C506:C508"/>
-    <mergeCell ref="B509:B511"/>
-    <mergeCell ref="C509:C511"/>
-    <mergeCell ref="B494:B496"/>
-    <mergeCell ref="C494:C496"/>
-    <mergeCell ref="B497:B499"/>
-    <mergeCell ref="C497:C499"/>
-    <mergeCell ref="B500:B502"/>
-    <mergeCell ref="C500:C502"/>
-    <mergeCell ref="B485:B487"/>
-    <mergeCell ref="C485:C487"/>
-    <mergeCell ref="B488:B490"/>
-    <mergeCell ref="C488:C490"/>
-    <mergeCell ref="B491:B493"/>
-    <mergeCell ref="C491:C493"/>
-    <mergeCell ref="B477:B479"/>
-    <mergeCell ref="C477:C479"/>
-    <mergeCell ref="B480:B482"/>
-    <mergeCell ref="C480:C482"/>
-    <mergeCell ref="B483:B484"/>
-    <mergeCell ref="C483:C484"/>
-    <mergeCell ref="B468:B470"/>
-    <mergeCell ref="C468:C470"/>
-    <mergeCell ref="B471:B473"/>
-    <mergeCell ref="C471:C473"/>
-    <mergeCell ref="B474:B476"/>
-    <mergeCell ref="C474:C476"/>
-    <mergeCell ref="B459:B461"/>
-    <mergeCell ref="C459:C461"/>
-    <mergeCell ref="B462:B464"/>
-    <mergeCell ref="C462:C464"/>
-    <mergeCell ref="B465:B467"/>
-    <mergeCell ref="C465:C467"/>
-    <mergeCell ref="B450:B452"/>
-    <mergeCell ref="C450:C452"/>
-    <mergeCell ref="B453:B455"/>
-    <mergeCell ref="C453:C455"/>
-    <mergeCell ref="B456:B458"/>
-    <mergeCell ref="C456:C458"/>
-    <mergeCell ref="B442:B444"/>
-    <mergeCell ref="C442:C444"/>
-    <mergeCell ref="B445:B447"/>
-    <mergeCell ref="C445:C447"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="C448:C449"/>
-    <mergeCell ref="B433:B435"/>
-    <mergeCell ref="C433:C435"/>
-    <mergeCell ref="B436:B438"/>
-    <mergeCell ref="C436:C438"/>
-    <mergeCell ref="B439:B441"/>
-    <mergeCell ref="C439:C441"/>
-    <mergeCell ref="B424:B426"/>
-    <mergeCell ref="C424:C426"/>
-    <mergeCell ref="B427:B429"/>
-    <mergeCell ref="C427:C429"/>
-    <mergeCell ref="B430:B432"/>
-    <mergeCell ref="C430:C432"/>
-    <mergeCell ref="B415:B417"/>
-    <mergeCell ref="C415:C417"/>
-    <mergeCell ref="B418:B420"/>
-    <mergeCell ref="C418:C420"/>
-    <mergeCell ref="B421:B423"/>
-    <mergeCell ref="C421:C423"/>
-    <mergeCell ref="B406:B408"/>
-    <mergeCell ref="C406:C408"/>
-    <mergeCell ref="B409:B411"/>
-    <mergeCell ref="C409:C411"/>
-    <mergeCell ref="B412:B414"/>
-    <mergeCell ref="C412:C414"/>
-    <mergeCell ref="B397:B399"/>
-    <mergeCell ref="C397:C399"/>
-    <mergeCell ref="B400:B402"/>
-    <mergeCell ref="C400:C402"/>
-    <mergeCell ref="B403:B405"/>
-    <mergeCell ref="C403:C405"/>
-    <mergeCell ref="B388:B390"/>
-    <mergeCell ref="C388:C390"/>
-    <mergeCell ref="B391:B393"/>
-    <mergeCell ref="C391:C393"/>
-    <mergeCell ref="B394:B396"/>
-    <mergeCell ref="C394:C396"/>
-    <mergeCell ref="B379:B381"/>
-    <mergeCell ref="C379:C381"/>
-    <mergeCell ref="B382:B384"/>
-    <mergeCell ref="C382:C384"/>
-    <mergeCell ref="B385:B387"/>
-    <mergeCell ref="C385:C387"/>
-    <mergeCell ref="B370:B372"/>
-    <mergeCell ref="C370:C372"/>
-    <mergeCell ref="B373:B375"/>
-    <mergeCell ref="C373:C375"/>
-    <mergeCell ref="B376:B378"/>
-    <mergeCell ref="C376:C378"/>
-    <mergeCell ref="B361:B363"/>
-    <mergeCell ref="C361:C363"/>
-    <mergeCell ref="B364:B366"/>
-    <mergeCell ref="C364:C366"/>
-    <mergeCell ref="B367:B369"/>
-    <mergeCell ref="C367:C369"/>
-    <mergeCell ref="B352:B354"/>
-    <mergeCell ref="C352:C354"/>
-    <mergeCell ref="B355:B357"/>
-    <mergeCell ref="C355:C357"/>
-    <mergeCell ref="B358:B360"/>
-    <mergeCell ref="C358:C360"/>
-    <mergeCell ref="B343:B345"/>
-    <mergeCell ref="C343:C345"/>
-    <mergeCell ref="B346:B348"/>
-    <mergeCell ref="C346:C348"/>
-    <mergeCell ref="B349:B351"/>
-    <mergeCell ref="C349:C351"/>
-    <mergeCell ref="B334:B336"/>
-    <mergeCell ref="C334:C336"/>
-    <mergeCell ref="B337:B339"/>
-    <mergeCell ref="C337:C339"/>
-    <mergeCell ref="B340:B342"/>
-    <mergeCell ref="C340:C342"/>
-    <mergeCell ref="B325:B327"/>
-    <mergeCell ref="C325:C327"/>
-    <mergeCell ref="B328:B330"/>
-    <mergeCell ref="C328:C330"/>
-    <mergeCell ref="B331:B333"/>
-    <mergeCell ref="C331:C333"/>
-    <mergeCell ref="B316:B318"/>
-    <mergeCell ref="C316:C318"/>
-    <mergeCell ref="B319:B321"/>
-    <mergeCell ref="C319:C321"/>
-    <mergeCell ref="B322:B324"/>
-    <mergeCell ref="C322:C324"/>
-    <mergeCell ref="B307:B309"/>
-    <mergeCell ref="C307:C309"/>
-    <mergeCell ref="B310:B312"/>
-    <mergeCell ref="C310:C312"/>
-    <mergeCell ref="B313:B315"/>
-    <mergeCell ref="C313:C315"/>
-    <mergeCell ref="B298:B300"/>
-    <mergeCell ref="C298:C300"/>
-    <mergeCell ref="B301:B303"/>
-    <mergeCell ref="C301:C303"/>
-    <mergeCell ref="B304:B306"/>
-    <mergeCell ref="C304:C306"/>
-    <mergeCell ref="B289:B291"/>
-    <mergeCell ref="C289:C291"/>
-    <mergeCell ref="B292:B294"/>
-    <mergeCell ref="C292:C294"/>
-    <mergeCell ref="B295:B297"/>
-    <mergeCell ref="C295:C297"/>
-    <mergeCell ref="B280:B282"/>
-    <mergeCell ref="C280:C282"/>
-    <mergeCell ref="B283:B285"/>
-    <mergeCell ref="C283:C285"/>
-    <mergeCell ref="B286:B288"/>
-    <mergeCell ref="C286:C288"/>
-    <mergeCell ref="B271:B273"/>
-    <mergeCell ref="C271:C273"/>
-    <mergeCell ref="B274:B276"/>
-    <mergeCell ref="C274:C276"/>
-    <mergeCell ref="B277:B279"/>
-    <mergeCell ref="C277:C279"/>
-    <mergeCell ref="B262:B264"/>
-    <mergeCell ref="C262:C264"/>
-    <mergeCell ref="B265:B267"/>
-    <mergeCell ref="C265:C267"/>
-    <mergeCell ref="B268:B270"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="B253:B255"/>
-    <mergeCell ref="C253:C255"/>
-    <mergeCell ref="B256:B258"/>
-    <mergeCell ref="C256:C258"/>
-    <mergeCell ref="B259:B261"/>
-    <mergeCell ref="C259:C261"/>
-    <mergeCell ref="B244:B246"/>
-    <mergeCell ref="C244:C246"/>
-    <mergeCell ref="B247:B249"/>
-    <mergeCell ref="C247:C249"/>
-    <mergeCell ref="B250:B252"/>
-    <mergeCell ref="C250:C252"/>
-    <mergeCell ref="B235:B237"/>
-    <mergeCell ref="C235:C237"/>
-    <mergeCell ref="B238:B240"/>
-    <mergeCell ref="C238:C240"/>
-    <mergeCell ref="B241:B243"/>
-    <mergeCell ref="C241:C243"/>
-    <mergeCell ref="B226:B228"/>
-    <mergeCell ref="C226:C228"/>
-    <mergeCell ref="B229:B231"/>
-    <mergeCell ref="C229:C231"/>
-    <mergeCell ref="B232:B234"/>
-    <mergeCell ref="C232:C234"/>
-    <mergeCell ref="B217:B219"/>
-    <mergeCell ref="C217:C219"/>
-    <mergeCell ref="B220:B222"/>
-    <mergeCell ref="C220:C222"/>
-    <mergeCell ref="B223:B225"/>
-    <mergeCell ref="C223:C225"/>
-    <mergeCell ref="B208:B210"/>
-    <mergeCell ref="C208:C210"/>
-    <mergeCell ref="B211:B213"/>
-    <mergeCell ref="C211:C213"/>
-    <mergeCell ref="B214:B216"/>
-    <mergeCell ref="C214:C216"/>
-    <mergeCell ref="B199:B201"/>
-    <mergeCell ref="C199:C201"/>
-    <mergeCell ref="B202:B204"/>
-    <mergeCell ref="C202:C204"/>
-    <mergeCell ref="B205:B207"/>
-    <mergeCell ref="C205:C207"/>
-    <mergeCell ref="B190:B192"/>
-    <mergeCell ref="C190:C192"/>
-    <mergeCell ref="B193:B195"/>
-    <mergeCell ref="C193:C195"/>
-    <mergeCell ref="B196:B198"/>
-    <mergeCell ref="C196:C198"/>
-    <mergeCell ref="B181:B183"/>
-    <mergeCell ref="C181:C183"/>
-    <mergeCell ref="B184:B186"/>
-    <mergeCell ref="C184:C186"/>
-    <mergeCell ref="B187:B189"/>
-    <mergeCell ref="C187:C189"/>
-    <mergeCell ref="B172:B174"/>
-    <mergeCell ref="C172:C174"/>
-    <mergeCell ref="B175:B177"/>
-    <mergeCell ref="C175:C177"/>
-    <mergeCell ref="B178:B180"/>
-    <mergeCell ref="C178:C180"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="C163:C165"/>
-    <mergeCell ref="B166:B168"/>
-    <mergeCell ref="C166:C168"/>
-    <mergeCell ref="B169:B171"/>
-    <mergeCell ref="C169:C171"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="C154:C156"/>
-    <mergeCell ref="B157:B159"/>
-    <mergeCell ref="C157:C159"/>
-    <mergeCell ref="B160:B162"/>
-    <mergeCell ref="C160:C162"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="C145:C147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="C148:C150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="C151:C153"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="C136:C138"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="C139:C141"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="C142:C144"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="B109:B111"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="B100:B102"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="C91:C93"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B97:B99"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="B22:B24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="B25:B27"/>
-    <mergeCell ref="C25:C27"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="C4:C6"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="B556:B557"/>
+    <mergeCell ref="C556:C557"/>
+    <mergeCell ref="B558:B560"/>
+    <mergeCell ref="C558:C560"/>
+    <mergeCell ref="B548:B550"/>
+    <mergeCell ref="C548:C550"/>
+    <mergeCell ref="B551:B552"/>
+    <mergeCell ref="C551:C552"/>
+    <mergeCell ref="B553:B555"/>
+    <mergeCell ref="C553:C555"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:xtRiw3GOFMkC" xr:uid="{0E1A47C0-B24F-A547-B175-807B2A556D7E}"/>
@@ -7436,6 +9098,107 @@
     <hyperlink ref="B556" r:id="rId340" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9513485110243366275" xr:uid="{EA64D2E5-0267-F541-A023-B046287144CA}"/>
     <hyperlink ref="A558" r:id="rId341" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=gJ4oeJEAAAAJ&amp;citation_for_view=gJ4oeJEAAAAJ:d1gkVwhDpl0C" xr:uid="{F20E747C-AD44-374A-A35B-4ED1CFA0451A}"/>
     <hyperlink ref="B558" r:id="rId342" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13387262746893670169" xr:uid="{BA87B8EC-DE94-344C-9678-0484D3591908}"/>
+    <hyperlink ref="A561" r:id="rId343" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:2osOgNQ5qMEC" xr:uid="{38323CF8-6FB9-A346-9004-9BCCB5D1ADF1}"/>
+    <hyperlink ref="B561" r:id="rId344" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=18438821309036428096" xr:uid="{4D227B07-A2DA-8440-8BF4-F1CD707B6767}"/>
+    <hyperlink ref="A564" r:id="rId345" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:9yKSN-GCB0IC" xr:uid="{7A2429BB-E8D8-1545-9615-C85E07B53FF3}"/>
+    <hyperlink ref="B564" r:id="rId346" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=10199253588006063450" xr:uid="{AB810BA5-DB5E-514C-BB90-946C09DD2DF4}"/>
+    <hyperlink ref="A567" r:id="rId347" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:d1gkVwhDpl0C" xr:uid="{BC7D4E69-C0F1-234F-933A-3421060894AF}"/>
+    <hyperlink ref="B567" r:id="rId348" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5394371955331720451,3464617528505037522" xr:uid="{8D45ADDF-E22F-B745-AB3A-968EFAB5F8F5}"/>
+    <hyperlink ref="A570" r:id="rId349" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:qjMakFHDy7sC" xr:uid="{299A71C5-9CA8-7E4C-A193-5CAC3B7419E5}"/>
+    <hyperlink ref="B570" r:id="rId350" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14682916917507945538" xr:uid="{0B8F4095-47E6-344A-80D8-E2BC1221D175}"/>
+    <hyperlink ref="A573" r:id="rId351" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:3fE2CSJIrl8C" xr:uid="{2A84EDE8-57CD-4749-9B6B-34A80D7BFCA4}"/>
+    <hyperlink ref="B573" r:id="rId352" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14518297721468927072" xr:uid="{A6EA550D-BE52-724E-B0C0-6BA07C8ADADA}"/>
+    <hyperlink ref="A576" r:id="rId353" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:5nxA0vEk-isC" xr:uid="{F7CEF5D7-6E09-924C-AC3E-E116821E97D9}"/>
+    <hyperlink ref="B576" r:id="rId354" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15431931766288051897" xr:uid="{570C1D8E-D822-EC44-9C69-FA8813ECD00B}"/>
+    <hyperlink ref="A579" r:id="rId355" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:W7OEmFMy1HYC" xr:uid="{A9D54770-C7FE-084D-BA80-D4D7137E6CFC}"/>
+    <hyperlink ref="B579" r:id="rId356" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15260255064978446488" xr:uid="{9137A70F-7B78-EC40-BFD7-D09C9C5838AF}"/>
+    <hyperlink ref="A582" r:id="rId357" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:UebtZRa9Y70C" xr:uid="{25C71EDA-279B-9842-8F38-F6E54234D0BD}"/>
+    <hyperlink ref="B582" r:id="rId358" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12384977865030484821" xr:uid="{A8855B04-63B7-8D4A-B15A-BECFEAC1F118}"/>
+    <hyperlink ref="A585" r:id="rId359" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Se3iqnhoufwC" xr:uid="{7737AD4C-2FEE-4544-BC03-6DCDDDA6AE7B}"/>
+    <hyperlink ref="B585" r:id="rId360" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11478491708220273652" xr:uid="{EF67D154-1548-9A42-AF2C-5B7E91B39544}"/>
+    <hyperlink ref="A588" r:id="rId361" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:eQOLeE2rZwMC" xr:uid="{E6865631-5B53-A248-B7FD-6DB49D735DC4}"/>
+    <hyperlink ref="B588" r:id="rId362" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=445594232509227482" xr:uid="{E5B78B03-61C6-1545-B4AF-8D09DC1B8D57}"/>
+    <hyperlink ref="A591" r:id="rId363" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Wp0gIr-vW9MC" xr:uid="{3DCC3FE4-B093-DC4C-9944-FB125D22C2DE}"/>
+    <hyperlink ref="B591" r:id="rId364" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=4599190040013596024" xr:uid="{5128CE87-B13B-2444-A3B6-093E5D21EACD}"/>
+    <hyperlink ref="A594" r:id="rId365" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Zph67rFs4hoC" xr:uid="{03E06999-84A5-5042-952A-CB02E53CB311}"/>
+    <hyperlink ref="B594" r:id="rId366" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=17221536997697496231" xr:uid="{2A15D51D-47B1-8B47-8FA6-869EBFB720E1}"/>
+    <hyperlink ref="A597" r:id="rId367" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:-f6ydRqryjwC" xr:uid="{CDFAD303-BAE2-B64B-9312-16F9EF60DAD9}"/>
+    <hyperlink ref="B597" r:id="rId368" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11247321173341005052" xr:uid="{031503EC-2C69-FF41-9758-8CF954D8D378}"/>
+    <hyperlink ref="A600" r:id="rId369" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:LkGwnXOMwfcC" xr:uid="{B690395B-D125-F44D-A06E-329C3B85D807}"/>
+    <hyperlink ref="B600" r:id="rId370" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11765246759472421603" xr:uid="{D896DEB7-902C-284A-ACB4-0E8683869642}"/>
+    <hyperlink ref="A602" r:id="rId371" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Y0pCki6q_DkC" xr:uid="{25227F6B-3550-DD46-A023-A96829CFC39E}"/>
+    <hyperlink ref="B602" r:id="rId372" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=17617524555772456740" xr:uid="{CAF87E98-7ADC-454D-8F27-FC97E11DED2E}"/>
+    <hyperlink ref="A605" r:id="rId373" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:4DMP91E08xMC" xr:uid="{A583228E-2B61-6B46-817E-E50216F43AAD}"/>
+    <hyperlink ref="B605" r:id="rId374" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11258725931960264031" xr:uid="{5AFEE5B4-4986-0648-A588-656828B8B0AB}"/>
+    <hyperlink ref="A608" r:id="rId375" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:mB3voiENLucC" xr:uid="{DA0884F2-9A8E-4243-A737-07050EA84AEA}"/>
+    <hyperlink ref="B608" xr:uid="{92884CA6-7D93-9E48-9499-83EB4E87643C}"/>
+    <hyperlink ref="A610" r:id="rId376" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:hFOr9nPyWt4C" xr:uid="{51180FB2-E55E-3248-9CD0-35C6132512BB}"/>
+    <hyperlink ref="B610" xr:uid="{A411A3D8-449E-E64D-BAC3-8BFB7FA555AF}"/>
+    <hyperlink ref="A613" r:id="rId377" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:YOwf2qJgpHMC" xr:uid="{D35FCF3D-732F-6144-A326-66C013C26801}"/>
+    <hyperlink ref="B613" xr:uid="{8DBF1737-CE95-0241-AF67-31AEF5B4D4FB}"/>
+    <hyperlink ref="A616" r:id="rId378" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:M3ejUd6NZC8C" xr:uid="{1AB2FAF2-6599-6744-85E7-0B4CA200039F}"/>
+    <hyperlink ref="B616" xr:uid="{941EF143-70B2-1543-B49C-0A32255D5826}"/>
+    <hyperlink ref="A619" r:id="rId379" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:_FxGoFyzp5QC" xr:uid="{04D3BF3D-AB71-6A43-8D99-C60D207B086A}"/>
+    <hyperlink ref="B619" r:id="rId380" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14943949718996492241,9295283714574589860" xr:uid="{55107CCA-6BD3-7E41-A5CE-994E76862821}"/>
+    <hyperlink ref="A622" r:id="rId381" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:YsMSGLbcyi4C" xr:uid="{AF42615C-0A8D-984F-AE74-DF10DAAD2273}"/>
+    <hyperlink ref="B622" r:id="rId382" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=13162351343408260130" xr:uid="{F5D734A1-0A7F-6F4C-BE93-0103F3DFDB37}"/>
+    <hyperlink ref="A625" r:id="rId383" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:WF5omc3nYNoC" xr:uid="{7485BA4D-AA5B-CD49-9FDF-7E04AD014BD6}"/>
+    <hyperlink ref="B625" r:id="rId384" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15445732360366845980,2096223136222651988" xr:uid="{34BBB573-C79F-CA42-AABB-58D30D5C343C}"/>
+    <hyperlink ref="A628" r:id="rId385" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:qjMakFHDy7sC" xr:uid="{99D9321F-A778-A346-A46D-704581189D38}"/>
+    <hyperlink ref="A631" r:id="rId386" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:2osOgNQ5qMEC" xr:uid="{AF0D195D-7C03-6A49-97A8-44E59FBA68D4}"/>
+    <hyperlink ref="B631" r:id="rId387" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=6892275663945815970" xr:uid="{3CC00941-739B-5B43-88C4-7E846ED67E12}"/>
+    <hyperlink ref="A634" r:id="rId388" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:u-x6o8ySG0sC" xr:uid="{6565E707-4911-A442-8AD3-87A69E8BF2FC}"/>
+    <hyperlink ref="B634" r:id="rId389" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=1505539922492679102" xr:uid="{B4FE0E29-BE24-4E4C-AFE2-8203AC8244B7}"/>
+    <hyperlink ref="A637" r:id="rId390" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:u5HHmVD_uO8C" xr:uid="{A1D9B95B-52AC-0945-92B4-2EE2A4A503B9}"/>
+    <hyperlink ref="B637" r:id="rId391" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=1195250452201948679" xr:uid="{B944A079-6782-D247-AC5F-8A2AF69D7DC6}"/>
+    <hyperlink ref="A640" r:id="rId392" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:W7OEmFMy1HYC" xr:uid="{2C3B0EDC-AE81-B945-800F-35ECE5619BB4}"/>
+    <hyperlink ref="B640" r:id="rId393" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12347233027893450893,4081673723780999764" xr:uid="{B221B3C1-375D-4A4D-829A-54E7B330E941}"/>
+    <hyperlink ref="A643" r:id="rId394" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Se3iqnhoufwC" xr:uid="{70A0535D-282F-E148-BA00-906BD07AB97E}"/>
+    <hyperlink ref="B643" r:id="rId395" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5518562443997509835" xr:uid="{222FC3B5-6B0E-E649-A849-78FFD283A757}"/>
+    <hyperlink ref="A646" r:id="rId396" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:zYLM7Y9cAGgC" xr:uid="{CA351F20-8381-994E-8831-A6E18260BA8A}"/>
+    <hyperlink ref="B646" r:id="rId397" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8639077744506763903" xr:uid="{0510EDE9-AF42-6D4B-8DE4-4E42197AAB05}"/>
+    <hyperlink ref="A649" r:id="rId398" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:UeHWp8X0CEIC" xr:uid="{34C7ED57-A208-2745-8BA4-90F1F2330EDA}"/>
+    <hyperlink ref="B649" r:id="rId399" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8398362486471036782" xr:uid="{57213D3F-1450-E844-BA14-644B833B6092}"/>
+    <hyperlink ref="A652" r:id="rId400" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:hqOjcs7Dif8C" xr:uid="{76528754-7F41-7849-AC1E-C5F99255D85A}"/>
+    <hyperlink ref="B652" r:id="rId401" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=13676995628850696864" xr:uid="{C30E8D6E-4E28-2945-891F-276BB5FB5135}"/>
+    <hyperlink ref="A655" r:id="rId402" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Y0pCki6q_DkC" xr:uid="{3ABE0018-5AB6-E14E-8CBD-F9A884C00A60}"/>
+    <hyperlink ref="B655" r:id="rId403" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12214531268750987377" xr:uid="{4929D805-6EAF-3F49-A4BA-68F0E1B1D0BB}"/>
+    <hyperlink ref="A658" r:id="rId404" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:5nxA0vEk-isC" xr:uid="{90E49A5D-3A85-3540-8EB9-4EADDC127403}"/>
+    <hyperlink ref="B658" r:id="rId405" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8557475709729251005" xr:uid="{3F327CF0-9A47-B044-A975-3E3FEF0351CE}"/>
+    <hyperlink ref="A661" r:id="rId406" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:UebtZRa9Y70C" xr:uid="{02CAF606-2149-0744-BAA5-8D9347D0968A}"/>
+    <hyperlink ref="B661" r:id="rId407" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=4390265008156162287" xr:uid="{ADE9C1A8-B8E6-4F48-BCD8-C12235519ECA}"/>
+    <hyperlink ref="A664" r:id="rId408" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:3fE2CSJIrl8C" xr:uid="{FD3ABF8A-A9F7-DE43-B440-EC98B0E16F94}"/>
+    <hyperlink ref="B664" xr:uid="{C971C95C-ABCD-8B40-8D81-F740BE830825}"/>
+    <hyperlink ref="A667" r:id="rId409" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:0EnyYjriUFMC" xr:uid="{3A9E737D-1822-464F-9091-E9B7BAF9DC84}"/>
+    <hyperlink ref="B667" xr:uid="{3599401A-8514-E44F-BD51-0451F08CE78E}"/>
+    <hyperlink ref="A670" r:id="rId410" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:8k81kl-MbHgC" xr:uid="{CD38D470-3A80-434D-9F5D-B3D7525E0800}"/>
+    <hyperlink ref="B670" xr:uid="{6C1056B1-5E2F-6D4D-AEE7-0C60A64A5887}"/>
+    <hyperlink ref="A673" r:id="rId411" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Tyk-4Ss8FVUC" xr:uid="{C78D2281-E55B-C746-A139-425869A51446}"/>
+    <hyperlink ref="B673" xr:uid="{DCF8A146-9B7F-2349-B2D2-5F6EA72D4CA4}"/>
+    <hyperlink ref="A676" r:id="rId412" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:IjCSPb-OGe4C" xr:uid="{0D3A73C3-6304-A045-80F5-9105FED4A9D6}"/>
+    <hyperlink ref="B676" xr:uid="{8E4F6276-9FF3-1449-BE25-8AE55ED093A1}"/>
+    <hyperlink ref="A679" r:id="rId413" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=MhVneNwAAAAJ:ufrVoPGSRksC" xr:uid="{ADEAA86B-1406-FC4D-AD92-9B84A4AA5796}"/>
+    <hyperlink ref="B679" xr:uid="{8134520B-D207-1440-BF89-A7125B3B0847}"/>
+    <hyperlink ref="A681" r:id="rId414" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:IjCSPb-OGe4C" xr:uid="{57EBE04C-1694-DE4C-8F3E-541B3015BDB6}"/>
+    <hyperlink ref="B681" r:id="rId415" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12125926802820743093" xr:uid="{D9668CC8-08E4-4942-BA77-2622EEB1CDE1}"/>
+    <hyperlink ref="A684" r:id="rId416" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:9yKSN-GCB0IC" xr:uid="{A367D32F-1923-8040-B461-F8624F16EB4F}"/>
+    <hyperlink ref="B684" r:id="rId417" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=7380889746393990269" xr:uid="{C5170D3E-8E00-F649-B907-168EE34CA7F2}"/>
+    <hyperlink ref="A687" r:id="rId418" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:d1gkVwhDpl0C" xr:uid="{336B9BA8-1FDF-3543-85D8-8ABDB1DBC7EA}"/>
+    <hyperlink ref="B687" r:id="rId419" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=895373070968311813" xr:uid="{F5A0C93E-407D-E945-B079-07A65DA11227}"/>
+    <hyperlink ref="A690" r:id="rId420" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:Y0pCki6q_DkC" xr:uid="{76322B4C-7C8D-6240-8BA6-C4320F2612C0}"/>
+    <hyperlink ref="B690" r:id="rId421" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=16759362408447206514" xr:uid="{04C2EAD0-53D9-5240-921A-A54CFDB8ADBE}"/>
+    <hyperlink ref="A693" r:id="rId422" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:qjMakFHDy7sC" xr:uid="{3B2E40B8-0DC3-BB43-81AA-2C6079D248D2}"/>
+    <hyperlink ref="B693" r:id="rId423" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9327618205908924005" xr:uid="{059B5B34-4E5D-AC45-B735-B4D212FB981B}"/>
+    <hyperlink ref="A696" r:id="rId424" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:YsMSGLbcyi4C" xr:uid="{3101AD4B-BFB6-EC4D-BF89-D1BC73AE0F9A}"/>
+    <hyperlink ref="B696" r:id="rId425" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9572686037325897793" xr:uid="{C5866D2F-76D9-1A4E-A7DA-5A873A5A69D9}"/>
+    <hyperlink ref="A699" r:id="rId426" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:UeHWp8X0CEIC" xr:uid="{D00B9E9E-650E-9C44-AC72-E25A39FE49F2}"/>
+    <hyperlink ref="B699" xr:uid="{12A15543-E927-2749-B30A-99C906709ECF}"/>
+    <hyperlink ref="A702" r:id="rId427" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:u-x6o8ySG0sC" xr:uid="{0CAD1EB8-94D0-9648-9588-39AC16B81326}"/>
+    <hyperlink ref="B702" xr:uid="{934E254C-B7C1-C244-BC93-6F2069D5C9BD}"/>
+    <hyperlink ref="A705" r:id="rId428" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:W7OEmFMy1HYC" xr:uid="{DC91BC4F-630B-A148-8FF6-7D9F2AD5016D}"/>
+    <hyperlink ref="B705" xr:uid="{D13194E0-44A8-554E-B85B-E9CE7EC4F5EF}"/>
+    <hyperlink ref="A708" r:id="rId429" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:zYLM7Y9cAGgC" xr:uid="{4D8C5D73-9BBD-1247-85F2-B4E8476D31C6}"/>
+    <hyperlink ref="B708" xr:uid="{458D8C43-2E67-DC41-80BE-95C73C272E62}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/scripts/data/publications.xlsx
+++ b/scripts/data/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilakolpashnikova/Dropbox/Mac/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E1D1F0-F2C6-964D-A3AB-C35C53BF2DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{75E4CF0A-B108-8446-B633-4E5111E961D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="44000" yWindow="1140" windowWidth="28040" windowHeight="17180" xr2:uid="{1AE54D6A-986F-F746-921F-6A2F1439D6A6}"/>
+    <workbookView xWindow="-31540" yWindow="2500" windowWidth="28040" windowHeight="17180" xr2:uid="{1AE54D6A-986F-F746-921F-6A2F1439D6A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="715" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="1018">
   <si>
     <t>Evolution of Semantic Similarity—A Survey</t>
   </si>
@@ -1766,15 +1766,6 @@
     <t>2024 46th Annual International Conference of the IEEE Engineering in …</t>
   </si>
   <si>
-    <t>Empowering bystanders: a psychological and institutional model for intervention in academic bullying</t>
-  </si>
-  <si>
-    <t>D Borthakur, L Crockett, J Mihalchan, J Swann, MJ Saikia</t>
-  </si>
-  <si>
-    <t>Frontiers in Psychology 16, 1650438</t>
-  </si>
-  <si>
     <t>Cardiorespiratory optimized guided-breathing for post-stress recovery in a group setting</t>
   </si>
   <si>
@@ -1991,6 +1982,1182 @@
   </si>
   <si>
     <t>DGM Dawit Gebeyehu Mekonen, AEY Ayenew Engida Yismaw, ...</t>
+  </si>
+  <si>
+    <t>Knowledge management in healthcare</t>
+  </si>
+  <si>
+    <t>C El Morr, J Subercaze</t>
+  </si>
+  <si>
+    <t>Handbook of research on developments in e-health and telemedicine …</t>
+  </si>
+  <si>
+    <t>Perceived impact of contextual determinants on depression, anxiety and stress: a survey with university students</t>
+  </si>
+  <si>
+    <t>N Othman, F Ahmad, C El Morr, P Ritvo</t>
+  </si>
+  <si>
+    <t>International journal of mental health systems 13 (1), 17</t>
+  </si>
+  <si>
+    <t>Effectiveness of an Eight-Week Web-Based Mindfulness Virtual Community Intervention for University Students on Symptoms of Stress, Anxiety, and Depression: A Randomized …</t>
+  </si>
+  <si>
+    <t>C El Morr, P Ritvo, F Ahmad, R Moineddin, MVC Team</t>
+  </si>
+  <si>
+    <t>JMIR mental health 7 (7)</t>
+  </si>
+  <si>
+    <t>Effectiveness of ICT-based intimate partner violence interventions: a systematic review</t>
+  </si>
+  <si>
+    <t>C El Morr, M Layal</t>
+  </si>
+  <si>
+    <t>BMC Public Health 20 (1), 1372</t>
+  </si>
+  <si>
+    <t>An eight-week, web-based mindfulness virtual community intervention for students’ mental health: Randomized controlled trial</t>
+  </si>
+  <si>
+    <t>F Ahmad, C El Morr, P Ritvo, N Othman, R Moineddin, MVC Team</t>
+  </si>
+  <si>
+    <t>JMIR mental health 7 (2), e15520</t>
+  </si>
+  <si>
+    <t>Equity within AI systems: What can health leaders expect?</t>
+  </si>
+  <si>
+    <t>E Gurevich, B El Hassan, C El Morr</t>
+  </si>
+  <si>
+    <t>Healthcare management forum 36 (2), 119-124</t>
+  </si>
+  <si>
+    <t>A mindfulness-based intervention for student depression, anxiety, and stress: randomized controlled trial</t>
+  </si>
+  <si>
+    <t>P Ritvo, F Ahmad, C El Morr, M Pirbaglou, R Moineddin, MVC Team</t>
+  </si>
+  <si>
+    <t>JMIR mental health 8 (1), e23491</t>
+  </si>
+  <si>
+    <t>Effectiveness of online mindfulness interventions on medical students’ mental health: a systematic review</t>
+  </si>
+  <si>
+    <t>V Yogeswaran, C El Morr</t>
+  </si>
+  <si>
+    <t>BMC Public Health 21 (1), 2293</t>
+  </si>
+  <si>
+    <t>Using mobile health to enhance outcomes of noncommunicable diseases care in rural settings and refugee camps: randomized controlled trial</t>
+  </si>
+  <si>
+    <t>S Saleh, A Farah, H Dimassi, N El Arnaout, J Constantin, M Osman, ...</t>
+  </si>
+  <si>
+    <t>JMIR mHealth and uHealth 6 (7), e8146</t>
+  </si>
+  <si>
+    <t>AI and disability: A systematic scoping review</t>
+  </si>
+  <si>
+    <t>C El Morr, B Kundi, F Mobeen, S Taleghani, Y El-Lahib, R Gorman</t>
+  </si>
+  <si>
+    <t>Health Informatics Journal 30 (3), 14604582241285743</t>
+  </si>
+  <si>
+    <t>AI-based epidemic and pandemic early warning systems: A systematic scoping review</t>
+  </si>
+  <si>
+    <t>C El Morr, D Ozdemir, Y Asdaah, A Saab, Y El-Lahib, ES Sokhn</t>
+  </si>
+  <si>
+    <t>Health Informatics Journal 30 (3), 14604582241275844</t>
+  </si>
+  <si>
+    <t>Mobile virtual communities research: a synthesis of current trends and a look at future perspectives</t>
+  </si>
+  <si>
+    <t>C El Morr, J Kawash</t>
+  </si>
+  <si>
+    <t>International Journal of Web Based Communities 3 (4), 386-403</t>
+  </si>
+  <si>
+    <t>Descriptive, predictive, and prescriptive analytics</t>
+  </si>
+  <si>
+    <t>C El Morr, H Ali-Hassan</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction, 31-55</t>
+  </si>
+  <si>
+    <t>Artificial intelligence and bias: a scoping review</t>
+  </si>
+  <si>
+    <t>B Kundi, C El Morr, R Gorman, E Dua</t>
+  </si>
+  <si>
+    <t>AI and Society, 199-215</t>
+  </si>
+  <si>
+    <t>M-UML: an extension to UML for the modeling of mobile agent-based software systems</t>
+  </si>
+  <si>
+    <t>K Saleh, C El-Morr</t>
+  </si>
+  <si>
+    <t>Information and Software Technology 46 (4), 219-227</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction</t>
+  </si>
+  <si>
+    <t>eHealth as a facilitator of equitable access to primary healthcare: the case of caring for non-communicable diseases in rural and refugee settings in Lebanon</t>
+  </si>
+  <si>
+    <t>S Saleh, M Alameddine, A Farah, N El Arnaout, H Dimassi, C Muntaner, ...</t>
+  </si>
+  <si>
+    <t>International journal of public health 63 (5), 577-588</t>
+  </si>
+  <si>
+    <t>Predictive machine learning models for assessing lebanese university students’ depression, anxiety, and stress during COVID-19</t>
+  </si>
+  <si>
+    <t>C El Morr, M Jammal, I Bou-Hamad, S Hijazi, D Ayna, M Romani, R Hoteit</t>
+  </si>
+  <si>
+    <t>Journal of Primary Care &amp; Community Health 15, 21501319241235588</t>
+  </si>
+  <si>
+    <t>mHealth use for non-communicable diseases care in primary health: patients’ perspective from rural settings and refugee camps</t>
+  </si>
+  <si>
+    <t>S Saleh, A Farah, N El Arnaout, H Dimassi, C El Morr, C Muntaner, ...</t>
+  </si>
+  <si>
+    <t>Journal of Public Health 40 (suppl_2), ii52-ii63</t>
+  </si>
+  <si>
+    <t>Data preprocessing</t>
+  </si>
+  <si>
+    <t>C El Morr, M Jammal, H Ali-Hassan, W El-Hallak</t>
+  </si>
+  <si>
+    <t>Machine learning for practical decision making: a multidisciplinary …</t>
+  </si>
+  <si>
+    <t>Design of a Mindfulness Virtual Community: A focus-group analysis</t>
+  </si>
+  <si>
+    <t>C El Morr, C Maule, I Ashfaq, P Ritvo, F Ahmad</t>
+  </si>
+  <si>
+    <t>Health informatics journal 26 (3), 1560-76</t>
+  </si>
+  <si>
+    <t>Fear of COVID-19 and depression, anxiety, stress, and PTSD among Syrian refugee parents in Canada</t>
+  </si>
+  <si>
+    <t>P Sharif-Esfahani, R Hoteit, C El Morr, H Tamim</t>
+  </si>
+  <si>
+    <t>Journal of migration and health 5, 100081</t>
+  </si>
+  <si>
+    <t>Machine learning for practical decision making: a multidisciplinary perspective with applications from healthcare, engineering and business analytics</t>
+  </si>
+  <si>
+    <t>C El Morr, M Jammal, H Ali-Hassan, EIH Walid</t>
+  </si>
+  <si>
+    <t>Healthcare, data analytics, and business intelligence</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction, 1-13</t>
+  </si>
+  <si>
+    <t>Assessing the Performance of a Modified LACE Index (LACE-rt) to Predict Unplanned Readmission After Discharge in a Community Teaching Hospital</t>
+  </si>
+  <si>
+    <t>C El Morr, L Ginsburg, S Nam, S Woollard</t>
+  </si>
+  <si>
+    <t>Interact J Med Res 6 (1), e2</t>
+  </si>
+  <si>
+    <t>Knowledge of peripheral arterial disease: results of an intervention to measure and improve PAD knowledge in Toronto</t>
+  </si>
+  <si>
+    <t>C El Morr, M AlHamzah, P Ng, A Purewal, M Al-Omran</t>
+  </si>
+  <si>
+    <t>Vascular 25 (5), 479-487</t>
+  </si>
+  <si>
+    <t>A Student-Centered Mental Health Virtual Community Needs and Features: A Focus Group Study</t>
+  </si>
+  <si>
+    <t>C El Morr, C Maule, I Ashfaq, P Ritvo, A Farah</t>
+  </si>
+  <si>
+    <t>The Information Technology and Communications in Health conference (ITCH …</t>
+  </si>
+  <si>
+    <t>Introduction to health informatics: a Canadian perspective</t>
+  </si>
+  <si>
+    <t>C El Morr</t>
+  </si>
+  <si>
+    <t>Canadian Scholars</t>
+  </si>
+  <si>
+    <t>A machine learning study to predict anxiety on campuses in Lebanon</t>
+  </si>
+  <si>
+    <t>M Mahalingam, M Jammal, R Hoteit, D Ayna, M Romani, S Hijazi, ...</t>
+  </si>
+  <si>
+    <t>Healthcare Transformation with Informatics and Artificial Intelligence 305, 85</t>
+  </si>
+  <si>
+    <t>A novel collaboration model for mobile virtual communities</t>
+  </si>
+  <si>
+    <t>J Kawash, C El Morr, M Itani</t>
+  </si>
+  <si>
+    <t>International Journal of Web Based Communities 3 (4), 427-447</t>
+  </si>
+  <si>
+    <t>Exploring AI governance in the Middle East and North Africa (MENA) region: gaps, efforts, and initiatives</t>
+  </si>
+  <si>
+    <t>H Trigui, F Guerfali, E Harigua-Souiai, R Qasrawi, C Atri, ES Sokhn, ...</t>
+  </si>
+  <si>
+    <t>Data &amp; Policy 6, e83</t>
+  </si>
+  <si>
+    <t>Exploring the intersection of AI and inclusive design for people with disabilities</t>
+  </si>
+  <si>
+    <t>C El Morr, D Singh, V Sawhney, S Fernandes, Y El-Lahib, R Gorman</t>
+  </si>
+  <si>
+    <t>Digital Health and Informatics Innovations for Sustainable Health Care …</t>
+  </si>
+  <si>
+    <t>Online mindfulness interventions: a systematic review</t>
+  </si>
+  <si>
+    <t>F Ahmad, JJ Wang, C El Morr</t>
+  </si>
+  <si>
+    <t>Novel applications of virtual communities in healthcare settings, 1-27</t>
+  </si>
+  <si>
+    <t>Virtual community building and the information society: Current and future directions</t>
+  </si>
+  <si>
+    <t>C El Morr, P Maret, M Dinca-Panaitescu, M Rioux, J Subercaze</t>
+  </si>
+  <si>
+    <t>Virtual Community Building and the Information Society: Current and Future …</t>
+  </si>
+  <si>
+    <t>Analyzing readmissions patterns: assessment of the LACE tool impact</t>
+  </si>
+  <si>
+    <t>C El Morr, L Ginsburg, VS Ma, S Woollard, B Hansen</t>
+  </si>
+  <si>
+    <t>Stud Health Technol Inform 223, 25-30</t>
+  </si>
+  <si>
+    <t>A cross-sectional study of university students’ mental health and lifestyle practices amidst the COVID-19 pandemic</t>
+  </si>
+  <si>
+    <t>R Hoteit, I Bou-Hamad, S Hijazi, D Ayna, M Romani, C El Morr</t>
+  </si>
+  <si>
+    <t>PloS One 19 (4), e0302265</t>
+  </si>
+  <si>
+    <t>A virtual community for disability advocacy: Development of a searchable artificial intelligence–Supported platform</t>
+  </si>
+  <si>
+    <t>C El Morr, P Maret, F Muhlenbach, D Dharmalingam, R Tadesse, ...</t>
+  </si>
+  <si>
+    <t>JMIR formative research 5 (11), e33335</t>
+  </si>
+  <si>
+    <t>Health care virtual communities: challenges and opportunities</t>
+  </si>
+  <si>
+    <t>A machine learning approach to predict the outcome of urinary calculi treatment using shock wave lithotripsy: model development and validation study</t>
+  </si>
+  <si>
+    <t>R Moghisi, C El Morr, KT Pace, M Hajiha, J Huang</t>
+  </si>
+  <si>
+    <t>Interactive Journal of Medical Research 11 (1), e33357</t>
+  </si>
+  <si>
+    <t>Coping with the COVID-19 pandemic: a cross-sectional study to investigate how mental health, lifestyle, and socio-demographic factors shape students’ quality of life</t>
+  </si>
+  <si>
+    <t>I Bou-Hamad, R Hoteit, S Hijazi, D Ayna, M Romani, C El Morr</t>
+  </si>
+  <si>
+    <t>PLoS One 18 (7), e0288358</t>
+  </si>
+  <si>
+    <t>AI and society: Tensions and opportunities</t>
+  </si>
+  <si>
+    <t>CRC Press</t>
+  </si>
+  <si>
+    <t>Support vector machine</t>
+  </si>
+  <si>
+    <t>Machine Learning for Practical Decision Making: A Multidisciplinary …</t>
+  </si>
+  <si>
+    <t>Virtual communities, machine learning and IoT: opportunities and challenges in mental health research</t>
+  </si>
+  <si>
+    <t>International Journal of Extreme Automation and Connectivity in Healthcare …</t>
+  </si>
+  <si>
+    <t>A health virtual community for patients with chronic kidney disease</t>
+  </si>
+  <si>
+    <t>C El Morr, C Cole, J Perl</t>
+  </si>
+  <si>
+    <t>Procedia Computer Science 37, 333-339</t>
+  </si>
+  <si>
+    <t>Mobile virtual communities in healthcare: managed self care on the move</t>
+  </si>
+  <si>
+    <t>Montreal: International Association of Science and Technology for …</t>
+  </si>
+  <si>
+    <t>Evaluation frameworks for health virtual communities</t>
+  </si>
+  <si>
+    <t>C El Morr, L Eftychiou</t>
+  </si>
+  <si>
+    <t>The digitization of healthcare: New challenges and opportunities, 99-118</t>
+  </si>
+  <si>
+    <t>Handbook of research on developments in e-health and telemedicine: Technological and social perspectives</t>
+  </si>
+  <si>
+    <t>CE Morr, J Subercaze</t>
+  </si>
+  <si>
+    <t>Hershey: Information Science Reference, 490-510</t>
+  </si>
+  <si>
+    <t>Decision trees</t>
+  </si>
+  <si>
+    <t>Novel Applications of Virtual Communities in Healthcare Settings</t>
+  </si>
+  <si>
+    <t>Mental health seeking behaviour of women university students: An intersectional analysis</t>
+  </si>
+  <si>
+    <t>R Lal, G Reaume, C El Morr, N Khanlou</t>
+  </si>
+  <si>
+    <t>International Health Trends and Perspectives 1 (2), 288-307</t>
+  </si>
+  <si>
+    <t>The potential of an artificial intelligence for disability advocacy: the WikiDisability project</t>
+  </si>
+  <si>
+    <t>R Gorman, P Maret, A Creighton, B Kundi, F Muhlenbach, A Buettgen, ...</t>
+  </si>
+  <si>
+    <t>Public Health and Informatics: Proceedings of MIE 2021, 1025-1026</t>
+  </si>
+  <si>
+    <t>A virtual knowledge community for human rights monitoring for people with disabilities</t>
+  </si>
+  <si>
+    <t>C El Morr, J Subercaze, P Maret, M Rioux</t>
+  </si>
+  <si>
+    <t>IADIS international conference on web based communities (WBC 2008), 78-84</t>
+  </si>
+  <si>
+    <t>Specifications of a mobile electronic voting system and a mobile agent platform</t>
+  </si>
+  <si>
+    <t>K Saleh, C El-Morr, A Mourtada, Y Morad</t>
+  </si>
+  <si>
+    <t>In Proc. of IADIS e-Society, 281-287</t>
+  </si>
+  <si>
+    <t>Predictive models for Canadian healthcare workers mental health during COVID-19</t>
+  </si>
+  <si>
+    <t>B Kumari, N Goyal, C El Morr</t>
+  </si>
+  <si>
+    <t>Journal of Primary Care &amp; Community Health 15, 21501319241241468</t>
+  </si>
+  <si>
+    <t>Logistic regression</t>
+  </si>
+  <si>
+    <t>Machine learning for practical decision making: A multidisciplinary …</t>
+  </si>
+  <si>
+    <t>XSL• FO</t>
+  </si>
+  <si>
+    <t>JMIR 8 (1), e27160</t>
+  </si>
+  <si>
+    <t>K-nearest neighbors</t>
+  </si>
+  <si>
+    <t>Mobile mental health virtual communities: challenges and opportunities</t>
+  </si>
+  <si>
+    <t>L Eftychiou, C El Morr</t>
+  </si>
+  <si>
+    <t>The Digitization of Healthcare: New Challenges and Opportunities, 257-275</t>
+  </si>
+  <si>
+    <t>Virtual community life cycle: A model to develop systems with fluid requirements</t>
+  </si>
+  <si>
+    <t>C El Morr, P Maret, M Rioux, M Dinca-Panaitescu, J Subercaze</t>
+  </si>
+  <si>
+    <t>Towards successful virtual communities</t>
+  </si>
+  <si>
+    <t>J Subercaze, C El Morr, P Maret, A Joly, M Koivisto, P Antoniadis, M Ihara</t>
+  </si>
+  <si>
+    <t>International Conference on Enterprise Information Systems, 677-688</t>
+  </si>
+  <si>
+    <t>Mental Health for Medical Students, what do we know today?</t>
+  </si>
+  <si>
+    <t>Procedia Computer Science 198, 307-310</t>
+  </si>
+  <si>
+    <t>Mobile virtual communities</t>
+  </si>
+  <si>
+    <t>Virtual technologies: concepts, methodologies, tools, and applications, 1539 …</t>
+  </si>
+  <si>
+    <t>Future directions and ethical considerations</t>
+  </si>
+  <si>
+    <t>Healthcare analytics applications</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction, 57-70</t>
+  </si>
+  <si>
+    <t>Mobile Virtual Communities in healthcare: The Chronic disease Management Case</t>
+  </si>
+  <si>
+    <t>Ubiquitous Health and Medical Informatics</t>
+  </si>
+  <si>
+    <t>Building mobile virtual communities for public transport awareness</t>
+  </si>
+  <si>
+    <t>J Kawash, C El Morr, W Charaf, H Taha</t>
+  </si>
+  <si>
+    <t>IEE Mobility Conference 2005. The Second International Conference on Mobile …</t>
+  </si>
+  <si>
+    <t>Wikibase as an infrastructure for community documents: The example of the Disability Wiki platform</t>
+  </si>
+  <si>
+    <t>KS Bisen, S Alemayehu, P Maret, A Creighton, R Gorman, B Kundi, ...</t>
+  </si>
+  <si>
+    <t>Episciences. org</t>
+  </si>
+  <si>
+    <t>A mindfulness-based intervention for student depression, anxiety, and stress: Randomized controlled trial. JMIR Mental Health, 8 (1)</t>
+  </si>
+  <si>
+    <t>P Ritvo, F Ahmad, CE Morr, M Pirbaglou, R Moineddin</t>
+  </si>
+  <si>
+    <t>Randomized controlled trial of mindfulness-based intervention for student depression, anxiety and stress: observations on a disrupted campus</t>
+  </si>
+  <si>
+    <t>P Ritvo, F Ahmad, C El Morr, M Pirbaglou, R Moineddin</t>
+  </si>
+  <si>
+    <t>JMIR mental health 8 (1)</t>
+  </si>
+  <si>
+    <t>It integration and patient safety: The case of a software tool</t>
+  </si>
+  <si>
+    <t>C El Morr, L Ginsburg, NV Seungree, S Woollard, B Hensen</t>
+  </si>
+  <si>
+    <t>Procedia computer science 98, 534-539</t>
+  </si>
+  <si>
+    <t>Practical approach for evaluating machine learning anomaly detection algorithms for epidemic early warning systems</t>
+  </si>
+  <si>
+    <t>A Saab, AH Dabboussi, CABI Khalil, J Rahme, ES Sokhn, CEL Morr</t>
+  </si>
+  <si>
+    <t>Examining the impact of web-based mindfulness on undergraduate student’s quality of life: a randomized controlled trial</t>
+  </si>
+  <si>
+    <t>F Ahmad, C El Morr, P Ritvo, ...</t>
+  </si>
+  <si>
+    <t>BMC Digital Health 1 (1), 22</t>
+  </si>
+  <si>
+    <t>Evaluation of search methods on community documents</t>
+  </si>
+  <si>
+    <t>K Singh Bisen, SA Alemayehu, P Maret, A Creighton, R Gorman, B Kundi, ...</t>
+  </si>
+  <si>
+    <t>Research Conference on Metadata and Semantics Research, 39-49</t>
+  </si>
+  <si>
+    <t>Need of equity in virtual mental health in Canada in the times of COVID-19</t>
+  </si>
+  <si>
+    <t>B Kundi, C El Morr</t>
+  </si>
+  <si>
+    <t>Advances in Informatics, Management and Technology in Healthcare, 358-359</t>
+  </si>
+  <si>
+    <t>Accessibility monitoring for people with disabilities: a collaborative virtual community</t>
+  </si>
+  <si>
+    <t>I Saraswat, A Brahim, C El Morr</t>
+  </si>
+  <si>
+    <t>Analytics building blocks</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction, 15-30</t>
+  </si>
+  <si>
+    <t>A health VC for chronic disease management in a global context</t>
+  </si>
+  <si>
+    <t>C El Morr, S Saleh, W Ammar, N Natafgi, K Kazandjian</t>
+  </si>
+  <si>
+    <t>communities 5, 6</t>
+  </si>
+  <si>
+    <t>Research Perspectives on the Role of Informatics in Health Policy and Management</t>
+  </si>
+  <si>
+    <t>Enabling virtual knowledge networks for human rights monitoring for people with disabilities</t>
+  </si>
+  <si>
+    <t>C El Morr, M Dinca-Panaitescu, M Rioux, J Subercaze, P Maret, ...</t>
+  </si>
+  <si>
+    <t>International Journal of Virtual Communities and Social Networking (IJVCSN …</t>
+  </si>
+  <si>
+    <t>Virtual Knowledge Network for Human Rights Monitoring</t>
+  </si>
+  <si>
+    <t>C El Morr, J Subercaze, M Rioux, M Dinca-Panaitescu</t>
+  </si>
+  <si>
+    <t>Workshop on Web Intelligence and Virtual Enterprises (WIVE’09), 10th IFIP …</t>
+  </si>
+  <si>
+    <t>A mobile‐agent platform and a game application specifications using M‐UML</t>
+  </si>
+  <si>
+    <t>K Saleh, C El Morr, A Mourtada, Y Morad</t>
+  </si>
+  <si>
+    <t>The Electronic Library 22 (1), 32-42</t>
+  </si>
+  <si>
+    <t>Specifications for a Mobile-Agent Platform and an Internet-Based Mobile Electronic Voting Application.</t>
+  </si>
+  <si>
+    <t>International Conference on Internet Computing, 730-736</t>
+  </si>
+  <si>
+    <t>Mindful Nonreactivity, Anxiety, Depression, and Perceived Stress as Mediators of the Mindfulness Virtual Community Intervention—Pathways to Enhance Mental Health in University …</t>
+  </si>
+  <si>
+    <t>M Pirbaglou, C El Morr, F Ahmad, P Ritvo</t>
+  </si>
+  <si>
+    <t>JMIR mental health 12 (1), e65853</t>
+  </si>
+  <si>
+    <t>Predicting the Effectiveness of a Mindfulness Virtual Community Intervention for University Students: A Machine Learning Model.</t>
+  </si>
+  <si>
+    <t>C El Morr, F Tavangar, F Ahmad, P Ritvo</t>
+  </si>
+  <si>
+    <t>Interactive Journal of Medical Research</t>
+  </si>
+  <si>
+    <t>Towards trustworthy artificial intelligence for equitable global health</t>
+  </si>
+  <si>
+    <t>H Qin, J Kong, W Ding, R Ahluwalia, CE Morr, Z Engin, JO Effoduh, ...</t>
+  </si>
+  <si>
+    <t>arXiv preprint arXiv:2309.05088</t>
+  </si>
+  <si>
+    <t>A Machine Learning Approach to Predict Poor Mental Health of Intimate Partner Violence Survivors</t>
+  </si>
+  <si>
+    <t>A Sisodia, M Jammal, C El Morr</t>
+  </si>
+  <si>
+    <t>2023 Fifth International Conference on Advances in Computational Tools for …</t>
+  </si>
+  <si>
+    <t>Overview of machine learning algorithms</t>
+  </si>
+  <si>
+    <t>Data Visualization</t>
+  </si>
+  <si>
+    <t>Data visualization</t>
+  </si>
+  <si>
+    <t>Analytics in healthcare: a practical introduction, 71-90</t>
+  </si>
+  <si>
+    <t>Mobile virtual communities in healthcare: self-managed care on the move</t>
+  </si>
+  <si>
+    <t>The Third IASTED International Conference on Telehealth, 40-44</t>
+  </si>
+  <si>
+    <t>Enhancing epidemic early warning systems with social media data</t>
+  </si>
+  <si>
+    <t>N Kashmar, D Ozdemir, I Yousuf, AH Dabboussi, A Saab, E Salem-Sokhn, ...</t>
+  </si>
+  <si>
+    <t>2025 International Conference on Control, Automation, and Instrumentation …</t>
+  </si>
+  <si>
+    <t>The need for a feminist approach to artificial intelligence</t>
+  </si>
+  <si>
+    <t>Proceedings of the AAAI Symposium Series 4 (1), 332-333</t>
+  </si>
+  <si>
+    <t>Advantages and Challenges of Using AI for People with Disabilities</t>
+  </si>
+  <si>
+    <t>S Taleghani, B Kundi, F Mobeen, Y El-Lahib, R Gorman, C El Morr</t>
+  </si>
+  <si>
+    <t>SciTePress</t>
+  </si>
+  <si>
+    <t>Introduction to Machine Learning</t>
+  </si>
+  <si>
+    <t>Methodology for creating a community corpus using a Wikibase knowledge graph</t>
+  </si>
+  <si>
+    <t>SA Alemayehu, KS Bisen, P Maret, A Creighton, R Gorman, B Kundi, ...</t>
+  </si>
+  <si>
+    <t>Iberoamerican Knowledge Graphs and Semantic Web Conference, 285-297</t>
+  </si>
+  <si>
+    <t>Disability advocacy using a smart virtual community</t>
+  </si>
+  <si>
+    <t>B Kundi, D Dharmalingam, R Tadesse, A Creighton, R Gorman, P Maret, ...</t>
+  </si>
+  <si>
+    <t>Proceedings of the 15th International Joint Conference on Biomedical …</t>
+  </si>
+  <si>
+    <t>Insight into health care outcomes for persons living with heart failure using health data analytics</t>
+  </si>
+  <si>
+    <t>C El Morr, L Ginsburg, S Nam, W Cheung, H Brien, A Maloul, N Cohen, ...</t>
+  </si>
+  <si>
+    <t>Improving Usability, Safety and Patient Outcomes with Health Information …</t>
+  </si>
+  <si>
+    <t>A Health Virtual Community Perspective for Peripheral Arterial Disease-The Need of an E-solution for PAD</t>
+  </si>
+  <si>
+    <t>C El Morr, P Ng, M Al Omran, CE Cole, M Al Hamza, A Purewal</t>
+  </si>
+  <si>
+    <t>Proceedings of the 9th International Joint Conference on Biomedical …</t>
+  </si>
+  <si>
+    <t>A Model for Global Health Virtual Communities</t>
+  </si>
+  <si>
+    <t>GLOBAL HEALTH 2013 Editors, 39</t>
+  </si>
+  <si>
+    <t>Special Issue on Web Intelligence and Virtual Communities. Editorial.</t>
+  </si>
+  <si>
+    <t>P Maret, L Vercouter, C El Morr</t>
+  </si>
+  <si>
+    <t>International Journal of Networking and Virtual Organisations (IJNVO) 9 (3 …</t>
+  </si>
+  <si>
+    <t>Scenarios for Mobile Virtual Communities of Students</t>
+  </si>
+  <si>
+    <t>C El Morr, K Jalal</t>
+  </si>
+  <si>
+    <t>International Resource Management Association Conference (IRMA2007)</t>
+  </si>
+  <si>
+    <t>Development of a PC based PACS open to ISDN and Internet for research purposes</t>
+  </si>
+  <si>
+    <t>C El Morr, JF Lerallut</t>
+  </si>
+  <si>
+    <t>Proceedings of 17th International Conference of the Engineering in Medicine …</t>
+  </si>
+  <si>
+    <t>Disability-centered policy opportunities and challenges for accessible and inclusive AI: A scoping review</t>
+  </si>
+  <si>
+    <t>C El Morr, S Fernandes, D Singh, V Sawhney, R da Silveira Gorman, ...</t>
+  </si>
+  <si>
+    <t>AI for a Just World, 108-122</t>
+  </si>
+  <si>
+    <t>AI-based epidemic early warning using social media and search engine signals: A scoping review</t>
+  </si>
+  <si>
+    <t>A Bayat, A Pavakopethan, N Kashmar, I Yousuf, A Saab, E Salem Sokhn, ...</t>
+  </si>
+  <si>
+    <t>Health Informatics Journal 32 (3), 14604582261479106</t>
+  </si>
+  <si>
+    <t>AI-Driven Assistive Technology: The Disability Justice Imperative</t>
+  </si>
+  <si>
+    <t>B Kundi, S Taleghani, R da Silveira Gorman, Y El-Lahib, C El Morr</t>
+  </si>
+  <si>
+    <t>Handbook on Smart Health 330, 973-985</t>
+  </si>
+  <si>
+    <t>Identifying the panorama of potential pandemic pathogens and their key characteristics: a systematic scoping review</t>
+  </si>
+  <si>
+    <t>Y Khachab, A Saab, C El Morr, Y El-Lahib, ES Sokhn</t>
+  </si>
+  <si>
+    <t>Critical Reviews in Microbiology 51 (2), 348-368</t>
+  </si>
+  <si>
+    <t>K-Means</t>
+  </si>
+  <si>
+    <t>Linear Regression</t>
+  </si>
+  <si>
+    <t>Naïve Bayes</t>
+  </si>
+  <si>
+    <t>Virtual Communities, Machine Learning and IoT: Opportunities and Challenges in Mental Health Research</t>
+  </si>
+  <si>
+    <t>Research Anthology on Mental Health Stigma, Education, and Treatment, 381-389</t>
+  </si>
+  <si>
+    <t>Human Rights monitoring in Virtual Community</t>
+  </si>
+  <si>
+    <t>Studies in health technology and informatics 180, 798-802</t>
+  </si>
+  <si>
+    <t>Integrating wireless network users and mobile software agents: an application</t>
+  </si>
+  <si>
+    <t>K Saleh, C El-Morr, M Jaragh</t>
+  </si>
+  <si>
+    <t>The IEEE Region 8 EUROCON 2003. Computer as a Tool. 2, 87-90</t>
+  </si>
+  <si>
+    <t>Algorithmic Bias and Feminist Futures: Unmasking Power Dynamics in Artificial Intelligence</t>
+  </si>
+  <si>
+    <t>Feminist Digital Methods, 46-63</t>
+  </si>
+  <si>
+    <t>AI for a Just World: Power, Liberation, and the People Left Behind</t>
+  </si>
+  <si>
+    <t>C El Morr, R da Silveira Gorman, E Dolatabadi, L Seyyed-Kalantari</t>
+  </si>
+  <si>
+    <t>Shaping AI Otherwise: From Critique to Collective Futures</t>
+  </si>
+  <si>
+    <t>Shaping AI: Ethics, Society, and the Future of Technology, 301-305</t>
+  </si>
+  <si>
+    <t>AI Through Critical Lenses: Decolonizing Technology and Advancing Feminist Futures</t>
+  </si>
+  <si>
+    <t>Shaping AI: Ethics, Society, and the Future of Technology, 277-300</t>
+  </si>
+  <si>
+    <t>If You’re not on the Table, You’re on the Menu: Generative AI, Cultural Appropriation and the Ethics of Data Use</t>
+  </si>
+  <si>
+    <t>P Pathak, C El Morr</t>
+  </si>
+  <si>
+    <t>Shaping AI: Ethics, Society, and the Future of Technology, 193-208</t>
+  </si>
+  <si>
+    <t>Data, Dignity, and Dehumanization: A Critical Examination of AI’s Impact on Disability and Human Experience</t>
+  </si>
+  <si>
+    <t>V Sawhney, C El Morr</t>
+  </si>
+  <si>
+    <t>Shaping AI: Ethics, Society, and the Future of Technology, 73-88</t>
+  </si>
+  <si>
+    <t>Advancing Psychiatric Safety With the Predictive Risk Identification for Mental Health Events Tool: Retrospective Cohort Study</t>
+  </si>
+  <si>
+    <t>E Dolatabadi, VT Velasquez, AH Dabboussi, D Wen, J Crawford, ...</t>
+  </si>
+  <si>
+    <t>JMIR Mental Health 13 (1), e84318</t>
+  </si>
+  <si>
+    <t>Truth and Post-truth in the Age of AI: Heidegger Among the Chat Bots</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence and Technocolonialism: Western Ethics, Morality, and the Absolving of Imperial Violence</t>
+  </si>
+  <si>
+    <t>Examining AI Market Failure and the Development of Use Cases: An Indian Perspective</t>
+  </si>
+  <si>
+    <t>Algorithmic Exploitation: A Historical Materialist Critique of AI in the Platform Economy and Health Systems Affecting Racialized Immigrants in Canada</t>
+  </si>
+  <si>
+    <t>‘Humans in the Loop’: Insights from Algorithmic Management on Digital Labour Platforms in India</t>
+  </si>
+  <si>
+    <t>Contours of Social Agency in Technology Development: Ethics Committees in Governance of AI</t>
+  </si>
+  <si>
+    <t>Promise and Perils of AI: Social and Economic</t>
+  </si>
+  <si>
+    <t>AI Through a Philosophical Lens</t>
+  </si>
+  <si>
+    <t>Measuring and Mitigating Bias and Discrimination in AI</t>
+  </si>
+  <si>
+    <t>Heidegger and Artificial Intelligence: A Philosophical Perspective</t>
+  </si>
+  <si>
+    <t>Moral Consciousness in Artificial Intelligence: Reflections on Its Possibility and Implications</t>
+  </si>
+  <si>
+    <t>Liminal Responsibility: Toward an Ethic of Human-AI Relation</t>
+  </si>
+  <si>
+    <t>Shaping AI: Ethics, Society, and the Future of Technology</t>
+  </si>
+  <si>
+    <t>Springer Nature</t>
+  </si>
+  <si>
+    <t>Why Write: Producing the Author in the Time of AI</t>
+  </si>
+  <si>
+    <t>Advances in Machine Learning for Stochastic Transport: A Perspective of Cellular Biology and Urban Transit Systems</t>
+  </si>
+  <si>
+    <t>The Gender Data Gap in Medical AI: Causes, Consequences, and Building Inclusive Solutions</t>
+  </si>
+  <si>
+    <t>India’s AI Policies and Postphenomenological Futures</t>
+  </si>
+  <si>
+    <t>Conclusion: Toward Collective Futures of AI and Disability Justice</t>
+  </si>
+  <si>
+    <t>C El Morr, Y El-Lahib, R da Silveira Gorman</t>
+  </si>
+  <si>
+    <t>Beyond Tech Fixes: Towards an AI Future Where Disability Justice Thrives …</t>
+  </si>
+  <si>
+    <t>AI and Disability Justice: Why Beyond Tech Fixes?</t>
+  </si>
+  <si>
+    <t>Y El-Lahib, R da Silveira Gorman, C El Morr</t>
+  </si>
+  <si>
+    <t>Beyond Tech Fixes: Towards an AI Future Where Disability Justice Thrives, 3-9</t>
+  </si>
+  <si>
+    <t>Beyond tech fixes: towards an aI future where disability justice thrives</t>
+  </si>
+  <si>
+    <t>C El Morr, Y El-Lahib, R da Silveria Gorma</t>
+  </si>
+  <si>
+    <t>The Development and Piloting of a Machine Learning Prediction Alerting System for Adverse Events in Psychiatry</t>
+  </si>
+  <si>
+    <t>VT Velasquez, M Smith, A Waddell, E Dolatabadi, C El Morr, A Mishra</t>
+  </si>
+  <si>
+    <t>Biological Psychiatry 97 (9), S77</t>
+  </si>
+  <si>
+    <t>The Healthy Immigrant Effect in Canada: Understandings of Debility: A Literature Review</t>
+  </si>
+  <si>
+    <t>W Abdel Kader, RDS Gorman, C El Morr</t>
+  </si>
+  <si>
+    <t>Voting and Bagging</t>
+  </si>
+  <si>
+    <t>Boosting and Stacking</t>
+  </si>
+  <si>
+    <t>Authentication of a Gravure Printer from Color Values using an Artificial Neural Network</t>
+  </si>
+  <si>
+    <t>IJRET: International Journal of Research in Engineering and Technology 11 (2 …</t>
+  </si>
+  <si>
+    <t>R Moineddin, P Ritvo, C El Morr, M Team</t>
+  </si>
+  <si>
+    <t>Introduction to Health Informatics: a canadian perspective</t>
+  </si>
+  <si>
+    <t>The Checklist of Unit Behaviours (CUB): Validation within a Canadian outpatient day hospital programme</t>
+  </si>
+  <si>
+    <t>M Taube‐Schiff, C El Morr, A Counsell, A Mehak, J Gollan</t>
+  </si>
+  <si>
+    <t>Journal of Psychiatric and Mental Health Nursing 25 (4), 217-227</t>
+  </si>
+  <si>
+    <t>Communicating Health information: what channel? A survey of User Preferences Type: Concurrent Sessions Topic: 01 Technology/Technology Innovation</t>
+  </si>
+  <si>
+    <t>C El Morr, P Ng, C Cole, A Purewal</t>
+  </si>
+  <si>
+    <t>eHealth 2016 Conference, Toronto June 5-8, 2016</t>
+  </si>
+  <si>
+    <t>A Health Virtual Community Model: A Bottom Up Approach</t>
+  </si>
+  <si>
+    <t>eTELEMED 2014, The Sixth International Conference on eHealth, Telemedicine …</t>
+  </si>
+  <si>
+    <t>El Morr C., Dinca-Panaitescu M., Rioux M., Subercaze J., Maret P., Bogdan N. Enabling virtual knowledge Networks for human rights monitoring for people with disabilities</t>
+  </si>
+  <si>
+    <t>C El Morr, DP Mihaela, M Rioux, J Subercaze, P Maret, N Bogdan</t>
+  </si>
+  <si>
+    <t>International Workshop on Web Intelligence and Communities (WI&amp;C 2011). Editorial.</t>
+  </si>
+  <si>
+    <t>International Conference on Web Intelligence and Intelligent Agent …</t>
+  </si>
+  <si>
+    <t>Web Intelligence and Communities (Workshop introduction)</t>
+  </si>
+  <si>
+    <t>The 2011 IEEE/WIC/ACM International Joint Conference on Web Intelligence and …</t>
+  </si>
+  <si>
+    <t>Pierre Maret</t>
+  </si>
+  <si>
+    <t>L Vercouter, C El Morr</t>
+  </si>
+  <si>
+    <t>Int. J. Networking and Virtual Organisations 9 (3), 211</t>
+  </si>
+  <si>
+    <t>International Workshop on Web Intelligence and Communities (WI&amp;C 2011)</t>
+  </si>
+  <si>
+    <t>P Maret, L Vercouter, C El Morr, R Akerkar, J Altmann, F Bugeaud, ...</t>
+  </si>
+  <si>
+    <t>International Conferences on WEB INTELLIGENCE and INTELLIGENT AGENT …</t>
+  </si>
+  <si>
+    <t>Special Issue on Web Intelligence and Virtual Communities.</t>
+  </si>
+  <si>
+    <t>Web Intelligence and Virtual Communities.</t>
+  </si>
+  <si>
+    <t>P MARET, L VERCOUTER, C EL MORR</t>
+  </si>
+  <si>
+    <t>Knowledge Management in Health care</t>
+  </si>
+  <si>
+    <t>Handbook of Research on Developments in e-Health and Telemedicine …</t>
+  </si>
+  <si>
+    <t>Health Care Virtual Communities: Challenges and Opportunities</t>
+  </si>
+  <si>
+    <t>International Journal of Web Based Communities. Special Issue on DYNAMIC VIRTUAL COMMUNITIES IN THE INFORMATION SOCIETY</t>
+  </si>
+  <si>
+    <t>C El Morr, P Maret, P Kommers</t>
+  </si>
+  <si>
+    <t>Inderscience Enterprises Ltd.</t>
+  </si>
+  <si>
+    <t>Special issue on dynamic virtual communities in the information society</t>
+  </si>
+  <si>
+    <t>C El Morr, P Maret, PAM Kommers</t>
+  </si>
+  <si>
+    <t>International journal of web based communities 5 (2), 139-143</t>
+  </si>
+  <si>
+    <t>Electronic Discharge Summaries: Physician Views and Perceptions</t>
+  </si>
+  <si>
+    <t>T B., E J., W Lily, A Khan, N Z., C El Morr, Dinca-Panaitescu S.</t>
+  </si>
+  <si>
+    <t>Virtual Student Research Symposium in e-Health, e-health 2008 conference</t>
+  </si>
+  <si>
+    <t>Mobile Virtual Communities of Commuters</t>
+  </si>
+  <si>
+    <t>J Kawash, C El Morr, H Taha, W Charaf</t>
+  </si>
+  <si>
+    <t>Encyclopedia of Networked and Virtual Organization</t>
+  </si>
+  <si>
+    <t>Specifications for a Mobile-Agent Platform &amp; an Internet-Based Mobile Electronic Voting Application</t>
+  </si>
+  <si>
+    <t>S K., EM Christo, M A., M Y.</t>
+  </si>
+  <si>
+    <t>The 4th International Conference on Internet Computing (IC2003)</t>
+  </si>
+  <si>
+    <t>The Mobile Unified Modeling Language for An Agent-based Bartering Software Application</t>
+  </si>
+  <si>
+    <t>EM Christo, S K.</t>
+  </si>
+  <si>
+    <t>IEEE/ACS International Conference on Computer Systems and Applications …</t>
+  </si>
+  <si>
+    <t>Specification and architecture of a mobile agent-based bartering business model</t>
+  </si>
+  <si>
+    <t>K Saleh, E Morr C.</t>
+  </si>
+  <si>
+    <t>International Conference on Electronic Commerce (ICEC 2001), Austria</t>
+  </si>
+  <si>
+    <t>Specification and Architecture of a Mobile Agent-based Bartering Business Model</t>
+  </si>
+  <si>
+    <t>S K., EM Christo</t>
+  </si>
+  <si>
+    <t>3rd International Conference on Electronic Commerce (ICEC 2001)</t>
+  </si>
+  <si>
+    <t>Multimedia Medical Archive Consultation using ISDN and Internet</t>
+  </si>
+  <si>
+    <t>MEDICAL AND BIOLOGICAL ENGINEERING AND COMPUTING 34, 267-268</t>
   </si>
 </sst>
 </file>
@@ -2071,8 +3238,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2408,7 +3575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63F586DF-5126-0C41-93C9-DC8AF5D22C1E}">
-  <dimension ref="A1:C709"/>
+  <dimension ref="A1:C1222"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="86.83203125" customWidth="1"/>
@@ -2518,7 +3685,7 @@
       <c r="A13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="4">
@@ -2529,14 +3696,14 @@
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="5"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="4"/>
     </row>
     <row r="15" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="5"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="4"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
@@ -2768,7 +3935,7 @@
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="6" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="4">
@@ -2779,14 +3946,14 @@
       <c r="A44" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B44" s="5"/>
+      <c r="B44" s="6"/>
       <c r="C44" s="4"/>
     </row>
     <row r="45" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B45" s="5"/>
+      <c r="B45" s="6"/>
       <c r="C45" s="4"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.2">
@@ -3168,7 +4335,7 @@
       <c r="A91" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B91" s="5" t="s">
+      <c r="B91" s="6" t="s">
         <v>93</v>
       </c>
       <c r="C91" s="4">
@@ -3179,14 +4346,14 @@
       <c r="A92" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B92" s="5"/>
+      <c r="B92" s="6"/>
       <c r="C92" s="4"/>
     </row>
     <row r="93" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B93" s="5"/>
+      <c r="B93" s="6"/>
       <c r="C93" s="4"/>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.2">
@@ -4693,7 +5860,7 @@
       <c r="A274" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B274" s="5" t="s">
+      <c r="B274" s="6" t="s">
         <v>273</v>
       </c>
       <c r="C274" s="4">
@@ -4704,14 +5871,14 @@
       <c r="A275" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B275" s="5"/>
+      <c r="B275" s="6"/>
       <c r="C275" s="4"/>
     </row>
     <row r="276" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A276" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B276" s="5"/>
+      <c r="B276" s="6"/>
       <c r="C276" s="4"/>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.2">
@@ -4968,7 +6135,7 @@
       <c r="A307" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B307" s="5" t="s">
+      <c r="B307" s="6" t="s">
         <v>305</v>
       </c>
       <c r="C307" s="4">
@@ -4979,14 +6146,14 @@
       <c r="A308" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B308" s="5"/>
+      <c r="B308" s="6"/>
       <c r="C308" s="4"/>
     </row>
     <row r="309" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A309" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B309" s="5"/>
+      <c r="B309" s="6"/>
       <c r="C309" s="4"/>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.2">
@@ -7331,10 +8498,10 @@
         <v>557</v>
       </c>
       <c r="B597" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C597" s="4">
-        <v>2025</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="598" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -7344,45 +8511,45 @@
       <c r="B598" s="3"/>
       <c r="C598" s="4"/>
     </row>
-    <row r="599" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A599" s="2" t="s">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A599" s="1" t="s">
         <v>559</v>
       </c>
-      <c r="B599" s="3"/>
-      <c r="C599" s="4"/>
-    </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A600" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="B600" s="3">
+      <c r="B599" s="3">
         <v>2</v>
       </c>
-      <c r="C600" s="4">
-        <v>2020</v>
-      </c>
+      <c r="C599" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A600" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B600" s="3"/>
+      <c r="C600" s="4"/>
     </row>
     <row r="601" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A601" s="2" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B601" s="3"/>
       <c r="C601" s="4"/>
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A602" s="1" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B602" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C602" s="4">
-        <v>2018</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="603" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A603" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B603" s="3"/>
       <c r="C603" s="4"/>
@@ -7398,11 +8565,9 @@
       <c r="A605" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="B605" s="3">
-        <v>1</v>
-      </c>
+      <c r="B605" s="3"/>
       <c r="C605" s="4">
-        <v>2025</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="606" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -7412,32 +8577,32 @@
       <c r="B606" s="3"/>
       <c r="C606" s="4"/>
     </row>
-    <row r="607" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A607" s="2" t="s">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A607" s="1" t="s">
         <v>566</v>
       </c>
       <c r="B607" s="3"/>
-      <c r="C607" s="4"/>
-    </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A608" s="1" t="s">
-        <v>567</v>
+      <c r="C607" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A608" s="2" t="s">
+        <v>565</v>
       </c>
       <c r="B608" s="3"/>
-      <c r="C608" s="4">
-        <v>2026</v>
-      </c>
+      <c r="C608" s="4"/>
     </row>
     <row r="609" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A609" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B609" s="3"/>
       <c r="C609" s="4"/>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A610" s="1" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B610" s="3"/>
       <c r="C610" s="4">
@@ -7446,30 +8611,30 @@
     </row>
     <row r="611" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A611" s="2" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="B611" s="3"/>
       <c r="C611" s="4"/>
     </row>
     <row r="612" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A612" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B612" s="3"/>
       <c r="C612" s="4"/>
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A613" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B613" s="3"/>
       <c r="C613" s="4">
-        <v>2025</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="614" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A614" s="2" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="B614" s="3"/>
       <c r="C614" s="4"/>
@@ -7485,359 +8650,361 @@
       <c r="A616" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="B616" s="3"/>
-      <c r="C616" s="4">
-        <v>2015</v>
+      <c r="B616" s="3">
+        <v>23</v>
+      </c>
+      <c r="C616" s="5">
+        <v>2023</v>
       </c>
     </row>
     <row r="617" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A617" s="2" t="s">
-        <v>574</v>
+        <v>116</v>
       </c>
       <c r="B617" s="3"/>
-      <c r="C617" s="4"/>
+      <c r="C617" s="5"/>
     </row>
     <row r="618" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A618" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B618" s="3"/>
-      <c r="C618" s="4"/>
+      <c r="C618" s="5"/>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A619" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B619" s="3">
-        <v>23</v>
-      </c>
-      <c r="C619" s="6">
-        <v>2023</v>
+        <v>18</v>
+      </c>
+      <c r="C619" s="5">
+        <v>2022</v>
       </c>
     </row>
     <row r="620" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A620" s="2" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="B620" s="3"/>
-      <c r="C620" s="6"/>
+      <c r="C620" s="5"/>
     </row>
     <row r="621" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A621" s="2" t="s">
-        <v>577</v>
+        <v>144</v>
       </c>
       <c r="B621" s="3"/>
-      <c r="C621" s="6"/>
+      <c r="C621" s="5"/>
     </row>
     <row r="622" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A622" s="1" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B622" s="3">
         <v>18</v>
       </c>
-      <c r="C622" s="6">
-        <v>2022</v>
+      <c r="C622" s="5">
+        <v>2020</v>
       </c>
     </row>
     <row r="623" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A623" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B623" s="3"/>
-      <c r="C623" s="6"/>
+      <c r="C623" s="5"/>
     </row>
     <row r="624" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A624" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B624" s="3"/>
-      <c r="C624" s="6"/>
+      <c r="C624" s="5"/>
     </row>
     <row r="625" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A625" s="1" t="s">
-        <v>579</v>
-      </c>
-      <c r="B625" s="3">
-        <v>18</v>
-      </c>
-      <c r="C625" s="6">
-        <v>2020</v>
+        <v>577</v>
+      </c>
+      <c r="B625" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="C625" s="5">
+        <v>2019</v>
       </c>
     </row>
     <row r="626" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A626" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="B626" s="3"/>
-      <c r="C626" s="6"/>
+        <v>578</v>
+      </c>
+      <c r="B626" s="6"/>
+      <c r="C626" s="5"/>
     </row>
     <row r="627" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A627" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B627" s="3"/>
-      <c r="C627" s="6"/>
+        <v>579</v>
+      </c>
+      <c r="B627" s="6"/>
+      <c r="C627" s="5"/>
     </row>
     <row r="628" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A628" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="B628" s="5" t="s">
-        <v>583</v>
-      </c>
-      <c r="C628" s="6">
-        <v>2019</v>
+        <v>581</v>
+      </c>
+      <c r="B628" s="3">
+        <v>14</v>
+      </c>
+      <c r="C628" s="5">
+        <v>2020</v>
       </c>
     </row>
     <row r="629" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A629" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B629" s="5"/>
-      <c r="C629" s="6"/>
+        <v>185</v>
+      </c>
+      <c r="B629" s="3"/>
+      <c r="C629" s="5"/>
     </row>
     <row r="630" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A630" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="B630" s="5"/>
-      <c r="C630" s="6"/>
+      <c r="B630" s="3"/>
+      <c r="C630" s="5"/>
     </row>
     <row r="631" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A631" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B631" s="3">
-        <v>14</v>
-      </c>
-      <c r="C631" s="6">
+        <v>12</v>
+      </c>
+      <c r="C631" s="5">
         <v>2020</v>
       </c>
     </row>
     <row r="632" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A632" s="2" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="B632" s="3"/>
-      <c r="C632" s="6"/>
+      <c r="C632" s="5"/>
     </row>
     <row r="633" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A633" s="2" t="s">
-        <v>585</v>
+        <v>150</v>
       </c>
       <c r="B633" s="3"/>
-      <c r="C633" s="6"/>
+      <c r="C633" s="5"/>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A634" s="1" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B634" s="3">
-        <v>12</v>
-      </c>
-      <c r="C634" s="6">
+        <v>9</v>
+      </c>
+      <c r="C634" s="5">
         <v>2020</v>
       </c>
     </row>
     <row r="635" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A635" s="2" t="s">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="B635" s="3"/>
-      <c r="C635" s="6"/>
+      <c r="C635" s="5"/>
     </row>
     <row r="636" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A636" s="2" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="B636" s="3"/>
-      <c r="C636" s="6"/>
+      <c r="C636" s="5"/>
     </row>
     <row r="637" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A637" s="1" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B637" s="3">
-        <v>9</v>
-      </c>
-      <c r="C637" s="6">
-        <v>2020</v>
+        <v>7</v>
+      </c>
+      <c r="C637" s="5">
+        <v>2022</v>
       </c>
     </row>
     <row r="638" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A638" s="2" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="B638" s="3"/>
-      <c r="C638" s="6"/>
+      <c r="C638" s="5"/>
     </row>
     <row r="639" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A639" s="2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="B639" s="3"/>
-      <c r="C639" s="6"/>
+      <c r="C639" s="5"/>
     </row>
     <row r="640" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A640" s="1" t="s">
-        <v>588</v>
+        <v>259</v>
       </c>
       <c r="B640" s="3">
-        <v>7</v>
-      </c>
-      <c r="C640" s="6">
-        <v>2022</v>
+        <v>6</v>
+      </c>
+      <c r="C640" s="5">
+        <v>2024</v>
       </c>
     </row>
     <row r="641" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A641" s="2" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B641" s="3"/>
-      <c r="C641" s="6"/>
+      <c r="C641" s="5"/>
     </row>
     <row r="642" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A642" s="2" t="s">
-        <v>249</v>
+        <v>586</v>
       </c>
       <c r="B642" s="3"/>
-      <c r="C642" s="6"/>
+      <c r="C642" s="5"/>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A643" s="1" t="s">
-        <v>259</v>
+        <v>587</v>
       </c>
       <c r="B643" s="3">
-        <v>6</v>
-      </c>
-      <c r="C643" s="6">
-        <v>2024</v>
+        <v>5</v>
+      </c>
+      <c r="C643" s="5">
+        <v>2021</v>
       </c>
     </row>
     <row r="644" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A644" s="2" t="s">
-        <v>260</v>
+        <v>289</v>
       </c>
       <c r="B644" s="3"/>
-      <c r="C644" s="6"/>
+      <c r="C644" s="5"/>
     </row>
     <row r="645" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A645" s="2" t="s">
-        <v>589</v>
+        <v>180</v>
       </c>
       <c r="B645" s="3"/>
-      <c r="C645" s="6"/>
+      <c r="C645" s="5"/>
     </row>
     <row r="646" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A646" s="1" t="s">
-        <v>590</v>
+        <v>317</v>
       </c>
       <c r="B646" s="3">
-        <v>5</v>
-      </c>
-      <c r="C646" s="6">
-        <v>2021</v>
+        <v>3</v>
+      </c>
+      <c r="C646" s="5">
+        <v>2023</v>
       </c>
     </row>
     <row r="647" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A647" s="2" t="s">
-        <v>289</v>
+        <v>318</v>
       </c>
       <c r="B647" s="3"/>
-      <c r="C647" s="6"/>
+      <c r="C647" s="5"/>
     </row>
     <row r="648" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A648" s="2" t="s">
-        <v>180</v>
+        <v>588</v>
       </c>
       <c r="B648" s="3"/>
-      <c r="C648" s="6"/>
+      <c r="C648" s="5"/>
     </row>
     <row r="649" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A649" s="1" t="s">
-        <v>317</v>
+        <v>589</v>
       </c>
       <c r="B649" s="3">
-        <v>3</v>
-      </c>
-      <c r="C649" s="6">
-        <v>2023</v>
+        <v>2</v>
+      </c>
+      <c r="C649" s="5">
+        <v>2025</v>
       </c>
     </row>
     <row r="650" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A650" s="2" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="B650" s="3"/>
-      <c r="C650" s="6"/>
+      <c r="C650" s="5"/>
     </row>
     <row r="651" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A651" s="2" t="s">
-        <v>591</v>
+        <v>340</v>
       </c>
       <c r="B651" s="3"/>
-      <c r="C651" s="6"/>
+      <c r="C651" s="5"/>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A652" s="1" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B652" s="3">
         <v>2</v>
       </c>
-      <c r="C652" s="6">
-        <v>2025</v>
+      <c r="C652" s="5">
+        <v>2019</v>
       </c>
     </row>
     <row r="653" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A653" s="2" t="s">
-        <v>339</v>
+        <v>591</v>
       </c>
       <c r="B653" s="3"/>
-      <c r="C653" s="6"/>
+      <c r="C653" s="5"/>
     </row>
     <row r="654" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A654" s="2" t="s">
-        <v>340</v>
+        <v>592</v>
       </c>
       <c r="B654" s="3"/>
-      <c r="C654" s="6"/>
+      <c r="C654" s="5"/>
     </row>
     <row r="655" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A655" s="1" t="s">
-        <v>593</v>
+        <v>365</v>
       </c>
       <c r="B655" s="3">
-        <v>2</v>
-      </c>
-      <c r="C655" s="6">
-        <v>2019</v>
+        <v>1</v>
+      </c>
+      <c r="C655" s="5">
+        <v>2026</v>
       </c>
     </row>
     <row r="656" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A656" s="2" t="s">
-        <v>594</v>
+        <v>366</v>
       </c>
       <c r="B656" s="3"/>
-      <c r="C656" s="6"/>
+      <c r="C656" s="5"/>
     </row>
     <row r="657" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A657" s="2" t="s">
-        <v>595</v>
+        <v>367</v>
       </c>
       <c r="B657" s="3"/>
-      <c r="C657" s="6"/>
+      <c r="C657" s="5"/>
     </row>
     <row r="658" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A658" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B658" s="3">
         <v>1</v>
       </c>
-      <c r="C658" s="6">
-        <v>2026</v>
+      <c r="C658" s="5">
+        <v>2025</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -7845,177 +9012,177 @@
         <v>366</v>
       </c>
       <c r="B659" s="3"/>
-      <c r="C659" s="6"/>
+      <c r="C659" s="5"/>
     </row>
     <row r="660" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A660" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="B660" s="3"/>
-      <c r="C660" s="6"/>
+      <c r="C660" s="5"/>
     </row>
     <row r="661" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A661" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="B661" s="3">
-        <v>1</v>
-      </c>
-      <c r="C661" s="6">
-        <v>2025</v>
+        <v>392</v>
+      </c>
+      <c r="B661" s="3"/>
+      <c r="C661" s="5">
+        <v>2026</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A662" s="2" t="s">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B662" s="3"/>
-      <c r="C662" s="6"/>
+      <c r="C662" s="5"/>
     </row>
     <row r="663" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A663" s="2" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="B663" s="3"/>
-      <c r="C663" s="6"/>
+      <c r="C663" s="5"/>
     </row>
     <row r="664" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A664" s="1" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="B664" s="3"/>
-      <c r="C664" s="6">
-        <v>2026</v>
+      <c r="C664" s="5">
+        <v>2025</v>
       </c>
     </row>
     <row r="665" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A665" s="2" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B665" s="3"/>
-      <c r="C665" s="6"/>
+      <c r="C665" s="5"/>
     </row>
     <row r="666" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A666" s="2" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="B666" s="3"/>
-      <c r="C666" s="6"/>
+      <c r="C666" s="5"/>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A667" s="1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B667" s="3"/>
-      <c r="C667" s="6">
+      <c r="C667" s="5">
         <v>2025</v>
       </c>
     </row>
     <row r="668" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A668" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B668" s="3"/>
-      <c r="C668" s="6"/>
+      <c r="C668" s="5"/>
     </row>
     <row r="669" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A669" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B669" s="3"/>
-      <c r="C669" s="6"/>
+      <c r="C669" s="5"/>
     </row>
     <row r="670" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A670" s="1" t="s">
-        <v>409</v>
+        <v>593</v>
       </c>
       <c r="B670" s="3"/>
-      <c r="C670" s="6">
-        <v>2025</v>
+      <c r="C670" s="5">
+        <v>2023</v>
       </c>
     </row>
     <row r="671" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A671" s="2" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="B671" s="3"/>
-      <c r="C671" s="6"/>
+      <c r="C671" s="5"/>
     </row>
     <row r="672" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A672" s="2" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B672" s="3"/>
-      <c r="C672" s="6"/>
+      <c r="C672" s="5"/>
     </row>
     <row r="673" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A673" s="1" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B673" s="3"/>
-      <c r="C673" s="6">
-        <v>2023</v>
+      <c r="C673" s="5">
+        <v>2022</v>
       </c>
     </row>
     <row r="674" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A674" s="2" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="B674" s="3"/>
-      <c r="C674" s="6"/>
+      <c r="C674" s="5"/>
     </row>
     <row r="675" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A675" s="2" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B675" s="3"/>
-      <c r="C675" s="6"/>
+      <c r="C675" s="5"/>
     </row>
     <row r="676" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A676" s="1" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B676" s="3"/>
-      <c r="C676" s="6">
-        <v>2022</v>
+      <c r="C676" s="5">
+        <v>2020</v>
       </c>
     </row>
     <row r="677" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A677" s="2" t="s">
-        <v>428</v>
+        <v>596</v>
       </c>
       <c r="B677" s="3"/>
-      <c r="C677" s="6"/>
-    </row>
-    <row r="678" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A678" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="B678" s="3"/>
-      <c r="C678" s="6"/>
-    </row>
-    <row r="679" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A679" s="1" t="s">
+      <c r="C677" s="5"/>
+    </row>
+    <row r="678" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A678" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B678" s="3">
+        <v>59</v>
+      </c>
+      <c r="C678" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="679" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A679" s="2" t="s">
         <v>598</v>
       </c>
       <c r="B679" s="3"/>
-      <c r="C679" s="6">
-        <v>2020</v>
-      </c>
+      <c r="C679" s="4"/>
     </row>
     <row r="680" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A680" s="2" t="s">
         <v>599</v>
       </c>
       <c r="B680" s="3"/>
-      <c r="C680" s="6"/>
+      <c r="C680" s="4"/>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A681" s="1" t="s">
         <v>600</v>
       </c>
       <c r="B681" s="3">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C681" s="4">
         <v>2019</v>
@@ -8040,10 +9207,10 @@
         <v>603</v>
       </c>
       <c r="B684" s="3">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C684" s="4">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="685" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8065,10 +9232,10 @@
         <v>606</v>
       </c>
       <c r="B687" s="3">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C687" s="4">
-        <v>2020</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="688" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8093,7 +9260,7 @@
         <v>8</v>
       </c>
       <c r="C690" s="4">
-        <v>2024</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="691" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8115,10 +9282,10 @@
         <v>612</v>
       </c>
       <c r="B693" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C693" s="4">
-        <v>2021</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="694" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8139,11 +9306,9 @@
       <c r="A696" s="1" t="s">
         <v>615</v>
       </c>
-      <c r="B696" s="3">
-        <v>2</v>
-      </c>
+      <c r="B696" s="3"/>
       <c r="C696" s="4">
-        <v>2024</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="697" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8166,7 +9331,7 @@
       </c>
       <c r="B699" s="3"/>
       <c r="C699" s="4">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="700" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8189,7 +9354,7 @@
       </c>
       <c r="B702" s="3"/>
       <c r="C702" s="4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="703" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8212,7 +9377,7 @@
       </c>
       <c r="B705" s="3"/>
       <c r="C705" s="4">
-        <v>2023</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -8222,129 +9387,4576 @@
       <c r="B706" s="3"/>
       <c r="C706" s="4"/>
     </row>
-    <row r="707" spans="1:3" ht="17" x14ac:dyDescent="0.2">
-      <c r="A707" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="B707" s="3"/>
-      <c r="C707" s="4"/>
-    </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A708" s="1" t="s">
-        <v>627</v>
+    <row r="707" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A707" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="B707" s="3">
+        <v>60</v>
+      </c>
+      <c r="C707" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="708" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A708" s="2" t="s">
+        <v>598</v>
       </c>
       <c r="B708" s="3"/>
-      <c r="C708" s="4">
-        <v>2019</v>
-      </c>
+      <c r="C708" s="4"/>
     </row>
     <row r="709" spans="1:3" ht="17" x14ac:dyDescent="0.2">
       <c r="A709" s="2" t="s">
-        <v>628</v>
+        <v>599</v>
       </c>
       <c r="B709" s="3"/>
       <c r="C709" s="4"/>
     </row>
+    <row r="710" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A710" s="1" t="s">
+        <v>600</v>
+      </c>
+      <c r="B710" s="3">
+        <v>42</v>
+      </c>
+      <c r="C710" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="711" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A711" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="B711" s="3"/>
+      <c r="C711" s="4"/>
+    </row>
+    <row r="712" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A712" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B712" s="3"/>
+      <c r="C712" s="4"/>
+    </row>
+    <row r="713" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A713" s="1" t="s">
+        <v>603</v>
+      </c>
+      <c r="B713" s="3">
+        <v>31</v>
+      </c>
+      <c r="C713" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="714" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A714" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B714" s="3"/>
+      <c r="C714" s="4"/>
+    </row>
+    <row r="715" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A715" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B715" s="3"/>
+      <c r="C715" s="4"/>
+    </row>
+    <row r="716" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A716" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="B716" s="3">
+        <v>8</v>
+      </c>
+      <c r="C716" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="717" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A717" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="B717" s="3"/>
+      <c r="C717" s="4"/>
+    </row>
+    <row r="718" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A718" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B718" s="3"/>
+      <c r="C718" s="4"/>
+    </row>
+    <row r="719" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A719" s="1" t="s">
+        <v>609</v>
+      </c>
+      <c r="B719" s="3">
+        <v>8</v>
+      </c>
+      <c r="C719" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="720" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A720" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B720" s="3"/>
+      <c r="C720" s="4"/>
+    </row>
+    <row r="721" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A721" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="B721" s="3"/>
+      <c r="C721" s="4"/>
+    </row>
+    <row r="722" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A722" s="1" t="s">
+        <v>612</v>
+      </c>
+      <c r="B722" s="3">
+        <v>3</v>
+      </c>
+      <c r="C722" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="723" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A723" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="B723" s="3"/>
+      <c r="C723" s="4"/>
+    </row>
+    <row r="724" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A724" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B724" s="3"/>
+      <c r="C724" s="4"/>
+    </row>
+    <row r="725" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A725" s="1" t="s">
+        <v>615</v>
+      </c>
+      <c r="B725" s="3"/>
+      <c r="C725" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="726" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A726" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B726" s="3"/>
+      <c r="C726" s="4"/>
+    </row>
+    <row r="727" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A727" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B727" s="3"/>
+      <c r="C727" s="4"/>
+    </row>
+    <row r="728" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A728" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B728" s="3"/>
+      <c r="C728" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="729" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A729" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B729" s="3"/>
+      <c r="C729" s="4"/>
+    </row>
+    <row r="730" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A730" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="B730" s="3"/>
+      <c r="C730" s="4"/>
+    </row>
+    <row r="731" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A731" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="B731" s="3"/>
+      <c r="C731" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="732" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A732" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="B732" s="3"/>
+      <c r="C732" s="4"/>
+    </row>
+    <row r="733" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A733" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="B733" s="3"/>
+      <c r="C733" s="4"/>
+    </row>
+    <row r="734" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A734" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="B734" s="3"/>
+      <c r="C734" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="735" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A735" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B735" s="3"/>
+      <c r="C735" s="4"/>
+    </row>
+    <row r="736" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A736" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="B736" s="3">
+        <v>380</v>
+      </c>
+      <c r="C736" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="737" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A737" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="B737" s="3"/>
+      <c r="C737" s="4"/>
+    </row>
+    <row r="738" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A738" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B738" s="3"/>
+      <c r="C738" s="4"/>
+    </row>
+    <row r="739" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A739" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="B739" s="3">
+        <v>280</v>
+      </c>
+      <c r="C739" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="740" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A740" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="B740" s="3"/>
+      <c r="C740" s="4"/>
+    </row>
+    <row r="741" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A741" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B741" s="3"/>
+      <c r="C741" s="4"/>
+    </row>
+    <row r="742" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A742" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B742" s="3">
+        <v>197</v>
+      </c>
+      <c r="C742" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="743" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A743" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="B743" s="3"/>
+      <c r="C743" s="4"/>
+    </row>
+    <row r="744" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A744" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B744" s="3"/>
+      <c r="C744" s="4"/>
+    </row>
+    <row r="745" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A745" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="B745" s="3">
+        <v>135</v>
+      </c>
+      <c r="C745" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="746" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A746" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B746" s="3"/>
+      <c r="C746" s="4"/>
+    </row>
+    <row r="747" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A747" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B747" s="3"/>
+      <c r="C747" s="4"/>
+    </row>
+    <row r="748" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A748" s="1" t="s">
+        <v>638</v>
+      </c>
+      <c r="B748" s="3">
+        <v>131</v>
+      </c>
+      <c r="C748" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="749" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A749" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B749" s="3"/>
+      <c r="C749" s="4"/>
+    </row>
+    <row r="750" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A750" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B750" s="3"/>
+      <c r="C750" s="4"/>
+    </row>
+    <row r="751" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A751" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="B751" s="3">
+        <v>120</v>
+      </c>
+      <c r="C751" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="752" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A752" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B752" s="3"/>
+      <c r="C752" s="4"/>
+    </row>
+    <row r="753" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A753" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B753" s="3"/>
+      <c r="C753" s="4"/>
+    </row>
+    <row r="754" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A754" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="B754" s="3">
+        <v>108</v>
+      </c>
+      <c r="C754" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="755" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A755" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B755" s="3"/>
+      <c r="C755" s="4"/>
+    </row>
+    <row r="756" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A756" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B756" s="3"/>
+      <c r="C756" s="4"/>
+    </row>
+    <row r="757" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A757" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B757" s="3">
+        <v>94</v>
+      </c>
+      <c r="C757" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="758" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A758" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B758" s="3"/>
+      <c r="C758" s="4"/>
+    </row>
+    <row r="759" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A759" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="B759" s="3"/>
+      <c r="C759" s="4"/>
+    </row>
+    <row r="760" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A760" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="B760" s="3">
+        <v>84</v>
+      </c>
+      <c r="C760" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="761" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A761" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B761" s="3"/>
+      <c r="C761" s="4"/>
+    </row>
+    <row r="762" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A762" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B762" s="3"/>
+      <c r="C762" s="4"/>
+    </row>
+    <row r="763" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A763" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="B763" s="3">
+        <v>78</v>
+      </c>
+      <c r="C763" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="764" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A764" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B764" s="3"/>
+      <c r="C764" s="4"/>
+    </row>
+    <row r="765" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A765" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="B765" s="3"/>
+      <c r="C765" s="4"/>
+    </row>
+    <row r="766" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A766" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="B766" s="3">
+        <v>77</v>
+      </c>
+      <c r="C766" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="767" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A767" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="B767" s="3"/>
+      <c r="C767" s="4"/>
+    </row>
+    <row r="768" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A768" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B768" s="3"/>
+      <c r="C768" s="4"/>
+    </row>
+    <row r="769" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A769" s="1" t="s">
+        <v>659</v>
+      </c>
+      <c r="B769" s="3">
+        <v>77</v>
+      </c>
+      <c r="C769" s="4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="770" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A770" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B770" s="3"/>
+      <c r="C770" s="4"/>
+    </row>
+    <row r="771" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A771" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="B771" s="3"/>
+      <c r="C771" s="4"/>
+    </row>
+    <row r="772" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A772" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="B772" s="3">
+        <v>73</v>
+      </c>
+      <c r="C772" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="773" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A773" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B773" s="3"/>
+      <c r="C773" s="4"/>
+    </row>
+    <row r="774" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A774" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B774" s="3"/>
+      <c r="C774" s="4"/>
+    </row>
+    <row r="775" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A775" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B775" s="3">
+        <v>66</v>
+      </c>
+      <c r="C775" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="776" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A776" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B776" s="3"/>
+      <c r="C776" s="4"/>
+    </row>
+    <row r="777" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A777" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B777" s="3"/>
+      <c r="C777" s="4"/>
+    </row>
+    <row r="778" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A778" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B778" s="3">
+        <v>60</v>
+      </c>
+      <c r="C778" s="4">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="779" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A779" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B779" s="3"/>
+      <c r="C779" s="4"/>
+    </row>
+    <row r="780" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A780" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B780" s="3"/>
+      <c r="C780" s="4"/>
+    </row>
+    <row r="781" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A781" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="B781" s="3">
+        <v>52</v>
+      </c>
+      <c r="C781" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="782" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A782" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B782" s="3"/>
+      <c r="C782" s="4"/>
+    </row>
+    <row r="783" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A783" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B783" s="3"/>
+      <c r="C783" s="4"/>
+    </row>
+    <row r="784" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A784" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B784" s="3">
+        <v>49</v>
+      </c>
+      <c r="C784" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="785" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A785" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="B785" s="3"/>
+      <c r="C785" s="4"/>
+    </row>
+    <row r="786" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A786" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B786" s="3"/>
+      <c r="C786" s="4"/>
+    </row>
+    <row r="787" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A787" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="B787" s="3">
+        <v>48</v>
+      </c>
+      <c r="C787" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="788" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A788" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B788" s="3"/>
+      <c r="C788" s="4"/>
+    </row>
+    <row r="789" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A789" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B789" s="3"/>
+      <c r="C789" s="4"/>
+    </row>
+    <row r="790" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A790" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B790" s="3">
+        <v>47</v>
+      </c>
+      <c r="C790" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="791" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A791" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B791" s="3"/>
+      <c r="C791" s="4"/>
+    </row>
+    <row r="792" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A792" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B792" s="3"/>
+      <c r="C792" s="4"/>
+    </row>
+    <row r="793" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A793" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B793" s="3">
+        <v>46</v>
+      </c>
+      <c r="C793" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="794" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A794" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B794" s="3"/>
+      <c r="C794" s="4"/>
+    </row>
+    <row r="795" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A795" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B795" s="3"/>
+      <c r="C795" s="4"/>
+    </row>
+    <row r="796" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A796" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="B796" s="3">
+        <v>45</v>
+      </c>
+      <c r="C796" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="797" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A797" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="B797" s="3"/>
+      <c r="C797" s="4"/>
+    </row>
+    <row r="798" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A798" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B798" s="3"/>
+      <c r="C798" s="4"/>
+    </row>
+    <row r="799" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A799" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="B799" s="3">
+        <v>44</v>
+      </c>
+      <c r="C799" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="800" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A800" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B800" s="3"/>
+      <c r="C800" s="4"/>
+    </row>
+    <row r="801" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A801" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="B801" s="3"/>
+      <c r="C801" s="4"/>
+    </row>
+    <row r="802" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A802" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="B802" s="3">
+        <v>42</v>
+      </c>
+      <c r="C802" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="803" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A803" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B803" s="3"/>
+      <c r="C803" s="4"/>
+    </row>
+    <row r="804" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A804" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B804" s="3"/>
+      <c r="C804" s="4"/>
+    </row>
+    <row r="805" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A805" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="B805" s="3">
+        <v>41</v>
+      </c>
+      <c r="C805" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="806" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A806" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B806" s="3"/>
+      <c r="C806" s="4"/>
+    </row>
+    <row r="807" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A807" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B807" s="3"/>
+      <c r="C807" s="4"/>
+    </row>
+    <row r="808" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A808" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="B808" s="3">
+        <v>40</v>
+      </c>
+      <c r="C808" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="809" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A809" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="B809" s="3"/>
+      <c r="C809" s="4"/>
+    </row>
+    <row r="810" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A810" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B810" s="3"/>
+      <c r="C810" s="4"/>
+    </row>
+    <row r="811" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A811" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="B811" s="3">
+        <v>32</v>
+      </c>
+      <c r="C811" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="812" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A812" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B812" s="3"/>
+      <c r="C812" s="4"/>
+    </row>
+    <row r="813" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A813" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="B813" s="3"/>
+      <c r="C813" s="4"/>
+    </row>
+    <row r="814" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A814" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B814" s="3">
+        <v>30</v>
+      </c>
+      <c r="C814" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="815" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A815" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="B815" s="3"/>
+      <c r="C815" s="4"/>
+    </row>
+    <row r="816" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A816" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B816" s="3"/>
+      <c r="C816" s="4"/>
+    </row>
+    <row r="817" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A817" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B817" s="3">
+        <v>29</v>
+      </c>
+      <c r="C817" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="818" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A818" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B818" s="3"/>
+      <c r="C818" s="4"/>
+    </row>
+    <row r="819" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A819" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="B819" s="3"/>
+      <c r="C819" s="4"/>
+    </row>
+    <row r="820" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A820" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="B820" s="3">
+        <v>24</v>
+      </c>
+      <c r="C820" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="821" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A821" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="B821" s="3"/>
+      <c r="C821" s="4"/>
+    </row>
+    <row r="822" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A822" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B822" s="3"/>
+      <c r="C822" s="4"/>
+    </row>
+    <row r="823" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A823" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B823" s="3">
+        <v>24</v>
+      </c>
+      <c r="C823" s="4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="824" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A824" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="B824" s="3"/>
+      <c r="C824" s="4"/>
+    </row>
+    <row r="825" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A825" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="B825" s="3"/>
+      <c r="C825" s="4"/>
+    </row>
+    <row r="826" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A826" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="B826" s="3">
+        <v>23</v>
+      </c>
+      <c r="C826" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="827" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A827" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B827" s="3"/>
+      <c r="C827" s="4"/>
+    </row>
+    <row r="828" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A828" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B828" s="3"/>
+      <c r="C828" s="4"/>
+    </row>
+    <row r="829" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A829" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B829" s="3">
+        <v>22</v>
+      </c>
+      <c r="C829" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="830" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A830" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B830" s="3"/>
+      <c r="C830" s="4"/>
+    </row>
+    <row r="831" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A831" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B831" s="3"/>
+      <c r="C831" s="4"/>
+    </row>
+    <row r="832" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A832" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B832" s="3">
+        <v>21</v>
+      </c>
+      <c r="C832" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="833" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A833" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B833" s="3"/>
+      <c r="C833" s="4"/>
+    </row>
+    <row r="834" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A834" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="B834" s="3"/>
+      <c r="C834" s="4"/>
+    </row>
+    <row r="835" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A835" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="B835" s="3">
+        <v>21</v>
+      </c>
+      <c r="C835" s="4">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="836" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A836" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="B836" s="3"/>
+      <c r="C836" s="4"/>
+    </row>
+    <row r="837" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A837" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B837" s="3"/>
+      <c r="C837" s="4"/>
+    </row>
+    <row r="838" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A838" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B838" s="3">
+        <v>20</v>
+      </c>
+      <c r="C838" s="4">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="839" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A839" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B839" s="3"/>
+      <c r="C839" s="4"/>
+    </row>
+    <row r="840" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A840" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="B840" s="3"/>
+      <c r="C840" s="4"/>
+    </row>
+    <row r="841" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A841" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B841" s="3">
+        <v>19</v>
+      </c>
+      <c r="C841" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="842" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A842" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B842" s="3"/>
+      <c r="C842" s="4"/>
+    </row>
+    <row r="843" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A843" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B843" s="3"/>
+      <c r="C843" s="4"/>
+    </row>
+    <row r="844" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A844" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B844" s="3">
+        <v>19</v>
+      </c>
+      <c r="C844" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="845" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A845" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B845" s="3"/>
+      <c r="C845" s="4"/>
+    </row>
+    <row r="846" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A846" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B846" s="3"/>
+      <c r="C846" s="4"/>
+    </row>
+    <row r="847" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A847" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B847" s="3">
+        <v>19</v>
+      </c>
+      <c r="C847" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="848" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A848" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B848" s="3"/>
+      <c r="C848" s="4"/>
+    </row>
+    <row r="849" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A849" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="B849" s="3"/>
+      <c r="C849" s="4"/>
+    </row>
+    <row r="850" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A850" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B850" s="3">
+        <v>18</v>
+      </c>
+      <c r="C850" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="851" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A851" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="B851" s="3"/>
+      <c r="C851" s="4"/>
+    </row>
+    <row r="852" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A852" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B852" s="3"/>
+      <c r="C852" s="4"/>
+    </row>
+    <row r="853" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A853" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B853" s="3">
+        <v>16</v>
+      </c>
+      <c r="C853" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="854" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A854" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B854" s="3"/>
+      <c r="C854" s="4"/>
+    </row>
+    <row r="855" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A855" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B855" s="3"/>
+      <c r="C855" s="4"/>
+    </row>
+    <row r="856" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A856" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B856" s="3">
+        <v>16</v>
+      </c>
+      <c r="C856" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="857" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A857" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B857" s="3"/>
+      <c r="C857" s="4"/>
+    </row>
+    <row r="858" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A858" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B858" s="3"/>
+      <c r="C858" s="4"/>
+    </row>
+    <row r="859" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A859" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B859" s="3">
+        <v>16</v>
+      </c>
+      <c r="C859" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="860" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A860" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B860" s="3"/>
+      <c r="C860" s="4"/>
+    </row>
+    <row r="861" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A861" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B861" s="3"/>
+      <c r="C861" s="4"/>
+    </row>
+    <row r="862" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A862" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B862" s="3">
+        <v>16</v>
+      </c>
+      <c r="C862" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="863" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A863" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B863" s="3"/>
+      <c r="C863" s="4"/>
+    </row>
+    <row r="864" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A864" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B864" s="3"/>
+      <c r="C864" s="4"/>
+    </row>
+    <row r="865" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A865" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B865" s="3">
+        <v>16</v>
+      </c>
+      <c r="C865" s="4">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="866" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A866" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="B866" s="3"/>
+      <c r="C866" s="4"/>
+    </row>
+    <row r="867" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A867" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B867" s="3"/>
+      <c r="C867" s="4"/>
+    </row>
+    <row r="868" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A868" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B868" s="3">
+        <v>15</v>
+      </c>
+      <c r="C868" s="4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="869" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A869" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B869" s="3"/>
+      <c r="C869" s="4"/>
+    </row>
+    <row r="870" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A870" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B870" s="3"/>
+      <c r="C870" s="4"/>
+    </row>
+    <row r="871" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A871" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B871" s="3">
+        <v>14</v>
+      </c>
+      <c r="C871" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="872" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A872" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B872" s="3"/>
+      <c r="C872" s="4"/>
+    </row>
+    <row r="873" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A873" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="B873" s="3"/>
+      <c r="C873" s="4"/>
+    </row>
+    <row r="874" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A874" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B874" s="3">
+        <v>14</v>
+      </c>
+      <c r="C874" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="875" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A875" s="2" t="s">
+        <v>755</v>
+      </c>
+      <c r="B875" s="3"/>
+      <c r="C875" s="4"/>
+    </row>
+    <row r="876" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A876" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="B876" s="3"/>
+      <c r="C876" s="4"/>
+    </row>
+    <row r="877" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A877" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B877" s="3">
+        <v>13</v>
+      </c>
+      <c r="C877" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="878" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A878" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B878" s="3"/>
+      <c r="C878" s="4"/>
+    </row>
+    <row r="879" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A879" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B879" s="3"/>
+      <c r="C879" s="4"/>
+    </row>
+    <row r="880" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A880" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B880" s="3">
+        <v>13</v>
+      </c>
+      <c r="C880" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="881" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A881" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B881" s="3"/>
+      <c r="C881" s="4"/>
+    </row>
+    <row r="882" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A882" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B882" s="3"/>
+      <c r="C882" s="4"/>
+    </row>
+    <row r="883" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A883" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B883" s="3">
+        <v>12</v>
+      </c>
+      <c r="C883" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="884" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A884" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="B884" s="3"/>
+      <c r="C884" s="4"/>
+    </row>
+    <row r="885" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A885" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="B885" s="3"/>
+      <c r="C885" s="4"/>
+    </row>
+    <row r="886" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A886" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B886" s="3">
+        <v>12</v>
+      </c>
+      <c r="C886" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="887" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A887" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B887" s="3"/>
+      <c r="C887" s="4"/>
+    </row>
+    <row r="888" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A888" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B888" s="3"/>
+      <c r="C888" s="4"/>
+    </row>
+    <row r="889" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A889" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B889" s="3">
+        <v>12</v>
+      </c>
+      <c r="C889" s="4">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="890" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A890" s="2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B890" s="3"/>
+      <c r="C890" s="4"/>
+    </row>
+    <row r="891" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A891" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B891" s="3"/>
+      <c r="C891" s="4"/>
+    </row>
+    <row r="892" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A892" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B892" s="3">
+        <v>12</v>
+      </c>
+      <c r="C892" s="4">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="893" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A893" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B893" s="3"/>
+      <c r="C893" s="4"/>
+    </row>
+    <row r="894" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A894" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B894" s="3"/>
+      <c r="C894" s="4"/>
+    </row>
+    <row r="895" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A895" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B895" s="3">
+        <v>10</v>
+      </c>
+      <c r="C895" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="896" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A896" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B896" s="3"/>
+      <c r="C896" s="4"/>
+    </row>
+    <row r="897" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A897" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B897" s="3"/>
+      <c r="C897" s="4"/>
+    </row>
+    <row r="898" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A898" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B898" s="3">
+        <v>10</v>
+      </c>
+      <c r="C898" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="899" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A899" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B899" s="3"/>
+      <c r="C899" s="4"/>
+    </row>
+    <row r="900" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A900" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B900" s="3"/>
+      <c r="C900" s="4"/>
+    </row>
+    <row r="901" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A901" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B901" s="3">
+        <v>10</v>
+      </c>
+      <c r="C901" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="902" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A902" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="B902" s="3"/>
+      <c r="C902" s="4"/>
+    </row>
+    <row r="903" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A903" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B903" s="3"/>
+      <c r="C903" s="4"/>
+    </row>
+    <row r="904" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A904" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B904" s="3">
+        <v>9</v>
+      </c>
+      <c r="C904" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="905" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A905" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B905" s="3"/>
+      <c r="C905" s="4"/>
+    </row>
+    <row r="906" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A906" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B906" s="3"/>
+      <c r="C906" s="4"/>
+    </row>
+    <row r="907" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A907" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B907" s="3">
+        <v>9</v>
+      </c>
+      <c r="C907" s="4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="908" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A908" s="2" t="s">
+        <v>780</v>
+      </c>
+      <c r="B908" s="3"/>
+      <c r="C908" s="4"/>
+    </row>
+    <row r="909" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A909" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B909" s="3"/>
+      <c r="C909" s="4"/>
+    </row>
+    <row r="910" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A910" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B910" s="3">
+        <v>9</v>
+      </c>
+      <c r="C910" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="911" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A911" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B911" s="3"/>
+      <c r="C911" s="4"/>
+    </row>
+    <row r="912" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A912" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B912" s="3"/>
+      <c r="C912" s="4"/>
+    </row>
+    <row r="913" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A913" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B913" s="3">
+        <v>9</v>
+      </c>
+      <c r="C913" s="4">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="914" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A914" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="B914" s="3"/>
+      <c r="C914" s="4"/>
+    </row>
+    <row r="915" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A915" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B915" s="3"/>
+      <c r="C915" s="4"/>
+    </row>
+    <row r="916" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A916" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="B916" s="3">
+        <v>8</v>
+      </c>
+      <c r="C916" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="917" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A917" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B917" s="3"/>
+      <c r="C917" s="4"/>
+    </row>
+    <row r="918" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A918" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B918" s="3"/>
+      <c r="C918" s="4"/>
+    </row>
+    <row r="919" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A919" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="B919" s="3">
+        <v>8</v>
+      </c>
+      <c r="C919" s="4">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="920" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A920" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B920" s="3"/>
+      <c r="C920" s="4"/>
+    </row>
+    <row r="921" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A921" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B921" s="3"/>
+      <c r="C921" s="4"/>
+    </row>
+    <row r="922" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A922" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="B922" s="3">
+        <v>7</v>
+      </c>
+      <c r="C922" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="923" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A923" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B923" s="3"/>
+      <c r="C923" s="4"/>
+    </row>
+    <row r="924" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A924" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B924" s="3"/>
+      <c r="C924" s="4"/>
+    </row>
+    <row r="925" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A925" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B925" s="3">
+        <v>7</v>
+      </c>
+      <c r="C925" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="926" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A926" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B926" s="3"/>
+      <c r="C926" s="4"/>
+    </row>
+    <row r="927" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A927" s="2" t="s">
+        <v>793</v>
+      </c>
+      <c r="B927" s="3"/>
+      <c r="C927" s="4"/>
+    </row>
+    <row r="928" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A928" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B928" s="3">
+        <v>7</v>
+      </c>
+      <c r="C928" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="929" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A929" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B929" s="3"/>
+      <c r="C929" s="4"/>
+    </row>
+    <row r="930" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A930" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B930" s="3"/>
+      <c r="C930" s="4"/>
+    </row>
+    <row r="931" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A931" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B931" s="3">
+        <v>6</v>
+      </c>
+      <c r="C931" s="4">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="932" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A932" s="2" t="s">
+        <v>797</v>
+      </c>
+      <c r="B932" s="3"/>
+      <c r="C932" s="4"/>
+    </row>
+    <row r="933" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A933" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B933" s="3"/>
+      <c r="C933" s="4"/>
+    </row>
+    <row r="934" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A934" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B934" s="3">
+        <v>5</v>
+      </c>
+      <c r="C934" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="935" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A935" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B935" s="3"/>
+      <c r="C935" s="4"/>
+    </row>
+    <row r="936" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A936" s="2" t="s">
+        <v>801</v>
+      </c>
+      <c r="B936" s="3"/>
+      <c r="C936" s="4"/>
+    </row>
+    <row r="937" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A937" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B937" s="3">
+        <v>5</v>
+      </c>
+      <c r="C937" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="938" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A938" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="B938" s="3"/>
+      <c r="C938" s="4"/>
+    </row>
+    <row r="939" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A939" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B939" s="3">
+        <v>5</v>
+      </c>
+      <c r="C939" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="940" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A940" s="2" t="s">
+        <v>805</v>
+      </c>
+      <c r="B940" s="3"/>
+      <c r="C940" s="4"/>
+    </row>
+    <row r="941" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A941" s="2" t="s">
+        <v>806</v>
+      </c>
+      <c r="B941" s="3"/>
+      <c r="C941" s="4"/>
+    </row>
+    <row r="942" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A942" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B942" s="3">
+        <v>5</v>
+      </c>
+      <c r="C942" s="4">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="943" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A943" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B943" s="3"/>
+      <c r="C943" s="4"/>
+    </row>
+    <row r="944" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A944" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B944" s="3"/>
+      <c r="C944" s="4"/>
+    </row>
+    <row r="945" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A945" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B945" s="3">
+        <v>4</v>
+      </c>
+      <c r="C945" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="946" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A946" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="B946" s="3"/>
+      <c r="C946" s="4"/>
+    </row>
+    <row r="947" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A947" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B947" s="3"/>
+      <c r="C947" s="4"/>
+    </row>
+    <row r="948" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A948" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B948" s="3">
+        <v>4</v>
+      </c>
+      <c r="C948" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="949" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A949" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B949" s="3"/>
+      <c r="C949" s="4"/>
+    </row>
+    <row r="950" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A950" s="2" t="s">
+        <v>814</v>
+      </c>
+      <c r="B950" s="3"/>
+      <c r="C950" s="4"/>
+    </row>
+    <row r="951" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A951" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B951" s="3">
+        <v>4</v>
+      </c>
+      <c r="C951" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="952" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A952" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B952" s="3"/>
+      <c r="C952" s="4"/>
+    </row>
+    <row r="953" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A953" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B953" s="3"/>
+      <c r="C953" s="4"/>
+    </row>
+    <row r="954" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A954" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B954" s="3">
+        <v>4</v>
+      </c>
+      <c r="C954" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="955" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A955" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B955" s="3"/>
+      <c r="C955" s="4"/>
+    </row>
+    <row r="956" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A956" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B956" s="3"/>
+      <c r="C956" s="4"/>
+    </row>
+    <row r="957" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A957" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B957" s="3">
+        <v>4</v>
+      </c>
+      <c r="C957" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="958" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A958" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B958" s="3"/>
+      <c r="C958" s="4"/>
+    </row>
+    <row r="959" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A959" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="B959" s="3"/>
+      <c r="C959" s="4"/>
+    </row>
+    <row r="960" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A960" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B960" s="3">
+        <v>4</v>
+      </c>
+      <c r="C960" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="961" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A961" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B961" s="3"/>
+      <c r="C961" s="4"/>
+    </row>
+    <row r="962" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A962" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B962" s="3"/>
+      <c r="C962" s="4"/>
+    </row>
+    <row r="963" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A963" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B963" s="3">
+        <v>4</v>
+      </c>
+      <c r="C963" s="4">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="964" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A964" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B964" s="3"/>
+      <c r="C964" s="4"/>
+    </row>
+    <row r="965" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A965" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="B965" s="3"/>
+      <c r="C965" s="4"/>
+    </row>
+    <row r="966" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A966" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="B966" s="3">
+        <v>4</v>
+      </c>
+      <c r="C966" s="4">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="967" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A967" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B967" s="3"/>
+      <c r="C967" s="4"/>
+    </row>
+    <row r="968" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A968" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B968" s="3"/>
+      <c r="C968" s="4"/>
+    </row>
+    <row r="969" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A969" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B969" s="3">
+        <v>4</v>
+      </c>
+      <c r="C969" s="4">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="970" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A970" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B970" s="3"/>
+      <c r="C970" s="4"/>
+    </row>
+    <row r="971" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A971" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B971" s="3"/>
+      <c r="C971" s="4"/>
+    </row>
+    <row r="972" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A972" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="B972" s="3">
+        <v>4</v>
+      </c>
+      <c r="C972" s="4">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="973" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A973" s="2" t="s">
+        <v>833</v>
+      </c>
+      <c r="B973" s="3"/>
+      <c r="C973" s="4"/>
+    </row>
+    <row r="974" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A974" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B974" s="3"/>
+      <c r="C974" s="4"/>
+    </row>
+    <row r="975" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A975" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B975" s="3">
+        <v>4</v>
+      </c>
+      <c r="C975" s="4">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="976" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A976" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B976" s="3"/>
+      <c r="C976" s="4"/>
+    </row>
+    <row r="977" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A977" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B977" s="3"/>
+      <c r="C977" s="4"/>
+    </row>
+    <row r="978" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A978" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B978" s="3">
+        <v>4</v>
+      </c>
+      <c r="C978" s="4">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="979" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A979" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B979" s="3"/>
+      <c r="C979" s="4"/>
+    </row>
+    <row r="980" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A980" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="B980" s="3"/>
+      <c r="C980" s="4"/>
+    </row>
+    <row r="981" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A981" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B981" s="3">
+        <v>3</v>
+      </c>
+      <c r="C981" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="982" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A982" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B982" s="3"/>
+      <c r="C982" s="4"/>
+    </row>
+    <row r="983" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A983" s="2" t="s">
+        <v>842</v>
+      </c>
+      <c r="B983" s="3"/>
+      <c r="C983" s="4"/>
+    </row>
+    <row r="984" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A984" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B984" s="3">
+        <v>3</v>
+      </c>
+      <c r="C984" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="985" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A985" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B985" s="3"/>
+      <c r="C985" s="4"/>
+    </row>
+    <row r="986" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A986" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B986" s="3"/>
+      <c r="C986" s="4"/>
+    </row>
+    <row r="987" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A987" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B987" s="3">
+        <v>3</v>
+      </c>
+      <c r="C987" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="988" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A988" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B988" s="3"/>
+      <c r="C988" s="4"/>
+    </row>
+    <row r="989" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A989" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="B989" s="3"/>
+      <c r="C989" s="4"/>
+    </row>
+    <row r="990" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A990" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B990" s="3">
+        <v>3</v>
+      </c>
+      <c r="C990" s="4">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="991" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A991" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="B991" s="3"/>
+      <c r="C991" s="4"/>
+    </row>
+    <row r="992" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A992" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B992" s="3"/>
+      <c r="C992" s="4"/>
+    </row>
+    <row r="993" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A993" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B993" s="3">
+        <v>3</v>
+      </c>
+      <c r="C993" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="994" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A994" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B994" s="3"/>
+      <c r="C994" s="4"/>
+    </row>
+    <row r="995" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A995" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B995" s="3"/>
+      <c r="C995" s="4"/>
+    </row>
+    <row r="996" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A996" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B996" s="3">
+        <v>3</v>
+      </c>
+      <c r="C996" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="997" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A997" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B997" s="3"/>
+      <c r="C997" s="4"/>
+    </row>
+    <row r="998" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A998" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B998" s="3"/>
+      <c r="C998" s="4"/>
+    </row>
+    <row r="999" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A999" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B999" s="3">
+        <v>3</v>
+      </c>
+      <c r="C999" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1000" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="B1000" s="3"/>
+      <c r="C1000" s="4"/>
+    </row>
+    <row r="1001" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1001" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="B1001" s="3"/>
+      <c r="C1001" s="4"/>
+    </row>
+    <row r="1002" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1002" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B1002" s="3">
+        <v>3</v>
+      </c>
+      <c r="C1002" s="4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1003" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1003" s="3"/>
+      <c r="C1003" s="4"/>
+    </row>
+    <row r="1004" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1004" s="2" t="s">
+        <v>857</v>
+      </c>
+      <c r="B1004" s="3"/>
+      <c r="C1004" s="4"/>
+    </row>
+    <row r="1005" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1005" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B1005" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1005" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1006" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="B1006" s="3"/>
+      <c r="C1006" s="4"/>
+    </row>
+    <row r="1007" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1007" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="B1007" s="3"/>
+      <c r="C1007" s="4"/>
+    </row>
+    <row r="1008" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1008" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B1008" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1008" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1009" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1009" s="3"/>
+      <c r="C1009" s="4"/>
+    </row>
+    <row r="1010" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1010" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="B1010" s="3"/>
+      <c r="C1010" s="4"/>
+    </row>
+    <row r="1011" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1011" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B1011" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1011" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1012" s="2" t="s">
+        <v>864</v>
+      </c>
+      <c r="B1012" s="3"/>
+      <c r="C1012" s="4"/>
+    </row>
+    <row r="1013" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1013" s="2" t="s">
+        <v>865</v>
+      </c>
+      <c r="B1013" s="3"/>
+      <c r="C1013" s="4"/>
+    </row>
+    <row r="1014" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1014" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B1014" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1014" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1015" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1015" s="3"/>
+      <c r="C1015" s="4"/>
+    </row>
+    <row r="1016" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1016" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1016" s="3"/>
+      <c r="C1016" s="4"/>
+    </row>
+    <row r="1017" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1017" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B1017" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1017" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1018" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="B1018" s="3"/>
+      <c r="C1018" s="4"/>
+    </row>
+    <row r="1019" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1019" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="B1019" s="3"/>
+      <c r="C1019" s="4"/>
+    </row>
+    <row r="1020" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1020" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B1020" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1020" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1021" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="B1021" s="3"/>
+      <c r="C1021" s="4"/>
+    </row>
+    <row r="1022" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1022" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="B1022" s="3"/>
+      <c r="C1022" s="4"/>
+    </row>
+    <row r="1023" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1023" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="B1023" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1023" s="4">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1024" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="B1024" s="3"/>
+      <c r="C1024" s="4"/>
+    </row>
+    <row r="1025" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1025" s="2" t="s">
+        <v>875</v>
+      </c>
+      <c r="B1025" s="3"/>
+      <c r="C1025" s="4"/>
+    </row>
+    <row r="1026" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1026" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B1026" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1026" s="4">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1027" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="B1027" s="3"/>
+      <c r="C1027" s="4"/>
+    </row>
+    <row r="1028" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1028" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="B1028" s="3"/>
+      <c r="C1028" s="4"/>
+    </row>
+    <row r="1029" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1029" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B1029" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1029" s="4">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1030" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1030" s="3"/>
+      <c r="C1030" s="4"/>
+    </row>
+    <row r="1031" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1031" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="B1031" s="3"/>
+      <c r="C1031" s="4"/>
+    </row>
+    <row r="1032" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1032" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B1032" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1032" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1033" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B1033" s="3"/>
+      <c r="C1033" s="4"/>
+    </row>
+    <row r="1034" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1034" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="B1034" s="3"/>
+      <c r="C1034" s="4"/>
+    </row>
+    <row r="1035" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1035" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B1035" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1035" s="4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1036" s="2" t="s">
+        <v>885</v>
+      </c>
+      <c r="B1036" s="3"/>
+      <c r="C1036" s="4"/>
+    </row>
+    <row r="1037" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1037" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="B1037" s="3"/>
+      <c r="C1037" s="4"/>
+    </row>
+    <row r="1038" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1038" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B1038" s="3">
+        <v>2</v>
+      </c>
+      <c r="C1038" s="4">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1039" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B1039" s="3"/>
+      <c r="C1039" s="4"/>
+    </row>
+    <row r="1040" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1040" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="B1040" s="3"/>
+      <c r="C1040" s="4"/>
+    </row>
+    <row r="1041" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1041" s="1" t="s">
+        <v>890</v>
+      </c>
+      <c r="B1041" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1041" s="4">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1042" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B1042" s="3"/>
+      <c r="C1042" s="4"/>
+    </row>
+    <row r="1043" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1043" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="B1043" s="3"/>
+      <c r="C1043" s="4"/>
+    </row>
+    <row r="1044" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1044" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="B1044" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1044" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1045" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B1045" s="3"/>
+      <c r="C1045" s="4"/>
+    </row>
+    <row r="1046" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1046" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="B1046" s="3"/>
+      <c r="C1046" s="4"/>
+    </row>
+    <row r="1047" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1047" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B1047" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1047" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1048" s="2" t="s">
+        <v>897</v>
+      </c>
+      <c r="B1048" s="3"/>
+      <c r="C1048" s="4"/>
+    </row>
+    <row r="1049" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1049" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="B1049" s="3"/>
+      <c r="C1049" s="4"/>
+    </row>
+    <row r="1050" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1050" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="B1050" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1050" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1051" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B1051" s="3"/>
+      <c r="C1051" s="4"/>
+    </row>
+    <row r="1052" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1052" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B1052" s="3"/>
+      <c r="C1052" s="4"/>
+    </row>
+    <row r="1053" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1053" s="1" t="s">
+        <v>899</v>
+      </c>
+      <c r="B1053" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1053" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1054" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="B1054" s="3"/>
+      <c r="C1054" s="4"/>
+    </row>
+    <row r="1055" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1055" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="B1055" s="3"/>
+      <c r="C1055" s="4"/>
+    </row>
+    <row r="1056" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1056" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B1056" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1056" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1057" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1057" s="3"/>
+      <c r="C1057" s="4"/>
+    </row>
+    <row r="1058" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1058" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1058" s="3"/>
+      <c r="C1058" s="4"/>
+    </row>
+    <row r="1059" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1059" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B1059" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1059" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1060" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1060" s="3"/>
+      <c r="C1060" s="4"/>
+    </row>
+    <row r="1061" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1061" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1061" s="3"/>
+      <c r="C1061" s="4"/>
+    </row>
+    <row r="1062" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1062" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B1062" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1062" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1063" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1063" s="3"/>
+      <c r="C1063" s="4"/>
+    </row>
+    <row r="1064" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1064" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1064" s="3"/>
+      <c r="C1064" s="4"/>
+    </row>
+    <row r="1065" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1065" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B1065" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1065" s="4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1066" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1066" s="3"/>
+      <c r="C1066" s="4"/>
+    </row>
+    <row r="1067" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1067" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="B1067" s="3"/>
+      <c r="C1067" s="4"/>
+    </row>
+    <row r="1068" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1068" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B1068" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1068" s="4">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1069" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1069" s="3"/>
+      <c r="C1069" s="4"/>
+    </row>
+    <row r="1070" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1070" s="2" t="s">
+        <v>908</v>
+      </c>
+      <c r="B1070" s="3"/>
+      <c r="C1070" s="4"/>
+    </row>
+    <row r="1071" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1071" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B1071" s="3">
+        <v>1</v>
+      </c>
+      <c r="C1071" s="4">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1072" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="B1072" s="3"/>
+      <c r="C1072" s="4"/>
+    </row>
+    <row r="1073" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1073" s="2" t="s">
+        <v>911</v>
+      </c>
+      <c r="B1073" s="3"/>
+      <c r="C1073" s="4"/>
+    </row>
+    <row r="1074" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1074" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B1074" s="3"/>
+      <c r="C1074" s="4">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1075" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1075" s="3"/>
+      <c r="C1075" s="4"/>
+    </row>
+    <row r="1076" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1076" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B1076" s="3"/>
+      <c r="C1076" s="4"/>
+    </row>
+    <row r="1077" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1077" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B1077" s="3"/>
+      <c r="C1077" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1078" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="B1078" s="3"/>
+      <c r="C1078" s="4"/>
+    </row>
+    <row r="1079" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1079" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B1079" s="3"/>
+      <c r="C1079" s="4"/>
+    </row>
+    <row r="1080" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1080" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B1080" s="3"/>
+      <c r="C1080" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1081" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1081" s="3"/>
+      <c r="C1081" s="4"/>
+    </row>
+    <row r="1082" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1082" s="2" t="s">
+        <v>917</v>
+      </c>
+      <c r="B1082" s="3"/>
+      <c r="C1082" s="4"/>
+    </row>
+    <row r="1083" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1083" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B1083" s="3"/>
+      <c r="C1083" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1084" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1084" s="3"/>
+      <c r="C1084" s="4"/>
+    </row>
+    <row r="1085" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1085" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="B1085" s="3"/>
+      <c r="C1085" s="4"/>
+    </row>
+    <row r="1086" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1086" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B1086" s="3"/>
+      <c r="C1086" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1087" s="2" t="s">
+        <v>921</v>
+      </c>
+      <c r="B1087" s="3"/>
+      <c r="C1087" s="4"/>
+    </row>
+    <row r="1088" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1088" s="2" t="s">
+        <v>922</v>
+      </c>
+      <c r="B1088" s="3"/>
+      <c r="C1088" s="4"/>
+    </row>
+    <row r="1089" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1089" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B1089" s="3"/>
+      <c r="C1089" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1090" s="2" t="s">
+        <v>924</v>
+      </c>
+      <c r="B1090" s="3"/>
+      <c r="C1090" s="4"/>
+    </row>
+    <row r="1091" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1091" s="2" t="s">
+        <v>925</v>
+      </c>
+      <c r="B1091" s="3"/>
+      <c r="C1091" s="4"/>
+    </row>
+    <row r="1092" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1092" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B1092" s="3"/>
+      <c r="C1092" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1093" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1093" s="3"/>
+      <c r="C1093" s="4"/>
+    </row>
+    <row r="1094" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1094" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B1094" s="3"/>
+      <c r="C1094" s="4"/>
+    </row>
+    <row r="1095" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1095" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B1095" s="3"/>
+      <c r="C1095" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1096" s="2" t="s">
+        <v>927</v>
+      </c>
+      <c r="B1096" s="3"/>
+      <c r="C1096" s="4"/>
+    </row>
+    <row r="1097" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1097" s="2" t="s">
+        <v>928</v>
+      </c>
+      <c r="B1097" s="3"/>
+      <c r="C1097" s="4"/>
+    </row>
+    <row r="1098" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1098" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B1098" s="3"/>
+      <c r="C1098" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1099" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1099" s="3"/>
+      <c r="C1099" s="4"/>
+    </row>
+    <row r="1100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1100" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B1100" s="3"/>
+      <c r="C1100" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1101" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1101" s="3"/>
+      <c r="C1101" s="4"/>
+    </row>
+    <row r="1102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1102" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B1102" s="3"/>
+      <c r="C1102" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1103" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1103" s="3"/>
+      <c r="C1103" s="4"/>
+    </row>
+    <row r="1104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1104" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B1104" s="3"/>
+      <c r="C1104" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1105" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1105" s="3"/>
+      <c r="C1105" s="4"/>
+    </row>
+    <row r="1106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1106" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B1106" s="3"/>
+      <c r="C1106" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1107" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1107" s="3"/>
+      <c r="C1107" s="4"/>
+    </row>
+    <row r="1108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1108" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B1108" s="3"/>
+      <c r="C1108" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1109" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1109" s="3"/>
+      <c r="C1109" s="4"/>
+    </row>
+    <row r="1110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1110" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B1110" s="3"/>
+      <c r="C1110" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1111" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1111" s="3"/>
+      <c r="C1111" s="4"/>
+    </row>
+    <row r="1112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1112" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B1112" s="3"/>
+      <c r="C1112" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1113" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1113" s="3"/>
+      <c r="C1113" s="4"/>
+    </row>
+    <row r="1114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1114" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B1114" s="3"/>
+      <c r="C1114" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1115" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1115" s="3"/>
+      <c r="C1115" s="4"/>
+    </row>
+    <row r="1116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1116" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B1116" s="3"/>
+      <c r="C1116" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1117" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1117" s="3"/>
+      <c r="C1117" s="4"/>
+    </row>
+    <row r="1118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1118" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="B1118" s="3"/>
+      <c r="C1118" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1119" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1119" s="3"/>
+      <c r="C1119" s="4"/>
+    </row>
+    <row r="1120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1120" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B1120" s="3"/>
+      <c r="C1120" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1121" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1121" s="3"/>
+      <c r="C1121" s="4"/>
+    </row>
+    <row r="1122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1122" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1122" s="3"/>
+      <c r="C1122" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1123" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1123" s="3"/>
+      <c r="C1123" s="4"/>
+    </row>
+    <row r="1124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1124" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B1124" s="3"/>
+      <c r="C1124" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1125" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1125" s="3"/>
+      <c r="C1125" s="4"/>
+    </row>
+    <row r="1126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1126" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B1126" s="3"/>
+      <c r="C1126" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1127" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1127" s="3"/>
+      <c r="C1127" s="4"/>
+    </row>
+    <row r="1128" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1128" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B1128" s="3"/>
+      <c r="C1128" s="4"/>
+    </row>
+    <row r="1129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1129" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B1129" s="3"/>
+      <c r="C1129" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1130" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1130" s="3"/>
+      <c r="C1130" s="4"/>
+    </row>
+    <row r="1131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1131" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B1131" s="3"/>
+      <c r="C1131" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1132" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1132" s="3"/>
+      <c r="C1132" s="4"/>
+    </row>
+    <row r="1133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1133" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B1133" s="3"/>
+      <c r="C1133" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1134" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1134" s="3"/>
+      <c r="C1134" s="4"/>
+    </row>
+    <row r="1135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1135" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B1135" s="3"/>
+      <c r="C1135" s="4">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1136" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B1136" s="3"/>
+      <c r="C1136" s="4"/>
+    </row>
+    <row r="1137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1137" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B1137" s="3"/>
+      <c r="C1137" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1138" s="2" t="s">
+        <v>948</v>
+      </c>
+      <c r="B1138" s="3"/>
+      <c r="C1138" s="4"/>
+    </row>
+    <row r="1139" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1139" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B1139" s="3"/>
+      <c r="C1139" s="4"/>
+    </row>
+    <row r="1140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1140" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B1140" s="3"/>
+      <c r="C1140" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1141" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="B1141" s="3"/>
+      <c r="C1141" s="4"/>
+    </row>
+    <row r="1142" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1142" s="2" t="s">
+        <v>952</v>
+      </c>
+      <c r="B1142" s="3"/>
+      <c r="C1142" s="4"/>
+    </row>
+    <row r="1143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1143" s="1" t="s">
+        <v>953</v>
+      </c>
+      <c r="B1143" s="3"/>
+      <c r="C1143" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1144" s="2" t="s">
+        <v>954</v>
+      </c>
+      <c r="B1144" s="3"/>
+      <c r="C1144" s="4"/>
+    </row>
+    <row r="1145" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1145" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="B1145" s="3"/>
+      <c r="C1145" s="4"/>
+    </row>
+    <row r="1146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1146" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B1146" s="3"/>
+      <c r="C1146" s="4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1147" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="B1147" s="3"/>
+      <c r="C1147" s="4"/>
+    </row>
+    <row r="1148" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1148" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="B1148" s="3"/>
+      <c r="C1148" s="4"/>
+    </row>
+    <row r="1149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1149" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B1149" s="3"/>
+      <c r="C1149" s="4">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1150" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="B1150" s="3"/>
+      <c r="C1150" s="4"/>
+    </row>
+    <row r="1151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1151" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B1151" s="3"/>
+      <c r="C1151" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1152" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1152" s="3"/>
+      <c r="C1152" s="4"/>
+    </row>
+    <row r="1153" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1153" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1153" s="3"/>
+      <c r="C1153" s="4"/>
+    </row>
+    <row r="1154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1154" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B1154" s="3"/>
+      <c r="C1154" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1155" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1155" s="3"/>
+      <c r="C1155" s="4"/>
+    </row>
+    <row r="1156" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1156" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B1156" s="3"/>
+      <c r="C1156" s="4"/>
+    </row>
+    <row r="1157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1157" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B1157" s="3"/>
+      <c r="C1157" s="4">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1158" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B1158" s="3"/>
+      <c r="C1158" s="4"/>
+    </row>
+    <row r="1159" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1159" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="B1159" s="3"/>
+      <c r="C1159" s="4"/>
+    </row>
+    <row r="1160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1160" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="B1160" s="3"/>
+      <c r="C1160" s="4">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1161" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B1161" s="3"/>
+      <c r="C1161" s="4"/>
+    </row>
+    <row r="1162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1162" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B1162" s="3"/>
+      <c r="C1162" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1163" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1163" s="3"/>
+      <c r="C1163" s="4"/>
+    </row>
+    <row r="1164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1164" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B1164" s="3"/>
+      <c r="C1164" s="4">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1165" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="B1165" s="3"/>
+      <c r="C1165" s="4"/>
+    </row>
+    <row r="1166" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1166" s="2" t="s">
+        <v>968</v>
+      </c>
+      <c r="B1166" s="3"/>
+      <c r="C1166" s="4"/>
+    </row>
+    <row r="1167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1167" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B1167" s="3"/>
+      <c r="C1167" s="4">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1168" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="B1168" s="3"/>
+      <c r="C1168" s="4"/>
+    </row>
+    <row r="1169" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1169" s="2" t="s">
+        <v>971</v>
+      </c>
+      <c r="B1169" s="3"/>
+      <c r="C1169" s="4"/>
+    </row>
+    <row r="1170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1170" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B1170" s="3"/>
+      <c r="C1170" s="4">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1171" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B1171" s="3"/>
+      <c r="C1171" s="4"/>
+    </row>
+    <row r="1172" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1172" s="2" t="s">
+        <v>973</v>
+      </c>
+      <c r="B1172" s="3"/>
+      <c r="C1172" s="4"/>
+    </row>
+    <row r="1173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1173" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B1173" s="3"/>
+      <c r="C1173" s="4">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1174" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="B1174" s="3"/>
+      <c r="C1174" s="4"/>
+    </row>
+    <row r="1175" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1175" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="B1175" s="3"/>
+      <c r="C1175" s="4"/>
+    </row>
+    <row r="1176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1176" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B1176" s="3"/>
+      <c r="C1176" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1177" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B1177" s="3"/>
+      <c r="C1177" s="4"/>
+    </row>
+    <row r="1178" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1178" s="2" t="s">
+        <v>977</v>
+      </c>
+      <c r="B1178" s="3"/>
+      <c r="C1178" s="4"/>
+    </row>
+    <row r="1179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1179" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B1179" s="3"/>
+      <c r="C1179" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1180" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B1180" s="3"/>
+      <c r="C1180" s="4"/>
+    </row>
+    <row r="1181" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1181" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="B1181" s="3"/>
+      <c r="C1181" s="4"/>
+    </row>
+    <row r="1182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1182" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B1182" s="3"/>
+      <c r="C1182" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1183" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="B1183" s="3"/>
+      <c r="C1183" s="4"/>
+    </row>
+    <row r="1184" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1184" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="B1184" s="3"/>
+      <c r="C1184" s="4"/>
+    </row>
+    <row r="1185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1185" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B1185" s="3"/>
+      <c r="C1185" s="4">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1186" s="2" t="s">
+        <v>984</v>
+      </c>
+      <c r="B1186" s="3"/>
+      <c r="C1186" s="4"/>
+    </row>
+    <row r="1187" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1187" s="2" t="s">
+        <v>985</v>
+      </c>
+      <c r="B1187" s="3"/>
+      <c r="C1187" s="4"/>
+    </row>
+    <row r="1188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1188" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B1188" s="3"/>
+      <c r="C1188" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1189" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="B1189" s="3"/>
+      <c r="C1189" s="4"/>
+    </row>
+    <row r="1190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1190" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B1190" s="3"/>
+      <c r="C1190" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1191" s="2" t="s">
+        <v>988</v>
+      </c>
+      <c r="B1191" s="3"/>
+      <c r="C1191" s="4"/>
+    </row>
+    <row r="1192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1192" s="1" t="s">
+        <v>989</v>
+      </c>
+      <c r="B1192" s="3"/>
+      <c r="C1192" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1193" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1193" s="3"/>
+      <c r="C1193" s="4"/>
+    </row>
+    <row r="1194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1194" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B1194" s="3"/>
+      <c r="C1194" s="4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1195" s="2" t="s">
+        <v>990</v>
+      </c>
+      <c r="B1195" s="3"/>
+      <c r="C1195" s="4"/>
+    </row>
+    <row r="1196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1196" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B1196" s="3"/>
+      <c r="C1196" s="4">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1197" s="2" t="s">
+        <v>993</v>
+      </c>
+      <c r="B1197" s="3"/>
+      <c r="C1197" s="4"/>
+    </row>
+    <row r="1198" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1198" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B1198" s="3"/>
+      <c r="C1198" s="4"/>
+    </row>
+    <row r="1199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1199" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B1199" s="3"/>
+      <c r="C1199" s="4">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1200" s="2" t="s">
+        <v>996</v>
+      </c>
+      <c r="B1200" s="3"/>
+      <c r="C1200" s="4"/>
+    </row>
+    <row r="1201" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1201" s="2" t="s">
+        <v>997</v>
+      </c>
+      <c r="B1201" s="3"/>
+      <c r="C1201" s="4"/>
+    </row>
+    <row r="1202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1202" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B1202" s="3"/>
+      <c r="C1202" s="4">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1203" s="2" t="s">
+        <v>999</v>
+      </c>
+      <c r="B1203" s="3"/>
+      <c r="C1203" s="4"/>
+    </row>
+    <row r="1204" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1204" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B1204" s="3"/>
+      <c r="C1204" s="4"/>
+    </row>
+    <row r="1205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1205" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B1205" s="3"/>
+      <c r="C1205" s="4">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1206" s="2" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B1206" s="3"/>
+      <c r="C1206" s="4"/>
+    </row>
+    <row r="1207" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1207" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B1207" s="3"/>
+      <c r="C1207" s="4"/>
+    </row>
+    <row r="1208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1208" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B1208" s="3"/>
+      <c r="C1208" s="4">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1209" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B1209" s="3"/>
+      <c r="C1209" s="4"/>
+    </row>
+    <row r="1210" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1210" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B1210" s="3"/>
+      <c r="C1210" s="4"/>
+    </row>
+    <row r="1211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1211" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B1211" s="3"/>
+      <c r="C1211" s="4">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1212" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B1212" s="3"/>
+      <c r="C1212" s="4"/>
+    </row>
+    <row r="1213" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1213" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B1213" s="3"/>
+      <c r="C1213" s="4"/>
+    </row>
+    <row r="1214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1214" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B1214" s="3"/>
+      <c r="C1214" s="4">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1215" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B1215" s="3"/>
+      <c r="C1215" s="4"/>
+    </row>
+    <row r="1216" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1216" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B1216" s="3"/>
+      <c r="C1216" s="4"/>
+    </row>
+    <row r="1217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1217" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B1217" s="3"/>
+      <c r="C1217" s="4">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1218" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B1218" s="3"/>
+      <c r="C1218" s="4"/>
+    </row>
+    <row r="1219" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1219" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B1219" s="3"/>
+      <c r="C1219" s="4"/>
+    </row>
+    <row r="1220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1220" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="B1220" s="3"/>
+      <c r="C1220" s="4">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1221" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="B1221" s="3"/>
+      <c r="C1221" s="4"/>
+    </row>
+    <row r="1222" spans="1:3" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1222" s="2" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B1222" s="3"/>
+      <c r="C1222" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="478">
-    <mergeCell ref="B699:B701"/>
-    <mergeCell ref="C699:C701"/>
-    <mergeCell ref="B702:B704"/>
-    <mergeCell ref="C702:C704"/>
-    <mergeCell ref="B705:B707"/>
-    <mergeCell ref="C705:C707"/>
-    <mergeCell ref="B708:B709"/>
-    <mergeCell ref="C708:C709"/>
-    <mergeCell ref="B684:B686"/>
-    <mergeCell ref="C684:C686"/>
-    <mergeCell ref="B687:B689"/>
-    <mergeCell ref="C687:C689"/>
-    <mergeCell ref="B690:B692"/>
-    <mergeCell ref="C690:C692"/>
-    <mergeCell ref="B693:B695"/>
-    <mergeCell ref="C693:C695"/>
-    <mergeCell ref="B696:B698"/>
-    <mergeCell ref="C696:C698"/>
-    <mergeCell ref="B670:B672"/>
-    <mergeCell ref="C670:C672"/>
-    <mergeCell ref="B673:B675"/>
-    <mergeCell ref="C673:C675"/>
-    <mergeCell ref="B676:B678"/>
-    <mergeCell ref="C676:C678"/>
-    <mergeCell ref="B679:B680"/>
-    <mergeCell ref="C679:C680"/>
-    <mergeCell ref="B681:B683"/>
-    <mergeCell ref="C681:C683"/>
-    <mergeCell ref="B655:B657"/>
-    <mergeCell ref="C655:C657"/>
-    <mergeCell ref="B658:B660"/>
-    <mergeCell ref="C658:C660"/>
-    <mergeCell ref="B661:B663"/>
-    <mergeCell ref="C661:C663"/>
-    <mergeCell ref="B664:B666"/>
-    <mergeCell ref="C664:C666"/>
-    <mergeCell ref="B667:B669"/>
-    <mergeCell ref="C667:C669"/>
-    <mergeCell ref="B640:B642"/>
-    <mergeCell ref="C640:C642"/>
-    <mergeCell ref="B643:B645"/>
-    <mergeCell ref="C643:C645"/>
-    <mergeCell ref="B646:B648"/>
-    <mergeCell ref="C646:C648"/>
-    <mergeCell ref="B649:B651"/>
-    <mergeCell ref="C649:C651"/>
-    <mergeCell ref="B652:B654"/>
-    <mergeCell ref="C652:C654"/>
-    <mergeCell ref="B625:B627"/>
-    <mergeCell ref="C625:C627"/>
-    <mergeCell ref="B628:B630"/>
-    <mergeCell ref="C628:C630"/>
-    <mergeCell ref="B631:B633"/>
-    <mergeCell ref="C631:C633"/>
-    <mergeCell ref="B634:B636"/>
-    <mergeCell ref="C634:C636"/>
-    <mergeCell ref="B637:B639"/>
-    <mergeCell ref="C637:C639"/>
-    <mergeCell ref="B610:B612"/>
-    <mergeCell ref="C610:C612"/>
-    <mergeCell ref="B613:B615"/>
-    <mergeCell ref="C613:C615"/>
-    <mergeCell ref="B616:B618"/>
-    <mergeCell ref="C616:C618"/>
-    <mergeCell ref="B619:B621"/>
-    <mergeCell ref="C619:C621"/>
-    <mergeCell ref="B622:B624"/>
-    <mergeCell ref="C622:C624"/>
-    <mergeCell ref="B597:B599"/>
-    <mergeCell ref="C597:C599"/>
-    <mergeCell ref="B600:B601"/>
-    <mergeCell ref="C600:C601"/>
-    <mergeCell ref="B602:B604"/>
-    <mergeCell ref="C602:C604"/>
-    <mergeCell ref="B605:B607"/>
-    <mergeCell ref="C605:C607"/>
-    <mergeCell ref="B608:B609"/>
-    <mergeCell ref="C608:C609"/>
-    <mergeCell ref="B582:B584"/>
-    <mergeCell ref="C582:C584"/>
-    <mergeCell ref="B585:B587"/>
-    <mergeCell ref="C585:C587"/>
-    <mergeCell ref="B588:B590"/>
-    <mergeCell ref="C588:C590"/>
-    <mergeCell ref="B591:B593"/>
-    <mergeCell ref="C591:C593"/>
-    <mergeCell ref="B594:B596"/>
-    <mergeCell ref="C594:C596"/>
-    <mergeCell ref="B567:B569"/>
-    <mergeCell ref="C567:C569"/>
-    <mergeCell ref="B570:B572"/>
-    <mergeCell ref="C570:C572"/>
-    <mergeCell ref="B573:B575"/>
-    <mergeCell ref="C573:C575"/>
-    <mergeCell ref="B576:B578"/>
-    <mergeCell ref="C576:C578"/>
-    <mergeCell ref="B579:B581"/>
-    <mergeCell ref="C579:C581"/>
+  <mergeCells count="838">
+    <mergeCell ref="B556:B557"/>
+    <mergeCell ref="C556:C557"/>
+    <mergeCell ref="B558:B560"/>
+    <mergeCell ref="C558:C560"/>
+    <mergeCell ref="B548:B550"/>
+    <mergeCell ref="C548:C550"/>
+    <mergeCell ref="B551:B552"/>
+    <mergeCell ref="C551:C552"/>
+    <mergeCell ref="B553:B555"/>
+    <mergeCell ref="C553:C555"/>
+    <mergeCell ref="B539:B541"/>
+    <mergeCell ref="C539:C541"/>
+    <mergeCell ref="B542:B544"/>
+    <mergeCell ref="C542:C544"/>
+    <mergeCell ref="B545:B547"/>
+    <mergeCell ref="C545:C547"/>
+    <mergeCell ref="B530:B532"/>
+    <mergeCell ref="C530:C532"/>
+    <mergeCell ref="B533:B535"/>
+    <mergeCell ref="C533:C535"/>
+    <mergeCell ref="B536:B538"/>
+    <mergeCell ref="C536:C538"/>
+    <mergeCell ref="B521:B523"/>
+    <mergeCell ref="C521:C523"/>
+    <mergeCell ref="B524:B526"/>
+    <mergeCell ref="C524:C526"/>
+    <mergeCell ref="B527:B529"/>
+    <mergeCell ref="C527:C529"/>
+    <mergeCell ref="B512:B514"/>
+    <mergeCell ref="C512:C514"/>
+    <mergeCell ref="B515:B517"/>
+    <mergeCell ref="C515:C517"/>
+    <mergeCell ref="B518:B520"/>
+    <mergeCell ref="C518:C520"/>
+    <mergeCell ref="B503:B505"/>
+    <mergeCell ref="C503:C505"/>
+    <mergeCell ref="B506:B508"/>
+    <mergeCell ref="C506:C508"/>
+    <mergeCell ref="B509:B511"/>
+    <mergeCell ref="C509:C511"/>
+    <mergeCell ref="B494:B496"/>
+    <mergeCell ref="C494:C496"/>
+    <mergeCell ref="B497:B499"/>
+    <mergeCell ref="C497:C499"/>
+    <mergeCell ref="B500:B502"/>
+    <mergeCell ref="C500:C502"/>
+    <mergeCell ref="B485:B487"/>
+    <mergeCell ref="C485:C487"/>
+    <mergeCell ref="B488:B490"/>
+    <mergeCell ref="C488:C490"/>
+    <mergeCell ref="B491:B493"/>
+    <mergeCell ref="C491:C493"/>
+    <mergeCell ref="B477:B479"/>
+    <mergeCell ref="C477:C479"/>
+    <mergeCell ref="B480:B482"/>
+    <mergeCell ref="C480:C482"/>
+    <mergeCell ref="B483:B484"/>
+    <mergeCell ref="C483:C484"/>
+    <mergeCell ref="B468:B470"/>
+    <mergeCell ref="C468:C470"/>
+    <mergeCell ref="B471:B473"/>
+    <mergeCell ref="C471:C473"/>
+    <mergeCell ref="B474:B476"/>
+    <mergeCell ref="C474:C476"/>
+    <mergeCell ref="B459:B461"/>
+    <mergeCell ref="C459:C461"/>
+    <mergeCell ref="B462:B464"/>
+    <mergeCell ref="C462:C464"/>
+    <mergeCell ref="B465:B467"/>
+    <mergeCell ref="C465:C467"/>
+    <mergeCell ref="B450:B452"/>
+    <mergeCell ref="C450:C452"/>
+    <mergeCell ref="B453:B455"/>
+    <mergeCell ref="C453:C455"/>
+    <mergeCell ref="B456:B458"/>
+    <mergeCell ref="C456:C458"/>
+    <mergeCell ref="B442:B444"/>
+    <mergeCell ref="C442:C444"/>
+    <mergeCell ref="B445:B447"/>
+    <mergeCell ref="C445:C447"/>
+    <mergeCell ref="B448:B449"/>
+    <mergeCell ref="C448:C449"/>
+    <mergeCell ref="B433:B435"/>
+    <mergeCell ref="C433:C435"/>
+    <mergeCell ref="B436:B438"/>
+    <mergeCell ref="C436:C438"/>
+    <mergeCell ref="B439:B441"/>
+    <mergeCell ref="C439:C441"/>
+    <mergeCell ref="B424:B426"/>
+    <mergeCell ref="C424:C426"/>
+    <mergeCell ref="B427:B429"/>
+    <mergeCell ref="C427:C429"/>
+    <mergeCell ref="B430:B432"/>
+    <mergeCell ref="C430:C432"/>
+    <mergeCell ref="B415:B417"/>
+    <mergeCell ref="C415:C417"/>
+    <mergeCell ref="B418:B420"/>
+    <mergeCell ref="C418:C420"/>
+    <mergeCell ref="B421:B423"/>
+    <mergeCell ref="C421:C423"/>
+    <mergeCell ref="B406:B408"/>
+    <mergeCell ref="C406:C408"/>
+    <mergeCell ref="B409:B411"/>
+    <mergeCell ref="C409:C411"/>
+    <mergeCell ref="B412:B414"/>
+    <mergeCell ref="C412:C414"/>
+    <mergeCell ref="B397:B399"/>
+    <mergeCell ref="C397:C399"/>
+    <mergeCell ref="B400:B402"/>
+    <mergeCell ref="C400:C402"/>
+    <mergeCell ref="B403:B405"/>
+    <mergeCell ref="C403:C405"/>
+    <mergeCell ref="B388:B390"/>
+    <mergeCell ref="C388:C390"/>
+    <mergeCell ref="B391:B393"/>
+    <mergeCell ref="C391:C393"/>
+    <mergeCell ref="B394:B396"/>
+    <mergeCell ref="C394:C396"/>
+    <mergeCell ref="B379:B381"/>
+    <mergeCell ref="C379:C381"/>
+    <mergeCell ref="B382:B384"/>
+    <mergeCell ref="C382:C384"/>
+    <mergeCell ref="B385:B387"/>
+    <mergeCell ref="C385:C387"/>
+    <mergeCell ref="B370:B372"/>
+    <mergeCell ref="C370:C372"/>
+    <mergeCell ref="B373:B375"/>
+    <mergeCell ref="C373:C375"/>
+    <mergeCell ref="B376:B378"/>
+    <mergeCell ref="C376:C378"/>
+    <mergeCell ref="B361:B363"/>
+    <mergeCell ref="C361:C363"/>
+    <mergeCell ref="B364:B366"/>
+    <mergeCell ref="C364:C366"/>
+    <mergeCell ref="B367:B369"/>
+    <mergeCell ref="C367:C369"/>
+    <mergeCell ref="B352:B354"/>
+    <mergeCell ref="C352:C354"/>
+    <mergeCell ref="B355:B357"/>
+    <mergeCell ref="C355:C357"/>
+    <mergeCell ref="B358:B360"/>
+    <mergeCell ref="C358:C360"/>
+    <mergeCell ref="B343:B345"/>
+    <mergeCell ref="C343:C345"/>
+    <mergeCell ref="B346:B348"/>
+    <mergeCell ref="C346:C348"/>
+    <mergeCell ref="B349:B351"/>
+    <mergeCell ref="C349:C351"/>
+    <mergeCell ref="B334:B336"/>
+    <mergeCell ref="C334:C336"/>
+    <mergeCell ref="B337:B339"/>
+    <mergeCell ref="C337:C339"/>
+    <mergeCell ref="B340:B342"/>
+    <mergeCell ref="C340:C342"/>
+    <mergeCell ref="B325:B327"/>
+    <mergeCell ref="C325:C327"/>
+    <mergeCell ref="B328:B330"/>
+    <mergeCell ref="C328:C330"/>
+    <mergeCell ref="B331:B333"/>
+    <mergeCell ref="C331:C333"/>
+    <mergeCell ref="B316:B318"/>
+    <mergeCell ref="C316:C318"/>
+    <mergeCell ref="B319:B321"/>
+    <mergeCell ref="C319:C321"/>
+    <mergeCell ref="B322:B324"/>
+    <mergeCell ref="C322:C324"/>
+    <mergeCell ref="B307:B309"/>
+    <mergeCell ref="C307:C309"/>
+    <mergeCell ref="B310:B312"/>
+    <mergeCell ref="C310:C312"/>
+    <mergeCell ref="B313:B315"/>
+    <mergeCell ref="C313:C315"/>
+    <mergeCell ref="B298:B300"/>
+    <mergeCell ref="C298:C300"/>
+    <mergeCell ref="B301:B303"/>
+    <mergeCell ref="C301:C303"/>
+    <mergeCell ref="B304:B306"/>
+    <mergeCell ref="C304:C306"/>
+    <mergeCell ref="B289:B291"/>
+    <mergeCell ref="C289:C291"/>
+    <mergeCell ref="B292:B294"/>
+    <mergeCell ref="C292:C294"/>
+    <mergeCell ref="B295:B297"/>
+    <mergeCell ref="C295:C297"/>
+    <mergeCell ref="B280:B282"/>
+    <mergeCell ref="C280:C282"/>
+    <mergeCell ref="B283:B285"/>
+    <mergeCell ref="C283:C285"/>
+    <mergeCell ref="B286:B288"/>
+    <mergeCell ref="C286:C288"/>
+    <mergeCell ref="B271:B273"/>
+    <mergeCell ref="C271:C273"/>
+    <mergeCell ref="B274:B276"/>
+    <mergeCell ref="C274:C276"/>
+    <mergeCell ref="B277:B279"/>
+    <mergeCell ref="C277:C279"/>
+    <mergeCell ref="B262:B264"/>
+    <mergeCell ref="C262:C264"/>
+    <mergeCell ref="B265:B267"/>
+    <mergeCell ref="C265:C267"/>
+    <mergeCell ref="B268:B270"/>
+    <mergeCell ref="C268:C270"/>
+    <mergeCell ref="B253:B255"/>
+    <mergeCell ref="C253:C255"/>
+    <mergeCell ref="B256:B258"/>
+    <mergeCell ref="C256:C258"/>
+    <mergeCell ref="B259:B261"/>
+    <mergeCell ref="C259:C261"/>
+    <mergeCell ref="B244:B246"/>
+    <mergeCell ref="C244:C246"/>
+    <mergeCell ref="B247:B249"/>
+    <mergeCell ref="C247:C249"/>
+    <mergeCell ref="B250:B252"/>
+    <mergeCell ref="C250:C252"/>
+    <mergeCell ref="B235:B237"/>
+    <mergeCell ref="C235:C237"/>
+    <mergeCell ref="B238:B240"/>
+    <mergeCell ref="C238:C240"/>
+    <mergeCell ref="B241:B243"/>
+    <mergeCell ref="C241:C243"/>
+    <mergeCell ref="B226:B228"/>
+    <mergeCell ref="C226:C228"/>
+    <mergeCell ref="B229:B231"/>
+    <mergeCell ref="C229:C231"/>
+    <mergeCell ref="B232:B234"/>
+    <mergeCell ref="C232:C234"/>
+    <mergeCell ref="B217:B219"/>
+    <mergeCell ref="C217:C219"/>
+    <mergeCell ref="B220:B222"/>
+    <mergeCell ref="C220:C222"/>
+    <mergeCell ref="B223:B225"/>
+    <mergeCell ref="C223:C225"/>
+    <mergeCell ref="B208:B210"/>
+    <mergeCell ref="C208:C210"/>
+    <mergeCell ref="B211:B213"/>
+    <mergeCell ref="C211:C213"/>
+    <mergeCell ref="B214:B216"/>
+    <mergeCell ref="C214:C216"/>
+    <mergeCell ref="B199:B201"/>
+    <mergeCell ref="C199:C201"/>
+    <mergeCell ref="B202:B204"/>
+    <mergeCell ref="C202:C204"/>
+    <mergeCell ref="B205:B207"/>
+    <mergeCell ref="C205:C207"/>
+    <mergeCell ref="B190:B192"/>
+    <mergeCell ref="C190:C192"/>
+    <mergeCell ref="B193:B195"/>
+    <mergeCell ref="C193:C195"/>
+    <mergeCell ref="B196:B198"/>
+    <mergeCell ref="C196:C198"/>
+    <mergeCell ref="B181:B183"/>
+    <mergeCell ref="C181:C183"/>
+    <mergeCell ref="B184:B186"/>
+    <mergeCell ref="C184:C186"/>
+    <mergeCell ref="B187:B189"/>
+    <mergeCell ref="C187:C189"/>
+    <mergeCell ref="B172:B174"/>
+    <mergeCell ref="C172:C174"/>
+    <mergeCell ref="B175:B177"/>
+    <mergeCell ref="C175:C177"/>
+    <mergeCell ref="B178:B180"/>
+    <mergeCell ref="C178:C180"/>
+    <mergeCell ref="B163:B165"/>
+    <mergeCell ref="C163:C165"/>
+    <mergeCell ref="B166:B168"/>
+    <mergeCell ref="C166:C168"/>
+    <mergeCell ref="B169:B171"/>
+    <mergeCell ref="C169:C171"/>
+    <mergeCell ref="B154:B156"/>
+    <mergeCell ref="C154:C156"/>
+    <mergeCell ref="B157:B159"/>
+    <mergeCell ref="C157:C159"/>
+    <mergeCell ref="B160:B162"/>
+    <mergeCell ref="C160:C162"/>
+    <mergeCell ref="B145:B147"/>
+    <mergeCell ref="C145:C147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="C148:C150"/>
+    <mergeCell ref="B151:B153"/>
+    <mergeCell ref="C151:C153"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="C136:C138"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="C139:C141"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="C142:C144"/>
+    <mergeCell ref="B127:B129"/>
+    <mergeCell ref="C127:C129"/>
+    <mergeCell ref="B130:B132"/>
+    <mergeCell ref="C130:C132"/>
+    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="C133:C135"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="C118:C120"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="C121:C123"/>
+    <mergeCell ref="B124:B126"/>
+    <mergeCell ref="C124:C126"/>
+    <mergeCell ref="B109:B111"/>
+    <mergeCell ref="C109:C111"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="C112:C114"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="C115:C117"/>
+    <mergeCell ref="B100:B102"/>
+    <mergeCell ref="C100:C102"/>
+    <mergeCell ref="B103:B105"/>
+    <mergeCell ref="C103:C105"/>
+    <mergeCell ref="B106:B108"/>
+    <mergeCell ref="C106:C108"/>
+    <mergeCell ref="B91:B93"/>
+    <mergeCell ref="C91:C93"/>
+    <mergeCell ref="B94:B96"/>
+    <mergeCell ref="C94:C96"/>
+    <mergeCell ref="B97:B99"/>
+    <mergeCell ref="C97:C99"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="C82:C84"/>
+    <mergeCell ref="B85:B87"/>
+    <mergeCell ref="C85:C87"/>
+    <mergeCell ref="B88:B90"/>
+    <mergeCell ref="C88:C90"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="B76:B78"/>
+    <mergeCell ref="C76:C78"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="C79:C81"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="C67:C69"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="C70:C72"/>
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="C55:C57"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B52:B54"/>
+    <mergeCell ref="C52:C54"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="B31:B33"/>
+    <mergeCell ref="C31:C33"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="C34:C36"/>
     <mergeCell ref="B1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="B4:B6"/>
@@ -8369,836 +13981,828 @@
     <mergeCell ref="C16:C18"/>
     <mergeCell ref="B37:B39"/>
     <mergeCell ref="C37:C39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="B43:B45"/>
-    <mergeCell ref="C43:C45"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="B31:B33"/>
-    <mergeCell ref="C31:C33"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="C55:C57"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="C61:C63"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="C52:C54"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="B76:B78"/>
-    <mergeCell ref="C76:C78"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="C79:C81"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="C67:C69"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="C70:C72"/>
-    <mergeCell ref="B91:B93"/>
-    <mergeCell ref="C91:C93"/>
-    <mergeCell ref="B94:B96"/>
-    <mergeCell ref="C94:C96"/>
-    <mergeCell ref="B97:B99"/>
-    <mergeCell ref="C97:C99"/>
-    <mergeCell ref="B82:B84"/>
-    <mergeCell ref="C82:C84"/>
-    <mergeCell ref="B85:B87"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="B88:B90"/>
-    <mergeCell ref="C88:C90"/>
-    <mergeCell ref="B109:B111"/>
-    <mergeCell ref="C109:C111"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="C112:C114"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="C115:C117"/>
-    <mergeCell ref="B100:B102"/>
-    <mergeCell ref="C100:C102"/>
-    <mergeCell ref="B103:B105"/>
-    <mergeCell ref="C103:C105"/>
-    <mergeCell ref="B106:B108"/>
-    <mergeCell ref="C106:C108"/>
-    <mergeCell ref="B127:B129"/>
-    <mergeCell ref="C127:C129"/>
-    <mergeCell ref="B130:B132"/>
-    <mergeCell ref="C130:C132"/>
-    <mergeCell ref="B133:B135"/>
-    <mergeCell ref="C133:C135"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="C118:C120"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="C121:C123"/>
-    <mergeCell ref="B124:B126"/>
-    <mergeCell ref="C124:C126"/>
-    <mergeCell ref="B145:B147"/>
-    <mergeCell ref="C145:C147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="C148:C150"/>
-    <mergeCell ref="B151:B153"/>
-    <mergeCell ref="C151:C153"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="C136:C138"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="C139:C141"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="C142:C144"/>
-    <mergeCell ref="B163:B165"/>
-    <mergeCell ref="C163:C165"/>
-    <mergeCell ref="B166:B168"/>
-    <mergeCell ref="C166:C168"/>
-    <mergeCell ref="B169:B171"/>
-    <mergeCell ref="C169:C171"/>
-    <mergeCell ref="B154:B156"/>
-    <mergeCell ref="C154:C156"/>
-    <mergeCell ref="B157:B159"/>
-    <mergeCell ref="C157:C159"/>
-    <mergeCell ref="B160:B162"/>
-    <mergeCell ref="C160:C162"/>
-    <mergeCell ref="B181:B183"/>
-    <mergeCell ref="C181:C183"/>
-    <mergeCell ref="B184:B186"/>
-    <mergeCell ref="C184:C186"/>
-    <mergeCell ref="B187:B189"/>
-    <mergeCell ref="C187:C189"/>
-    <mergeCell ref="B172:B174"/>
-    <mergeCell ref="C172:C174"/>
-    <mergeCell ref="B175:B177"/>
-    <mergeCell ref="C175:C177"/>
-    <mergeCell ref="B178:B180"/>
-    <mergeCell ref="C178:C180"/>
-    <mergeCell ref="B199:B201"/>
-    <mergeCell ref="C199:C201"/>
-    <mergeCell ref="B202:B204"/>
-    <mergeCell ref="C202:C204"/>
-    <mergeCell ref="B205:B207"/>
-    <mergeCell ref="C205:C207"/>
-    <mergeCell ref="B190:B192"/>
-    <mergeCell ref="C190:C192"/>
-    <mergeCell ref="B193:B195"/>
-    <mergeCell ref="C193:C195"/>
-    <mergeCell ref="B196:B198"/>
-    <mergeCell ref="C196:C198"/>
-    <mergeCell ref="B217:B219"/>
-    <mergeCell ref="C217:C219"/>
-    <mergeCell ref="B220:B222"/>
-    <mergeCell ref="C220:C222"/>
-    <mergeCell ref="B223:B225"/>
-    <mergeCell ref="C223:C225"/>
-    <mergeCell ref="B208:B210"/>
-    <mergeCell ref="C208:C210"/>
-    <mergeCell ref="B211:B213"/>
-    <mergeCell ref="C211:C213"/>
-    <mergeCell ref="B214:B216"/>
-    <mergeCell ref="C214:C216"/>
-    <mergeCell ref="B235:B237"/>
-    <mergeCell ref="C235:C237"/>
-    <mergeCell ref="B238:B240"/>
-    <mergeCell ref="C238:C240"/>
-    <mergeCell ref="B241:B243"/>
-    <mergeCell ref="C241:C243"/>
-    <mergeCell ref="B226:B228"/>
-    <mergeCell ref="C226:C228"/>
-    <mergeCell ref="B229:B231"/>
-    <mergeCell ref="C229:C231"/>
-    <mergeCell ref="B232:B234"/>
-    <mergeCell ref="C232:C234"/>
-    <mergeCell ref="B253:B255"/>
-    <mergeCell ref="C253:C255"/>
-    <mergeCell ref="B256:B258"/>
-    <mergeCell ref="C256:C258"/>
-    <mergeCell ref="B259:B261"/>
-    <mergeCell ref="C259:C261"/>
-    <mergeCell ref="B244:B246"/>
-    <mergeCell ref="C244:C246"/>
-    <mergeCell ref="B247:B249"/>
-    <mergeCell ref="C247:C249"/>
-    <mergeCell ref="B250:B252"/>
-    <mergeCell ref="C250:C252"/>
-    <mergeCell ref="B271:B273"/>
-    <mergeCell ref="C271:C273"/>
-    <mergeCell ref="B274:B276"/>
-    <mergeCell ref="C274:C276"/>
-    <mergeCell ref="B277:B279"/>
-    <mergeCell ref="C277:C279"/>
-    <mergeCell ref="B262:B264"/>
-    <mergeCell ref="C262:C264"/>
-    <mergeCell ref="B265:B267"/>
-    <mergeCell ref="C265:C267"/>
-    <mergeCell ref="B268:B270"/>
-    <mergeCell ref="C268:C270"/>
-    <mergeCell ref="B289:B291"/>
-    <mergeCell ref="C289:C291"/>
-    <mergeCell ref="B292:B294"/>
-    <mergeCell ref="C292:C294"/>
-    <mergeCell ref="B295:B297"/>
-    <mergeCell ref="C295:C297"/>
-    <mergeCell ref="B280:B282"/>
-    <mergeCell ref="C280:C282"/>
-    <mergeCell ref="B283:B285"/>
-    <mergeCell ref="C283:C285"/>
-    <mergeCell ref="B286:B288"/>
-    <mergeCell ref="C286:C288"/>
-    <mergeCell ref="B307:B309"/>
-    <mergeCell ref="C307:C309"/>
-    <mergeCell ref="B310:B312"/>
-    <mergeCell ref="C310:C312"/>
-    <mergeCell ref="B313:B315"/>
-    <mergeCell ref="C313:C315"/>
-    <mergeCell ref="B298:B300"/>
-    <mergeCell ref="C298:C300"/>
-    <mergeCell ref="B301:B303"/>
-    <mergeCell ref="C301:C303"/>
-    <mergeCell ref="B304:B306"/>
-    <mergeCell ref="C304:C306"/>
-    <mergeCell ref="B325:B327"/>
-    <mergeCell ref="C325:C327"/>
-    <mergeCell ref="B328:B330"/>
-    <mergeCell ref="C328:C330"/>
-    <mergeCell ref="B331:B333"/>
-    <mergeCell ref="C331:C333"/>
-    <mergeCell ref="B316:B318"/>
-    <mergeCell ref="C316:C318"/>
-    <mergeCell ref="B319:B321"/>
-    <mergeCell ref="C319:C321"/>
-    <mergeCell ref="B322:B324"/>
-    <mergeCell ref="C322:C324"/>
-    <mergeCell ref="B343:B345"/>
-    <mergeCell ref="C343:C345"/>
-    <mergeCell ref="B346:B348"/>
-    <mergeCell ref="C346:C348"/>
-    <mergeCell ref="B349:B351"/>
-    <mergeCell ref="C349:C351"/>
-    <mergeCell ref="B334:B336"/>
-    <mergeCell ref="C334:C336"/>
-    <mergeCell ref="B337:B339"/>
-    <mergeCell ref="C337:C339"/>
-    <mergeCell ref="B340:B342"/>
-    <mergeCell ref="C340:C342"/>
-    <mergeCell ref="B361:B363"/>
-    <mergeCell ref="C361:C363"/>
-    <mergeCell ref="B364:B366"/>
-    <mergeCell ref="C364:C366"/>
-    <mergeCell ref="B367:B369"/>
-    <mergeCell ref="C367:C369"/>
-    <mergeCell ref="B352:B354"/>
-    <mergeCell ref="C352:C354"/>
-    <mergeCell ref="B355:B357"/>
-    <mergeCell ref="C355:C357"/>
-    <mergeCell ref="B358:B360"/>
-    <mergeCell ref="C358:C360"/>
-    <mergeCell ref="B379:B381"/>
-    <mergeCell ref="C379:C381"/>
-    <mergeCell ref="B382:B384"/>
-    <mergeCell ref="C382:C384"/>
-    <mergeCell ref="B385:B387"/>
-    <mergeCell ref="C385:C387"/>
-    <mergeCell ref="B370:B372"/>
-    <mergeCell ref="C370:C372"/>
-    <mergeCell ref="B373:B375"/>
-    <mergeCell ref="C373:C375"/>
-    <mergeCell ref="B376:B378"/>
-    <mergeCell ref="C376:C378"/>
-    <mergeCell ref="B397:B399"/>
-    <mergeCell ref="C397:C399"/>
-    <mergeCell ref="B400:B402"/>
-    <mergeCell ref="C400:C402"/>
-    <mergeCell ref="B403:B405"/>
-    <mergeCell ref="C403:C405"/>
-    <mergeCell ref="B388:B390"/>
-    <mergeCell ref="C388:C390"/>
-    <mergeCell ref="B391:B393"/>
-    <mergeCell ref="C391:C393"/>
-    <mergeCell ref="B394:B396"/>
-    <mergeCell ref="C394:C396"/>
-    <mergeCell ref="B415:B417"/>
-    <mergeCell ref="C415:C417"/>
-    <mergeCell ref="B418:B420"/>
-    <mergeCell ref="C418:C420"/>
-    <mergeCell ref="B421:B423"/>
-    <mergeCell ref="C421:C423"/>
-    <mergeCell ref="B406:B408"/>
-    <mergeCell ref="C406:C408"/>
-    <mergeCell ref="B409:B411"/>
-    <mergeCell ref="C409:C411"/>
-    <mergeCell ref="B412:B414"/>
-    <mergeCell ref="C412:C414"/>
-    <mergeCell ref="B433:B435"/>
-    <mergeCell ref="C433:C435"/>
-    <mergeCell ref="B436:B438"/>
-    <mergeCell ref="C436:C438"/>
-    <mergeCell ref="B439:B441"/>
-    <mergeCell ref="C439:C441"/>
-    <mergeCell ref="B424:B426"/>
-    <mergeCell ref="C424:C426"/>
-    <mergeCell ref="B427:B429"/>
-    <mergeCell ref="C427:C429"/>
-    <mergeCell ref="B430:B432"/>
-    <mergeCell ref="C430:C432"/>
-    <mergeCell ref="B450:B452"/>
-    <mergeCell ref="C450:C452"/>
-    <mergeCell ref="B453:B455"/>
-    <mergeCell ref="C453:C455"/>
-    <mergeCell ref="B456:B458"/>
-    <mergeCell ref="C456:C458"/>
-    <mergeCell ref="B442:B444"/>
-    <mergeCell ref="C442:C444"/>
-    <mergeCell ref="B445:B447"/>
-    <mergeCell ref="C445:C447"/>
-    <mergeCell ref="B448:B449"/>
-    <mergeCell ref="C448:C449"/>
-    <mergeCell ref="B468:B470"/>
-    <mergeCell ref="C468:C470"/>
-    <mergeCell ref="B471:B473"/>
-    <mergeCell ref="C471:C473"/>
-    <mergeCell ref="B474:B476"/>
-    <mergeCell ref="C474:C476"/>
-    <mergeCell ref="B459:B461"/>
-    <mergeCell ref="C459:C461"/>
-    <mergeCell ref="B462:B464"/>
-    <mergeCell ref="C462:C464"/>
-    <mergeCell ref="B465:B467"/>
-    <mergeCell ref="C465:C467"/>
-    <mergeCell ref="B485:B487"/>
-    <mergeCell ref="C485:C487"/>
-    <mergeCell ref="B488:B490"/>
-    <mergeCell ref="C488:C490"/>
-    <mergeCell ref="B491:B493"/>
-    <mergeCell ref="C491:C493"/>
-    <mergeCell ref="B477:B479"/>
-    <mergeCell ref="C477:C479"/>
-    <mergeCell ref="B480:B482"/>
-    <mergeCell ref="C480:C482"/>
-    <mergeCell ref="B483:B484"/>
-    <mergeCell ref="C483:C484"/>
-    <mergeCell ref="B503:B505"/>
-    <mergeCell ref="C503:C505"/>
-    <mergeCell ref="B506:B508"/>
-    <mergeCell ref="C506:C508"/>
-    <mergeCell ref="B509:B511"/>
-    <mergeCell ref="C509:C511"/>
-    <mergeCell ref="B494:B496"/>
-    <mergeCell ref="C494:C496"/>
-    <mergeCell ref="B497:B499"/>
-    <mergeCell ref="C497:C499"/>
-    <mergeCell ref="B500:B502"/>
-    <mergeCell ref="C500:C502"/>
-    <mergeCell ref="B521:B523"/>
-    <mergeCell ref="C521:C523"/>
-    <mergeCell ref="B524:B526"/>
-    <mergeCell ref="C524:C526"/>
-    <mergeCell ref="B527:B529"/>
-    <mergeCell ref="C527:C529"/>
-    <mergeCell ref="B512:B514"/>
-    <mergeCell ref="C512:C514"/>
-    <mergeCell ref="B515:B517"/>
-    <mergeCell ref="C515:C517"/>
-    <mergeCell ref="B518:B520"/>
-    <mergeCell ref="C518:C520"/>
-    <mergeCell ref="B539:B541"/>
-    <mergeCell ref="C539:C541"/>
-    <mergeCell ref="B542:B544"/>
-    <mergeCell ref="C542:C544"/>
-    <mergeCell ref="B545:B547"/>
-    <mergeCell ref="C545:C547"/>
-    <mergeCell ref="B530:B532"/>
-    <mergeCell ref="C530:C532"/>
-    <mergeCell ref="B533:B535"/>
-    <mergeCell ref="C533:C535"/>
-    <mergeCell ref="B536:B538"/>
-    <mergeCell ref="C536:C538"/>
-    <mergeCell ref="B556:B557"/>
-    <mergeCell ref="C556:C557"/>
-    <mergeCell ref="B558:B560"/>
-    <mergeCell ref="C558:C560"/>
-    <mergeCell ref="B548:B550"/>
-    <mergeCell ref="C548:C550"/>
-    <mergeCell ref="B551:B552"/>
-    <mergeCell ref="C551:C552"/>
-    <mergeCell ref="B553:B555"/>
-    <mergeCell ref="C553:C555"/>
+    <mergeCell ref="B567:B569"/>
+    <mergeCell ref="C567:C569"/>
+    <mergeCell ref="B570:B572"/>
+    <mergeCell ref="C570:C572"/>
+    <mergeCell ref="B573:B575"/>
+    <mergeCell ref="C573:C575"/>
+    <mergeCell ref="B576:B578"/>
+    <mergeCell ref="C576:C578"/>
+    <mergeCell ref="B579:B581"/>
+    <mergeCell ref="C579:C581"/>
+    <mergeCell ref="B597:B598"/>
+    <mergeCell ref="C597:C598"/>
+    <mergeCell ref="B599:B601"/>
+    <mergeCell ref="C599:C601"/>
+    <mergeCell ref="B602:B604"/>
+    <mergeCell ref="C602:C604"/>
+    <mergeCell ref="B605:B606"/>
+    <mergeCell ref="C605:C606"/>
+    <mergeCell ref="B582:B584"/>
+    <mergeCell ref="C582:C584"/>
+    <mergeCell ref="B585:B587"/>
+    <mergeCell ref="C585:C587"/>
+    <mergeCell ref="B588:B590"/>
+    <mergeCell ref="C588:C590"/>
+    <mergeCell ref="B591:B593"/>
+    <mergeCell ref="C591:C593"/>
+    <mergeCell ref="B594:B596"/>
+    <mergeCell ref="C594:C596"/>
+    <mergeCell ref="B607:B609"/>
+    <mergeCell ref="C607:C609"/>
+    <mergeCell ref="B610:B612"/>
+    <mergeCell ref="C610:C612"/>
+    <mergeCell ref="B613:B615"/>
+    <mergeCell ref="C613:C615"/>
+    <mergeCell ref="B616:B618"/>
+    <mergeCell ref="C616:C618"/>
+    <mergeCell ref="B619:B621"/>
+    <mergeCell ref="C619:C621"/>
+    <mergeCell ref="B622:B624"/>
+    <mergeCell ref="C622:C624"/>
+    <mergeCell ref="B625:B627"/>
+    <mergeCell ref="C625:C627"/>
+    <mergeCell ref="B628:B630"/>
+    <mergeCell ref="C628:C630"/>
+    <mergeCell ref="B631:B633"/>
+    <mergeCell ref="C631:C633"/>
+    <mergeCell ref="B634:B636"/>
+    <mergeCell ref="C634:C636"/>
+    <mergeCell ref="B637:B639"/>
+    <mergeCell ref="C637:C639"/>
+    <mergeCell ref="B640:B642"/>
+    <mergeCell ref="C640:C642"/>
+    <mergeCell ref="B643:B645"/>
+    <mergeCell ref="C643:C645"/>
+    <mergeCell ref="B646:B648"/>
+    <mergeCell ref="C646:C648"/>
+    <mergeCell ref="B649:B651"/>
+    <mergeCell ref="C649:C651"/>
+    <mergeCell ref="B652:B654"/>
+    <mergeCell ref="C652:C654"/>
+    <mergeCell ref="B655:B657"/>
+    <mergeCell ref="C655:C657"/>
+    <mergeCell ref="B658:B660"/>
+    <mergeCell ref="C658:C660"/>
+    <mergeCell ref="B661:B663"/>
+    <mergeCell ref="C661:C663"/>
+    <mergeCell ref="B664:B666"/>
+    <mergeCell ref="C664:C666"/>
+    <mergeCell ref="B667:B669"/>
+    <mergeCell ref="C667:C669"/>
+    <mergeCell ref="B670:B672"/>
+    <mergeCell ref="C670:C672"/>
+    <mergeCell ref="B673:B675"/>
+    <mergeCell ref="C673:C675"/>
+    <mergeCell ref="B676:B677"/>
+    <mergeCell ref="C676:C677"/>
+    <mergeCell ref="B678:B680"/>
+    <mergeCell ref="C678:C680"/>
+    <mergeCell ref="B696:B698"/>
+    <mergeCell ref="C696:C698"/>
+    <mergeCell ref="B699:B701"/>
+    <mergeCell ref="C699:C701"/>
+    <mergeCell ref="B702:B704"/>
+    <mergeCell ref="C702:C704"/>
+    <mergeCell ref="B705:B706"/>
+    <mergeCell ref="C705:C706"/>
+    <mergeCell ref="B681:B683"/>
+    <mergeCell ref="C681:C683"/>
+    <mergeCell ref="B684:B686"/>
+    <mergeCell ref="C684:C686"/>
+    <mergeCell ref="B687:B689"/>
+    <mergeCell ref="C687:C689"/>
+    <mergeCell ref="B690:B692"/>
+    <mergeCell ref="C690:C692"/>
+    <mergeCell ref="B693:B695"/>
+    <mergeCell ref="C693:C695"/>
+    <mergeCell ref="B707:B709"/>
+    <mergeCell ref="C707:C709"/>
+    <mergeCell ref="B710:B712"/>
+    <mergeCell ref="C710:C712"/>
+    <mergeCell ref="B713:B715"/>
+    <mergeCell ref="C713:C715"/>
+    <mergeCell ref="B716:B718"/>
+    <mergeCell ref="C716:C718"/>
+    <mergeCell ref="B719:B721"/>
+    <mergeCell ref="C719:C721"/>
+    <mergeCell ref="B722:B724"/>
+    <mergeCell ref="C722:C724"/>
+    <mergeCell ref="B725:B727"/>
+    <mergeCell ref="C725:C727"/>
+    <mergeCell ref="B728:B730"/>
+    <mergeCell ref="C728:C730"/>
+    <mergeCell ref="B731:B733"/>
+    <mergeCell ref="C731:C733"/>
+    <mergeCell ref="B734:B735"/>
+    <mergeCell ref="C734:C735"/>
+    <mergeCell ref="B736:B738"/>
+    <mergeCell ref="C736:C738"/>
+    <mergeCell ref="B739:B741"/>
+    <mergeCell ref="C739:C741"/>
+    <mergeCell ref="B742:B744"/>
+    <mergeCell ref="C742:C744"/>
+    <mergeCell ref="B745:B747"/>
+    <mergeCell ref="C745:C747"/>
+    <mergeCell ref="B748:B750"/>
+    <mergeCell ref="C748:C750"/>
+    <mergeCell ref="B751:B753"/>
+    <mergeCell ref="C751:C753"/>
+    <mergeCell ref="B754:B756"/>
+    <mergeCell ref="C754:C756"/>
+    <mergeCell ref="B757:B759"/>
+    <mergeCell ref="C757:C759"/>
+    <mergeCell ref="B760:B762"/>
+    <mergeCell ref="C760:C762"/>
+    <mergeCell ref="B763:B765"/>
+    <mergeCell ref="C763:C765"/>
+    <mergeCell ref="B766:B768"/>
+    <mergeCell ref="C766:C768"/>
+    <mergeCell ref="B769:B771"/>
+    <mergeCell ref="C769:C771"/>
+    <mergeCell ref="B772:B774"/>
+    <mergeCell ref="C772:C774"/>
+    <mergeCell ref="B775:B777"/>
+    <mergeCell ref="C775:C777"/>
+    <mergeCell ref="B778:B780"/>
+    <mergeCell ref="C778:C780"/>
+    <mergeCell ref="B781:B783"/>
+    <mergeCell ref="C781:C783"/>
+    <mergeCell ref="B784:B786"/>
+    <mergeCell ref="C784:C786"/>
+    <mergeCell ref="B787:B789"/>
+    <mergeCell ref="C787:C789"/>
+    <mergeCell ref="B790:B792"/>
+    <mergeCell ref="C790:C792"/>
+    <mergeCell ref="B793:B795"/>
+    <mergeCell ref="C793:C795"/>
+    <mergeCell ref="B796:B798"/>
+    <mergeCell ref="C796:C798"/>
+    <mergeCell ref="B799:B801"/>
+    <mergeCell ref="C799:C801"/>
+    <mergeCell ref="B802:B804"/>
+    <mergeCell ref="C802:C804"/>
+    <mergeCell ref="B805:B807"/>
+    <mergeCell ref="C805:C807"/>
+    <mergeCell ref="B808:B810"/>
+    <mergeCell ref="C808:C810"/>
+    <mergeCell ref="B811:B813"/>
+    <mergeCell ref="C811:C813"/>
+    <mergeCell ref="B814:B816"/>
+    <mergeCell ref="C814:C816"/>
+    <mergeCell ref="B817:B819"/>
+    <mergeCell ref="C817:C819"/>
+    <mergeCell ref="B820:B822"/>
+    <mergeCell ref="C820:C822"/>
+    <mergeCell ref="B823:B825"/>
+    <mergeCell ref="C823:C825"/>
+    <mergeCell ref="B826:B828"/>
+    <mergeCell ref="C826:C828"/>
+    <mergeCell ref="B829:B831"/>
+    <mergeCell ref="C829:C831"/>
+    <mergeCell ref="B832:B834"/>
+    <mergeCell ref="C832:C834"/>
+    <mergeCell ref="B835:B837"/>
+    <mergeCell ref="C835:C837"/>
+    <mergeCell ref="B838:B840"/>
+    <mergeCell ref="C838:C840"/>
+    <mergeCell ref="B841:B843"/>
+    <mergeCell ref="C841:C843"/>
+    <mergeCell ref="B844:B846"/>
+    <mergeCell ref="C844:C846"/>
+    <mergeCell ref="B847:B849"/>
+    <mergeCell ref="C847:C849"/>
+    <mergeCell ref="B850:B852"/>
+    <mergeCell ref="C850:C852"/>
+    <mergeCell ref="B853:B855"/>
+    <mergeCell ref="C853:C855"/>
+    <mergeCell ref="B856:B858"/>
+    <mergeCell ref="C856:C858"/>
+    <mergeCell ref="B859:B861"/>
+    <mergeCell ref="C859:C861"/>
+    <mergeCell ref="B862:B864"/>
+    <mergeCell ref="C862:C864"/>
+    <mergeCell ref="B865:B867"/>
+    <mergeCell ref="C865:C867"/>
+    <mergeCell ref="B868:B870"/>
+    <mergeCell ref="C868:C870"/>
+    <mergeCell ref="B871:B873"/>
+    <mergeCell ref="C871:C873"/>
+    <mergeCell ref="B874:B876"/>
+    <mergeCell ref="C874:C876"/>
+    <mergeCell ref="B877:B879"/>
+    <mergeCell ref="C877:C879"/>
+    <mergeCell ref="B880:B882"/>
+    <mergeCell ref="C880:C882"/>
+    <mergeCell ref="B883:B885"/>
+    <mergeCell ref="C883:C885"/>
+    <mergeCell ref="B886:B888"/>
+    <mergeCell ref="C886:C888"/>
+    <mergeCell ref="B889:B891"/>
+    <mergeCell ref="C889:C891"/>
+    <mergeCell ref="B892:B894"/>
+    <mergeCell ref="C892:C894"/>
+    <mergeCell ref="B895:B897"/>
+    <mergeCell ref="C895:C897"/>
+    <mergeCell ref="B898:B900"/>
+    <mergeCell ref="C898:C900"/>
+    <mergeCell ref="B901:B903"/>
+    <mergeCell ref="C901:C903"/>
+    <mergeCell ref="B904:B906"/>
+    <mergeCell ref="C904:C906"/>
+    <mergeCell ref="B907:B909"/>
+    <mergeCell ref="C907:C909"/>
+    <mergeCell ref="B910:B912"/>
+    <mergeCell ref="C910:C912"/>
+    <mergeCell ref="B913:B915"/>
+    <mergeCell ref="C913:C915"/>
+    <mergeCell ref="B916:B918"/>
+    <mergeCell ref="C916:C918"/>
+    <mergeCell ref="B919:B921"/>
+    <mergeCell ref="C919:C921"/>
+    <mergeCell ref="B922:B924"/>
+    <mergeCell ref="C922:C924"/>
+    <mergeCell ref="B925:B927"/>
+    <mergeCell ref="C925:C927"/>
+    <mergeCell ref="B928:B930"/>
+    <mergeCell ref="C928:C930"/>
+    <mergeCell ref="B931:B933"/>
+    <mergeCell ref="C931:C933"/>
+    <mergeCell ref="B934:B936"/>
+    <mergeCell ref="C934:C936"/>
+    <mergeCell ref="B937:B938"/>
+    <mergeCell ref="C937:C938"/>
+    <mergeCell ref="B939:B941"/>
+    <mergeCell ref="C939:C941"/>
+    <mergeCell ref="B942:B944"/>
+    <mergeCell ref="C942:C944"/>
+    <mergeCell ref="B945:B947"/>
+    <mergeCell ref="C945:C947"/>
+    <mergeCell ref="B948:B950"/>
+    <mergeCell ref="C948:C950"/>
+    <mergeCell ref="B951:B953"/>
+    <mergeCell ref="C951:C953"/>
+    <mergeCell ref="B954:B956"/>
+    <mergeCell ref="C954:C956"/>
+    <mergeCell ref="B957:B959"/>
+    <mergeCell ref="C957:C959"/>
+    <mergeCell ref="B960:B962"/>
+    <mergeCell ref="C960:C962"/>
+    <mergeCell ref="B963:B965"/>
+    <mergeCell ref="C963:C965"/>
+    <mergeCell ref="B966:B968"/>
+    <mergeCell ref="C966:C968"/>
+    <mergeCell ref="B969:B971"/>
+    <mergeCell ref="C969:C971"/>
+    <mergeCell ref="B972:B974"/>
+    <mergeCell ref="C972:C974"/>
+    <mergeCell ref="B975:B977"/>
+    <mergeCell ref="C975:C977"/>
+    <mergeCell ref="B978:B980"/>
+    <mergeCell ref="C978:C980"/>
+    <mergeCell ref="B981:B983"/>
+    <mergeCell ref="C981:C983"/>
+    <mergeCell ref="B984:B986"/>
+    <mergeCell ref="C984:C986"/>
+    <mergeCell ref="B987:B989"/>
+    <mergeCell ref="C987:C989"/>
+    <mergeCell ref="B990:B992"/>
+    <mergeCell ref="C990:C992"/>
+    <mergeCell ref="B993:B995"/>
+    <mergeCell ref="C993:C995"/>
+    <mergeCell ref="B996:B998"/>
+    <mergeCell ref="C996:C998"/>
+    <mergeCell ref="B999:B1001"/>
+    <mergeCell ref="C999:C1001"/>
+    <mergeCell ref="B1002:B1004"/>
+    <mergeCell ref="C1002:C1004"/>
+    <mergeCell ref="B1005:B1007"/>
+    <mergeCell ref="C1005:C1007"/>
+    <mergeCell ref="B1008:B1010"/>
+    <mergeCell ref="C1008:C1010"/>
+    <mergeCell ref="B1011:B1013"/>
+    <mergeCell ref="C1011:C1013"/>
+    <mergeCell ref="B1014:B1016"/>
+    <mergeCell ref="C1014:C1016"/>
+    <mergeCell ref="B1017:B1019"/>
+    <mergeCell ref="C1017:C1019"/>
+    <mergeCell ref="B1020:B1022"/>
+    <mergeCell ref="C1020:C1022"/>
+    <mergeCell ref="B1023:B1025"/>
+    <mergeCell ref="C1023:C1025"/>
+    <mergeCell ref="B1026:B1028"/>
+    <mergeCell ref="C1026:C1028"/>
+    <mergeCell ref="B1029:B1031"/>
+    <mergeCell ref="C1029:C1031"/>
+    <mergeCell ref="B1032:B1034"/>
+    <mergeCell ref="C1032:C1034"/>
+    <mergeCell ref="B1035:B1037"/>
+    <mergeCell ref="C1035:C1037"/>
+    <mergeCell ref="B1038:B1040"/>
+    <mergeCell ref="C1038:C1040"/>
+    <mergeCell ref="B1041:B1043"/>
+    <mergeCell ref="C1041:C1043"/>
+    <mergeCell ref="B1044:B1046"/>
+    <mergeCell ref="C1044:C1046"/>
+    <mergeCell ref="B1047:B1049"/>
+    <mergeCell ref="C1047:C1049"/>
+    <mergeCell ref="B1050:B1052"/>
+    <mergeCell ref="C1050:C1052"/>
+    <mergeCell ref="B1053:B1055"/>
+    <mergeCell ref="C1053:C1055"/>
+    <mergeCell ref="B1056:B1058"/>
+    <mergeCell ref="C1056:C1058"/>
+    <mergeCell ref="B1059:B1061"/>
+    <mergeCell ref="C1059:C1061"/>
+    <mergeCell ref="B1062:B1064"/>
+    <mergeCell ref="C1062:C1064"/>
+    <mergeCell ref="B1065:B1067"/>
+    <mergeCell ref="C1065:C1067"/>
+    <mergeCell ref="B1068:B1070"/>
+    <mergeCell ref="C1068:C1070"/>
+    <mergeCell ref="B1071:B1073"/>
+    <mergeCell ref="C1071:C1073"/>
+    <mergeCell ref="B1074:B1076"/>
+    <mergeCell ref="C1074:C1076"/>
+    <mergeCell ref="B1077:B1079"/>
+    <mergeCell ref="C1077:C1079"/>
+    <mergeCell ref="B1080:B1082"/>
+    <mergeCell ref="C1080:C1082"/>
+    <mergeCell ref="B1083:B1085"/>
+    <mergeCell ref="C1083:C1085"/>
+    <mergeCell ref="B1086:B1088"/>
+    <mergeCell ref="C1086:C1088"/>
+    <mergeCell ref="B1089:B1091"/>
+    <mergeCell ref="C1089:C1091"/>
+    <mergeCell ref="B1092:B1094"/>
+    <mergeCell ref="C1092:C1094"/>
+    <mergeCell ref="B1095:B1097"/>
+    <mergeCell ref="C1095:C1097"/>
+    <mergeCell ref="B1098:B1099"/>
+    <mergeCell ref="C1098:C1099"/>
+    <mergeCell ref="B1100:B1101"/>
+    <mergeCell ref="C1100:C1101"/>
+    <mergeCell ref="B1102:B1103"/>
+    <mergeCell ref="C1102:C1103"/>
+    <mergeCell ref="B1104:B1105"/>
+    <mergeCell ref="C1104:C1105"/>
+    <mergeCell ref="B1106:B1107"/>
+    <mergeCell ref="C1106:C1107"/>
+    <mergeCell ref="B1108:B1109"/>
+    <mergeCell ref="C1108:C1109"/>
+    <mergeCell ref="B1110:B1111"/>
+    <mergeCell ref="C1110:C1111"/>
+    <mergeCell ref="B1112:B1113"/>
+    <mergeCell ref="C1112:C1113"/>
+    <mergeCell ref="B1114:B1115"/>
+    <mergeCell ref="C1114:C1115"/>
+    <mergeCell ref="B1116:B1117"/>
+    <mergeCell ref="C1116:C1117"/>
+    <mergeCell ref="B1118:B1119"/>
+    <mergeCell ref="C1118:C1119"/>
+    <mergeCell ref="B1120:B1121"/>
+    <mergeCell ref="C1120:C1121"/>
+    <mergeCell ref="B1122:B1123"/>
+    <mergeCell ref="C1122:C1123"/>
+    <mergeCell ref="B1124:B1125"/>
+    <mergeCell ref="C1124:C1125"/>
+    <mergeCell ref="B1126:B1128"/>
+    <mergeCell ref="C1126:C1128"/>
+    <mergeCell ref="B1129:B1130"/>
+    <mergeCell ref="C1129:C1130"/>
+    <mergeCell ref="B1131:B1132"/>
+    <mergeCell ref="C1131:C1132"/>
+    <mergeCell ref="B1133:B1134"/>
+    <mergeCell ref="C1133:C1134"/>
+    <mergeCell ref="B1135:B1136"/>
+    <mergeCell ref="C1135:C1136"/>
+    <mergeCell ref="B1137:B1139"/>
+    <mergeCell ref="C1137:C1139"/>
+    <mergeCell ref="B1140:B1142"/>
+    <mergeCell ref="C1140:C1142"/>
+    <mergeCell ref="B1143:B1145"/>
+    <mergeCell ref="C1143:C1145"/>
+    <mergeCell ref="B1146:B1148"/>
+    <mergeCell ref="C1146:C1148"/>
+    <mergeCell ref="B1149:B1150"/>
+    <mergeCell ref="C1149:C1150"/>
+    <mergeCell ref="B1151:B1153"/>
+    <mergeCell ref="C1151:C1153"/>
+    <mergeCell ref="B1154:B1156"/>
+    <mergeCell ref="C1154:C1156"/>
+    <mergeCell ref="B1157:B1159"/>
+    <mergeCell ref="C1157:C1159"/>
+    <mergeCell ref="B1160:B1161"/>
+    <mergeCell ref="C1160:C1161"/>
+    <mergeCell ref="B1162:B1163"/>
+    <mergeCell ref="C1162:C1163"/>
+    <mergeCell ref="B1164:B1166"/>
+    <mergeCell ref="C1164:C1166"/>
+    <mergeCell ref="B1167:B1169"/>
+    <mergeCell ref="C1167:C1169"/>
+    <mergeCell ref="B1170:B1172"/>
+    <mergeCell ref="C1170:C1172"/>
+    <mergeCell ref="B1173:B1175"/>
+    <mergeCell ref="C1173:C1175"/>
+    <mergeCell ref="B1176:B1178"/>
+    <mergeCell ref="C1176:C1178"/>
+    <mergeCell ref="B1179:B1181"/>
+    <mergeCell ref="C1179:C1181"/>
+    <mergeCell ref="B1182:B1184"/>
+    <mergeCell ref="C1182:C1184"/>
+    <mergeCell ref="B1185:B1187"/>
+    <mergeCell ref="C1185:C1187"/>
+    <mergeCell ref="B1188:B1189"/>
+    <mergeCell ref="C1188:C1189"/>
+    <mergeCell ref="B1190:B1191"/>
+    <mergeCell ref="C1190:C1191"/>
+    <mergeCell ref="B1192:B1193"/>
+    <mergeCell ref="C1192:C1193"/>
+    <mergeCell ref="B1194:B1195"/>
+    <mergeCell ref="C1194:C1195"/>
+    <mergeCell ref="B1196:B1198"/>
+    <mergeCell ref="C1196:C1198"/>
+    <mergeCell ref="B1199:B1201"/>
+    <mergeCell ref="C1199:C1201"/>
+    <mergeCell ref="B1202:B1204"/>
+    <mergeCell ref="C1202:C1204"/>
+    <mergeCell ref="B1220:B1222"/>
+    <mergeCell ref="C1220:C1222"/>
+    <mergeCell ref="B1205:B1207"/>
+    <mergeCell ref="C1205:C1207"/>
+    <mergeCell ref="B1208:B1210"/>
+    <mergeCell ref="C1208:C1210"/>
+    <mergeCell ref="B1211:B1213"/>
+    <mergeCell ref="C1211:C1213"/>
+    <mergeCell ref="B1214:B1216"/>
+    <mergeCell ref="C1214:C1216"/>
+    <mergeCell ref="B1217:B1219"/>
+    <mergeCell ref="C1217:C1219"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A1" r:id="rId1" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:xtRiw3GOFMkC" xr:uid="{0E1A47C0-B24F-A547-B175-807B2A556D7E}"/>
-    <hyperlink ref="B1" r:id="rId2" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14835418577795587998" xr:uid="{7BD449C1-E356-EC44-8F81-D29E1E3E97EF}"/>
-    <hyperlink ref="A4" r:id="rId3" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:D03iK_w7-QYC" xr:uid="{2D09071F-C74C-754A-8511-07666244EDB2}"/>
-    <hyperlink ref="B4" r:id="rId4" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2565420096347388496" xr:uid="{2C93E254-DFFF-7044-8FDB-3920DBEB4D87}"/>
-    <hyperlink ref="A7" r:id="rId5" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:hkOj_22Ku90C" xr:uid="{C332DFC5-9F47-2A49-877A-B44C983CE187}"/>
-    <hyperlink ref="B7" r:id="rId6" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18272262975470332764,171540718227260172" xr:uid="{6645FFA1-8F56-A443-95C4-7A1B71A26C13}"/>
-    <hyperlink ref="A10" r:id="rId7" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:kNdYIx-mwKoC" xr:uid="{E3665CD3-D682-7144-8646-389F2DBC947F}"/>
-    <hyperlink ref="B10" r:id="rId8" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8963365811758092195" xr:uid="{19D8DA61-33B4-CD41-97AF-1CB89D266616}"/>
-    <hyperlink ref="A13" r:id="rId9" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:lSLTfruPkqcC" xr:uid="{25C05CB8-5C85-0E47-9BC5-9B71280F0572}"/>
-    <hyperlink ref="A16" r:id="rId10" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:u9iWguZQMMsC" xr:uid="{BAEFEA11-8B4E-E047-B489-C1A0A3006E91}"/>
-    <hyperlink ref="B16" r:id="rId11" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=342094618899736309" xr:uid="{9497040B-2C82-D44F-8FCE-2D4396EB2697}"/>
-    <hyperlink ref="A19" r:id="rId12" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:YsMSGLbcyi4C" xr:uid="{D26725CE-2A21-EF4B-AD0C-31AF2AF43A02}"/>
-    <hyperlink ref="B19" r:id="rId13" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4255078183517610355" xr:uid="{163AFC12-07A1-E447-A8CD-5B31604D9224}"/>
-    <hyperlink ref="A22" r:id="rId14" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:Y0pCki6q_DkC" xr:uid="{97377268-BF31-2842-9316-1375BCADF07F}"/>
-    <hyperlink ref="B22" r:id="rId15" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14489566340995518931" xr:uid="{3716523F-9DE4-474D-825B-7C2105F942B1}"/>
-    <hyperlink ref="A25" r:id="rId16" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:geHnlv5EZngC" xr:uid="{49D0BA48-C932-D24C-9FF6-1FD15519A7BF}"/>
-    <hyperlink ref="B25" r:id="rId17" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13884792519762817378" xr:uid="{E8A83FBF-C5B0-9D46-BD18-22E3AE5CAEBB}"/>
-    <hyperlink ref="A28" r:id="rId18" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:maZDTaKrznsC" xr:uid="{03DBBEF4-718D-CC41-9C6C-A1E87D4E64CC}"/>
-    <hyperlink ref="B28" r:id="rId19" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16765810861638975140" xr:uid="{E7BD317C-F7A4-A742-B1E9-8B1A89A04F56}"/>
-    <hyperlink ref="A31" r:id="rId20" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:fPk4N6BV_jEC" xr:uid="{D1D4953C-FD4C-C746-B34A-3183A8147421}"/>
-    <hyperlink ref="B31" r:id="rId21" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15756127806033295418" xr:uid="{67E5A1A3-2597-354E-8862-FEDC639487F3}"/>
-    <hyperlink ref="A34" r:id="rId22" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:4DMP91E08xMC" xr:uid="{DC65F82B-7464-1A44-9F3F-467D70A76273}"/>
-    <hyperlink ref="B34" r:id="rId23" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11611536443654066771" xr:uid="{4DA53BDC-D7AB-4E46-8531-AD12451CDBA9}"/>
-    <hyperlink ref="A37" r:id="rId24" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:d1gkVwhDpl0C" xr:uid="{8A87A0BA-16BD-2347-B7DC-C39F76A6EE75}"/>
-    <hyperlink ref="B37" r:id="rId25" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=594809252767145284" xr:uid="{84A4EE1D-7FFF-D24B-894A-D3563ED4B90B}"/>
-    <hyperlink ref="A40" r:id="rId26" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:aqlVkmm33-oC" xr:uid="{8C8F61D4-D5B0-4E47-94A2-5F0DA629D6CC}"/>
-    <hyperlink ref="B40" r:id="rId27" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11269389967627436310" xr:uid="{9F0CCF4C-FC45-9246-B5E6-6DB6615B648A}"/>
-    <hyperlink ref="A43" r:id="rId28" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:_Ybze24A_UAC" xr:uid="{366C9F49-6A6A-F449-852F-27DD300D9002}"/>
-    <hyperlink ref="A46" r:id="rId29" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:W5xh706n7nkC" xr:uid="{9E271487-583E-D742-B8E8-AA7EA9044947}"/>
-    <hyperlink ref="B46" r:id="rId30" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13041118335278313143" xr:uid="{13A9A2D9-0450-CA41-8663-BB6B193A6699}"/>
-    <hyperlink ref="A49" r:id="rId31" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:g5m5HwL7SMYC" xr:uid="{90A89DDB-57AA-E243-AC01-580E9DBD214C}"/>
-    <hyperlink ref="B49" r:id="rId32" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7644244967039202759" xr:uid="{ED1A56D7-82DD-4F4E-8A00-463F9405F740}"/>
-    <hyperlink ref="A52" r:id="rId33" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:TQgYirikUcIC" xr:uid="{EC62BE64-F05B-DA46-8109-BB95B6CD9B3B}"/>
-    <hyperlink ref="B52" r:id="rId34" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18010235891695903387" xr:uid="{3CE39C66-ABBB-484C-B619-750385740194}"/>
-    <hyperlink ref="A55" r:id="rId35" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:uJ-U7cs_P_0C" xr:uid="{D4F1E7EA-57C2-7549-AD24-08D9D25225BB}"/>
-    <hyperlink ref="B55" r:id="rId36" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8967359328377680136" xr:uid="{81507579-DD32-D047-8DE7-2CAE72FC4A30}"/>
-    <hyperlink ref="A58" r:id="rId37" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;citation_for_view=lotIW94AAAAJ:_B80troHkn4C" xr:uid="{EB1F6A03-23D3-2549-B414-1094720EFF75}"/>
-    <hyperlink ref="B58" r:id="rId38" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13700783791544983922" xr:uid="{B6002858-9389-0044-9B66-CA92841A5A3D}"/>
-    <hyperlink ref="A61" r:id="rId39" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:ns9cj8rnVeAC" xr:uid="{35469227-0103-CB43-8F0B-A28A24B32CB9}"/>
-    <hyperlink ref="B61" r:id="rId40" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1724013537548133817" xr:uid="{A36A6AEF-4F2B-FF41-B10B-E208554AE879}"/>
-    <hyperlink ref="A64" r:id="rId41" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:HDshCWvjkbEC" xr:uid="{572D9A9A-CF85-034D-B21D-F6F17004A92D}"/>
-    <hyperlink ref="B64" r:id="rId42" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16510279951136903778" xr:uid="{5893EF00-C1E9-7B4F-8748-E7BB99E8E541}"/>
-    <hyperlink ref="A67" r:id="rId43" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:XiSMed-E-HIC" xr:uid="{E277CDA1-73F1-5846-A1C9-B83D0CC7BE17}"/>
-    <hyperlink ref="B67" r:id="rId44" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10684369078235246507" xr:uid="{45481E65-3F32-2D4C-8067-879CF474DCB3}"/>
-    <hyperlink ref="A70" r:id="rId45" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:isC4tDSrTZIC" xr:uid="{41C798E8-CADF-9945-ADF8-0E0E5AB7F989}"/>
-    <hyperlink ref="B70" r:id="rId46" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18276410092073951488" xr:uid="{0B8391DB-D5DB-0943-9B4E-74698801CB5B}"/>
-    <hyperlink ref="A73" r:id="rId47" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:D_sINldO8mEC" xr:uid="{AF3D6EC0-E18B-8B47-9376-5CBD59FDD3F2}"/>
-    <hyperlink ref="B73" r:id="rId48" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4439285330323626344" xr:uid="{3B67A718-6D7F-B341-A115-75195EBEAC0A}"/>
-    <hyperlink ref="A76" r:id="rId49" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:a0OBvERweLwC" xr:uid="{70AFCB8B-D4B0-DE42-9F25-839A44698E30}"/>
-    <hyperlink ref="B76" r:id="rId50" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10742791660521465417" xr:uid="{D6FE9372-BC4F-7849-A52D-0B07D1321ECA}"/>
-    <hyperlink ref="A79" r:id="rId51" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:blknAaTinKkC" xr:uid="{6C340AB8-0CE9-0541-AD34-30537A655C12}"/>
-    <hyperlink ref="B79" r:id="rId52" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17434149345146474674,5566309790439441067" xr:uid="{DD06B9BC-6306-364B-8D6E-C1CCEBECBCE6}"/>
-    <hyperlink ref="A82" r:id="rId53" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:ULOm3_A8WrAC" xr:uid="{2D16E9F3-4020-264A-AA8E-4BF1EA8D1DB0}"/>
-    <hyperlink ref="B82" r:id="rId54" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9865753024551152925" xr:uid="{20199370-98B9-EF44-A7D2-6E34D062AE84}"/>
-    <hyperlink ref="A85" r:id="rId55" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:8k81kl-MbHgC" xr:uid="{9DF2D963-0476-F74E-B1C9-184E1C9D54F7}"/>
-    <hyperlink ref="B85" r:id="rId56" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7253237206835815752" xr:uid="{B50D0EDD-0A0B-5744-87ED-AE8BC8E48770}"/>
-    <hyperlink ref="A88" r:id="rId57" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:e5wmG9Sq2KIC" xr:uid="{4AC670CA-3CE9-BD43-8452-49C01BB30CD5}"/>
-    <hyperlink ref="B88" r:id="rId58" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18076152141955982965" xr:uid="{B8921814-9008-1342-B994-B439CCA9502C}"/>
-    <hyperlink ref="A91" r:id="rId59" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:uWQEDVKXjbEC" xr:uid="{7D7FEB11-F2AC-D64C-ADF7-12E5FB2E76D0}"/>
-    <hyperlink ref="A94" r:id="rId60" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:abG-DnoFyZgC" xr:uid="{FAB9D35D-5B66-F047-8A5C-E7B3B90FBC80}"/>
-    <hyperlink ref="B94" r:id="rId61" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16138910279455140123" xr:uid="{A51FED60-DCB7-C84E-AEA7-E24723F81C56}"/>
-    <hyperlink ref="A97" r:id="rId62" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:ZeXyd9-uunAC" xr:uid="{A7276656-425A-944D-865F-886929B6745E}"/>
-    <hyperlink ref="B97" r:id="rId63" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17122264761415477321" xr:uid="{224E0C6F-504A-1946-9548-BBC1774E7D42}"/>
-    <hyperlink ref="A100" r:id="rId64" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:iH-uZ7U-co4C" xr:uid="{5AC106F6-AD4B-CF4E-BB0C-DCAA210718CF}"/>
-    <hyperlink ref="B100" r:id="rId65" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15078330899090729341" xr:uid="{958EE51E-9E26-2C46-B03F-5411DE338715}"/>
-    <hyperlink ref="A103" r:id="rId66" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:j3f4tGmQtD8C" xr:uid="{12E0B175-539C-9D42-BD12-7EB1F51C1ED7}"/>
-    <hyperlink ref="B103" r:id="rId67" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1338754417666333237" xr:uid="{1D11D1BE-CACE-9A46-9603-0B952F251AD9}"/>
-    <hyperlink ref="A106" r:id="rId68" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:7PzlFSSx8tAC" xr:uid="{AE6B4008-6EE6-EA4C-8C75-E8AD4D4A0738}"/>
-    <hyperlink ref="B106" r:id="rId69" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14667416093752552532" xr:uid="{9C087AEB-F7C5-0747-95A3-2EE46B5480BD}"/>
-    <hyperlink ref="A109" r:id="rId70" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:KlAtU1dfN6UC" xr:uid="{5AF98E46-7AF4-D94B-8813-8AD8B65FDBAA}"/>
-    <hyperlink ref="B109" r:id="rId71" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9078859537966870224" xr:uid="{CC025A6B-74DA-5841-BD1F-EFAD7498AD09}"/>
-    <hyperlink ref="A112" r:id="rId72" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:IjCSPb-OGe4C" xr:uid="{FBCB7A47-0B6A-0541-A4FB-DC9B5A308551}"/>
-    <hyperlink ref="B112" r:id="rId73" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2083988724531507488" xr:uid="{217899E8-2FF2-3A4B-A8F3-4C7269F05C5A}"/>
-    <hyperlink ref="A115" r:id="rId74" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:VL0QpB8kHFEC" xr:uid="{F91D336F-32FD-CC4F-BF2A-8DB87D184AC8}"/>
-    <hyperlink ref="B115" r:id="rId75" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14943949718996492241" xr:uid="{C4570779-3235-AF45-8694-904B2A30EAA1}"/>
-    <hyperlink ref="A118" r:id="rId76" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:LkGwnXOMwfcC" xr:uid="{0A2CDCE6-4EB2-C145-BA70-95D1B3198C2C}"/>
-    <hyperlink ref="B118" r:id="rId77" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15865915662073690434" xr:uid="{A9B0BF82-1141-CA47-8D20-61A233587125}"/>
-    <hyperlink ref="A121" r:id="rId78" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:J_g5lzvAfSwC" xr:uid="{8E5197D6-7070-954B-A9AD-89E85E69D1D8}"/>
-    <hyperlink ref="B121" r:id="rId79" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13041803834546486863" xr:uid="{49116C28-B7CF-C345-A8B0-51F6E0958FC0}"/>
-    <hyperlink ref="A124" r:id="rId80" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:TFP_iSt0sucC" xr:uid="{63E21166-3941-5D44-AC77-2A9DF9A5B0BA}"/>
-    <hyperlink ref="B124" r:id="rId81" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5183657156869665693" xr:uid="{90992773-495E-1645-B9FD-38FD38B4E523}"/>
-    <hyperlink ref="A127" r:id="rId82" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:BrmTIyaxlBUC" xr:uid="{3B8FB74D-2C4E-4445-8074-5B15567253A6}"/>
-    <hyperlink ref="B127" r:id="rId83" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4052205225055713910" xr:uid="{6EE3CA6A-EACA-5F4A-A05F-FE76CE59E5DD}"/>
-    <hyperlink ref="A130" r:id="rId84" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:ZuybSZzF8UAC" xr:uid="{69CC93C7-E3FB-344F-8D37-A2DA116D6BA4}"/>
-    <hyperlink ref="B130" r:id="rId85" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16436423180245240701,5020251165016998386" xr:uid="{80A64456-4E61-5C40-8D88-DB134D781C87}"/>
-    <hyperlink ref="A133" r:id="rId86" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:pyW8ca7W8N0C" xr:uid="{955AB3D3-3E70-D440-9B23-1F0B48747C3B}"/>
-    <hyperlink ref="B133" r:id="rId87" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8171938835388123872" xr:uid="{A51B29E4-F840-CF45-84D4-58B34AB55066}"/>
-    <hyperlink ref="A136" r:id="rId88" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:_Qo2XoVZTnwC" xr:uid="{6239D940-69BE-AC4C-A891-7CEB4B50A1DB}"/>
-    <hyperlink ref="B136" r:id="rId89" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18113924889310421778" xr:uid="{9FF6E3A0-F06F-9E42-9AAC-271C71910930}"/>
-    <hyperlink ref="A139" r:id="rId90" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:WF5omc3nYNoC" xr:uid="{4F786937-5598-8A47-8EDC-45ED82DDFF77}"/>
-    <hyperlink ref="B139" r:id="rId91" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5055946827873629097" xr:uid="{945C7FA5-137D-A74A-A415-896B03504D35}"/>
-    <hyperlink ref="A142" r:id="rId92" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:tOudhMTPpwUC" xr:uid="{8EF5B65C-42D9-3D46-8557-E3993B08B23C}"/>
-    <hyperlink ref="B142" r:id="rId93" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13162351343408260130" xr:uid="{1BD61E0D-8541-B447-BD9A-C41F57F24448}"/>
-    <hyperlink ref="A145" r:id="rId94" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:Tiz5es2fbqcC" xr:uid="{C0645AC7-2298-CE49-886D-839A53B91397}"/>
-    <hyperlink ref="B145" r:id="rId95" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16006370158085323403" xr:uid="{8C11A033-659F-C145-AE6E-3ADE7E97BA1E}"/>
-    <hyperlink ref="A148" r:id="rId96" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:cFHS6HbyZ2cC" xr:uid="{7EF88CEA-E3D2-1C4C-B8CE-FA05B6FB5678}"/>
-    <hyperlink ref="B148" r:id="rId97" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7850357982461807455" xr:uid="{57FF341C-CD36-E244-A426-EABD47AF7F8C}"/>
-    <hyperlink ref="A151" r:id="rId98" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:2P1L_qKh6hAC" xr:uid="{2CEA341C-1CC7-DF4C-8FFA-5A0EE14BF777}"/>
-    <hyperlink ref="B151" r:id="rId99" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15445732360366845980,2096223136222651988" xr:uid="{EA80034B-FAB0-EC4F-8ECC-DFA252A2BAB3}"/>
-    <hyperlink ref="A154" r:id="rId100" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:Tyk-4Ss8FVUC" xr:uid="{E462E15C-E42B-DE4B-B818-C0C51849DD62}"/>
-    <hyperlink ref="B154" r:id="rId101" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2179405781858533086" xr:uid="{8204DAFB-C765-9D40-865D-A827D8D3B96B}"/>
-    <hyperlink ref="A157" r:id="rId102" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:JoZmwDi-zQgC" xr:uid="{510F7567-7F57-A141-9154-8EB3E0648952}"/>
-    <hyperlink ref="B157" r:id="rId103" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11929775433986175749" xr:uid="{EDC9992E-DA9A-2C4A-A346-916F930353C2}"/>
-    <hyperlink ref="A160" r:id="rId104" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:B3FOqHPlNUQC" xr:uid="{BFBD6355-314D-E54C-B3B1-6BC904C868DB}"/>
-    <hyperlink ref="B160" r:id="rId105" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18375404758817130995" xr:uid="{83317D6D-1564-DF4D-A5D8-AECED561BF2E}"/>
-    <hyperlink ref="A163" r:id="rId106" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:Mojj43d5GZwC" xr:uid="{2DAFCF41-335B-EE4E-AD3F-1417966235C3}"/>
-    <hyperlink ref="B163" r:id="rId107" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16454821329668421264" xr:uid="{7829DB9F-4D37-A545-AF9F-84E7297CEC94}"/>
-    <hyperlink ref="A166" r:id="rId108" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:_xSYboBqXhAC" xr:uid="{4F7C6D77-7EBB-9949-B1EB-13586788E236}"/>
-    <hyperlink ref="B166" r:id="rId109" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5227499844007580516" xr:uid="{4F17D860-017F-D14F-AC4D-647EC8E77957}"/>
-    <hyperlink ref="A169" r:id="rId110" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:OU6Ihb5iCvQC" xr:uid="{37441867-5895-F147-A4DA-676D4962C8A5}"/>
-    <hyperlink ref="B169" r:id="rId111" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6218640191070496313" xr:uid="{F83502DE-4E18-0446-958A-41CFB595B311}"/>
-    <hyperlink ref="A172" r:id="rId112" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:ldfaerwXgEUC" xr:uid="{0A417056-9B24-3640-8277-14DC74674BCD}"/>
-    <hyperlink ref="B172" r:id="rId113" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4156213026527907028" xr:uid="{F3119C93-A138-B04B-9540-9AC8E5C5E931}"/>
-    <hyperlink ref="A175" r:id="rId114" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:bFI3QPDXJZMC" xr:uid="{009528AE-B03C-F94B-B2BA-B4858FF5C5A6}"/>
-    <hyperlink ref="B175" r:id="rId115" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9740159967654838810" xr:uid="{7CD3BB62-29C2-ED40-BA0A-67B71F6AC9F9}"/>
-    <hyperlink ref="A178" r:id="rId116" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:KxtntwgDAa4C" xr:uid="{3A79C73A-8914-8846-9EF1-29914AEAC2D8}"/>
-    <hyperlink ref="B178" r:id="rId117" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14738870703705434963" xr:uid="{1663CD0B-9981-A744-8405-6C247511BD72}"/>
-    <hyperlink ref="A181" r:id="rId118" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:qxL8FJ1GzNcC" xr:uid="{D1C4F9AD-8B8E-8C42-8675-FD5162320BEA}"/>
-    <hyperlink ref="B181" r:id="rId119" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10296266986924577007" xr:uid="{A8B3071F-71CD-1546-9959-385434DD83E0}"/>
-    <hyperlink ref="A184" r:id="rId120" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:pqnbT2bcN3wC" xr:uid="{24746BFE-55CD-624E-B601-4CA0BE2264F7}"/>
-    <hyperlink ref="B184" r:id="rId121" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6892275663945815970" xr:uid="{EBE33B65-4238-6047-B8BD-C3239A4B857A}"/>
-    <hyperlink ref="A187" r:id="rId122" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:RGFaLdJalmkC" xr:uid="{91E9F6F0-1DDA-F549-AAD2-DA8D58F13660}"/>
-    <hyperlink ref="B187" r:id="rId123" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9776731836656109167" xr:uid="{34B747D8-5C0D-7B45-A3CD-33664053F417}"/>
-    <hyperlink ref="A190" r:id="rId124" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:YOwf2qJgpHMC" xr:uid="{C8730771-3F98-724E-84E1-053DA56900F5}"/>
-    <hyperlink ref="B190" r:id="rId125" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9948183663789986000" xr:uid="{9F923263-D3DF-2F46-A81D-C724DA50BAB5}"/>
-    <hyperlink ref="A193" r:id="rId126" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:b0M2c_1WBrUC" xr:uid="{B817C73E-1633-FD49-8A0C-214E6E3A434F}"/>
-    <hyperlink ref="B193" r:id="rId127" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6088468648892368612" xr:uid="{918A9C94-E9B4-3A4E-B08E-569BF5B2F782}"/>
-    <hyperlink ref="A196" r:id="rId128" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:qjMakFHDy7sC" xr:uid="{640EF8B2-B5AD-184D-87E9-3B50AD6D5A44}"/>
-    <hyperlink ref="B196" r:id="rId129" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1521592263984751168" xr:uid="{2E24124A-3CA8-684C-96FD-3FA06DDD0A74}"/>
-    <hyperlink ref="A199" r:id="rId130" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:dfsIfKJdRG4C" xr:uid="{06BD21D4-B6DC-5349-B24E-37788C7E4E7E}"/>
-    <hyperlink ref="B199" r:id="rId131" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1505539922492679102" xr:uid="{401E9045-6E55-F047-962C-C204FCED4D74}"/>
-    <hyperlink ref="A202" r:id="rId132" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:R3hNpaxXUhUC" xr:uid="{704E0C29-8BD3-604D-8BB5-4AF849C66D53}"/>
-    <hyperlink ref="B202" r:id="rId133" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18019965229599229116" xr:uid="{29AF459C-4B5A-4F43-A28F-EB079B6D2754}"/>
-    <hyperlink ref="A205" r:id="rId134" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:NaGl4SEjCO4C" xr:uid="{F262FDA9-F369-E84D-8851-FA41A98B7089}"/>
-    <hyperlink ref="B205" r:id="rId135" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12760873149124739301" xr:uid="{6B5A37E5-5C98-1243-87D1-475FDEF47624}"/>
-    <hyperlink ref="A208" r:id="rId136" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:k_IJM867U9cC" xr:uid="{108441A1-23EA-8F44-AF17-AA2F8B233CA9}"/>
-    <hyperlink ref="B208" r:id="rId137" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8594912638179182270" xr:uid="{1948A6E2-CA11-654F-9F29-7962CB127C34}"/>
-    <hyperlink ref="A211" r:id="rId138" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:qUcmZB5y_30C" xr:uid="{0DFF56AB-9218-BD42-A16E-60EE369716EE}"/>
-    <hyperlink ref="B211" r:id="rId139" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15739401261851303636" xr:uid="{B95A7084-04AC-784C-981D-CD4B4CAC1D50}"/>
-    <hyperlink ref="A214" r:id="rId140" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:dshw04ExmUIC" xr:uid="{A94AA48C-5502-6C42-8258-D6544C9B5962}"/>
-    <hyperlink ref="B214" r:id="rId141" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12541372592653855104" xr:uid="{660B48F4-4F2F-9D48-B17E-5A9F0DFF8B61}"/>
-    <hyperlink ref="A217" r:id="rId142" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:u-x6o8ySG0sC" xr:uid="{5DF12DF3-CC5E-0742-9C88-BDCC04485889}"/>
-    <hyperlink ref="B217" r:id="rId143" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=499578808728508021" xr:uid="{56652FAB-4BCE-AD43-B6E0-E1A7BD53C234}"/>
-    <hyperlink ref="A220" r:id="rId144" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:Se3iqnhoufwC" xr:uid="{11B73AC2-2374-9E4F-AF22-E55837C79923}"/>
-    <hyperlink ref="B220" r:id="rId145" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6251969191740981414" xr:uid="{B6CF7220-AEAC-FC4A-88D5-4D411A367ECA}"/>
-    <hyperlink ref="A223" r:id="rId146" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:kzcrU_BdoSEC" xr:uid="{BD1F21FE-95C2-1343-A67F-747046CEF2C1}"/>
-    <hyperlink ref="B223" r:id="rId147" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15148502300070183642" xr:uid="{5AE8A4F7-996E-7140-9E5D-F5647BFEE473}"/>
-    <hyperlink ref="A226" r:id="rId148" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:u_35RYKgDlwC" xr:uid="{F56D120A-C0C5-7540-A4B4-A15BDF215C6C}"/>
-    <hyperlink ref="B226" r:id="rId149" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1195250452201948679" xr:uid="{BAA53CDC-571D-634D-89B0-B4715756D18F}"/>
-    <hyperlink ref="A229" r:id="rId150" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:M3ejUd6NZC8C" xr:uid="{AAE69A98-577E-1445-A065-48ABEC9426C2}"/>
-    <hyperlink ref="B229" r:id="rId151" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10236779604127218043" xr:uid="{8020B38B-D74E-F14D-A477-7D8395C05177}"/>
-    <hyperlink ref="A232" r:id="rId152" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:EYYDruWGBe4C" xr:uid="{8E696970-421A-EC4D-8E2D-9CEF00550E4F}"/>
-    <hyperlink ref="B232" r:id="rId153" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7976637345549608036" xr:uid="{0AA03BA2-BBA8-A647-B051-0B0D82CE5608}"/>
-    <hyperlink ref="A235" r:id="rId154" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:5Ul4iDaHHb8C" xr:uid="{8969C4EF-855F-2C47-A28A-C96C11E5D7BD}"/>
-    <hyperlink ref="B235" r:id="rId155" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8976671023132835953" xr:uid="{5D278F74-447F-F64B-AE89-0AF739FA8467}"/>
-    <hyperlink ref="A238" r:id="rId156" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:P5F9QuxV20EC" xr:uid="{2A366B41-41DE-D547-B264-9F86D7EEB50E}"/>
-    <hyperlink ref="B238" r:id="rId157" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6692257272007999745" xr:uid="{CF0CC43D-EAF0-2448-8BEC-1E7607243A68}"/>
-    <hyperlink ref="A241" r:id="rId158" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:35r97b3x0nAC" xr:uid="{821AF421-5B7C-9640-9458-8CE27D173E04}"/>
-    <hyperlink ref="B241" r:id="rId159" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17781446448602595679" xr:uid="{1DB2E828-A030-B44A-B551-B9BE7BA96E85}"/>
-    <hyperlink ref="A244" r:id="rId160" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:evX43VCCuoAC" xr:uid="{EDD36A5A-055D-6A44-A90B-A569561DA5E8}"/>
-    <hyperlink ref="B244" r:id="rId161" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15613077192755878165" xr:uid="{E9A4A103-ACD7-CD4B-897E-27CDC034F4FB}"/>
-    <hyperlink ref="A247" r:id="rId162" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:NJ774b8OgUMC" xr:uid="{FCCC1932-80C8-3942-8702-4C8179A93E17}"/>
-    <hyperlink ref="B247" r:id="rId163" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7916540758135801985" xr:uid="{4823F52D-60C7-7C4B-8DB3-B908E7007EF7}"/>
-    <hyperlink ref="A250" r:id="rId164" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:WbkHhVStYXYC" xr:uid="{166128D4-2EE8-0D4A-8BF7-DC5E36A3ED37}"/>
-    <hyperlink ref="B250" r:id="rId165" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12347233027893450893,4081673723780999764" xr:uid="{626F6BB8-F6D2-944F-9B74-8E1337C779AA}"/>
-    <hyperlink ref="A253" r:id="rId166" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:yD5IFk8b50cC" xr:uid="{F039ABA1-6138-0A4B-9FD3-2B1404F90788}"/>
-    <hyperlink ref="B253" r:id="rId167" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5809049634235940864" xr:uid="{F01E00B6-1762-4F43-832A-30B333DEFB0B}"/>
-    <hyperlink ref="A256" r:id="rId168" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:M3NEmzRMIkIC" xr:uid="{3B1241ED-C401-C84D-97A7-DE943BDE4A75}"/>
-    <hyperlink ref="B256" r:id="rId169" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=3544464980849111198" xr:uid="{CF294D4E-46A3-6447-9E7D-679968EB8218}"/>
-    <hyperlink ref="A259" r:id="rId170" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:MXK_kJrjxJIC" xr:uid="{E4FC7D56-8924-3145-A53A-15D1CF06D4EE}"/>
-    <hyperlink ref="B259" r:id="rId171" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7307252284206317678" xr:uid="{2ED2C41D-B24C-B34B-8977-B1EB3123DE23}"/>
-    <hyperlink ref="A262" r:id="rId172" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:UHK10RUVsp4C" xr:uid="{2440B4C4-5D34-CB4E-93BF-DB92D1844837}"/>
-    <hyperlink ref="B262" r:id="rId173" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5518562443997509835" xr:uid="{6B0992F9-7669-CF42-8BD8-C9D9E3DE2B59}"/>
-    <hyperlink ref="A265" r:id="rId174" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:WqliGbK-hY8C" xr:uid="{356652A2-A0C3-3848-96D3-FA4420B06EB7}"/>
-    <hyperlink ref="B265" r:id="rId175" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13923875661633068415" xr:uid="{72297D5B-227C-A44B-AF57-85B70C0F7CE9}"/>
-    <hyperlink ref="A268" r:id="rId176" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:9vf0nzSNQJEC" xr:uid="{E1B4A8F8-5410-754A-A5F1-67601EA32A35}"/>
-    <hyperlink ref="B268" r:id="rId177" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11024059258601086524" xr:uid="{4291A755-A949-8748-ACC4-294D69407CDF}"/>
-    <hyperlink ref="A271" r:id="rId178" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:AXPGKjj_ei8C" xr:uid="{43F9FEAD-CE56-3A43-A391-B1B1F94A7D52}"/>
-    <hyperlink ref="B271" r:id="rId179" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10450486218110735942" xr:uid="{E6B8241C-9F3B-6149-96FA-A407CBAC23D2}"/>
-    <hyperlink ref="A274" r:id="rId180" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:4fKUyHm3Qg0C" xr:uid="{473AB1C4-92D4-4C40-8C95-769796D1BBC2}"/>
-    <hyperlink ref="A277" r:id="rId181" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:1sJd4Hv_s6UC" xr:uid="{AA583035-EAC9-8A4F-ADCE-2A8F835B729C}"/>
-    <hyperlink ref="B277" r:id="rId182" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10389709692359282307" xr:uid="{80BB1E26-112C-8442-9F1F-CE22EC651C9E}"/>
-    <hyperlink ref="A280" r:id="rId183" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:u5HHmVD_uO8C" xr:uid="{0957ED45-8FFC-BD40-9FB8-69C6D4C638FB}"/>
-    <hyperlink ref="B280" r:id="rId184" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=200565888300983999" xr:uid="{A6D8794E-1880-B547-9250-2AA1135934C7}"/>
-    <hyperlink ref="A283" r:id="rId185" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:mVmsd5A6BfQC" xr:uid="{A884D0A6-CD4D-BD4C-9533-53A8FEBB4B89}"/>
-    <hyperlink ref="B283" r:id="rId186" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11585418168150218650" xr:uid="{6A1F3F0A-C35D-C040-B60E-4A2E3C16F08B}"/>
-    <hyperlink ref="A286" r:id="rId187" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:-_dYPAW6P2MC" xr:uid="{2E87AD0C-51AB-F54D-9BF1-B8D734B20EFC}"/>
-    <hyperlink ref="B286" r:id="rId188" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9669732322967748013" xr:uid="{A73DAEB9-227E-0544-AF2B-D9631C8139C5}"/>
-    <hyperlink ref="A289" r:id="rId189" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:p2g8aNsByqUC" xr:uid="{78FB3EC0-E7BF-1446-A0D1-ECD66DD9C4A6}"/>
-    <hyperlink ref="B289" r:id="rId190" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7218974355010000251" xr:uid="{AC55F0CC-31BC-1D4B-9678-054EC53EB3CF}"/>
-    <hyperlink ref="A292" r:id="rId191" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:SP6oXDckpogC" xr:uid="{5AE371D2-D69C-D94F-B2D8-11FCA14049BB}"/>
-    <hyperlink ref="B292" r:id="rId192" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8639077744506763903" xr:uid="{6CFFDD2E-884D-4B4D-820F-E0552AA35E41}"/>
-    <hyperlink ref="A295" r:id="rId193" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:UxriW0iASnsC" xr:uid="{97E01C3C-94CD-B646-8371-D9C0D8180F15}"/>
-    <hyperlink ref="B295" r:id="rId194" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=410796400638482184" xr:uid="{4E431457-F6B9-9640-B7F5-27DE4CEC42B2}"/>
-    <hyperlink ref="A298" r:id="rId195" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=lotIW94AAAAJ:zA6iFVUQeVQC" xr:uid="{B7BC1BF9-828F-AE40-9E24-1C6D8176DBAC}"/>
-    <hyperlink ref="B298" r:id="rId196" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13360730226505543334" xr:uid="{5826F977-FC19-174C-9049-60FA3E0C211F}"/>
-    <hyperlink ref="A301" r:id="rId197" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:mB3voiENLucC" xr:uid="{C3BEC5BB-0CDC-4D4A-938F-2DA201450E9B}"/>
-    <hyperlink ref="B301" r:id="rId198" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16285463943111636393" xr:uid="{C42E29C4-BB9A-2E47-975B-F680D9E801AA}"/>
-    <hyperlink ref="A304" r:id="rId199" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:5nxA0vEk-isC" xr:uid="{64A161D5-1D39-644E-85A8-40542CDB40CB}"/>
-    <hyperlink ref="B304" r:id="rId200" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17964153398804685847" xr:uid="{840D565B-614A-5D43-ABBE-1B337CABC16B}"/>
-    <hyperlink ref="A307" r:id="rId201" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:tkaPQYYpVKoC" xr:uid="{02EC0D63-111E-AA4F-A0C6-80ED337017F1}"/>
-    <hyperlink ref="A310" r:id="rId202" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:fQNAKQ3IYiAC" xr:uid="{FFA26EA6-01E9-1049-A348-30FF98034947}"/>
-    <hyperlink ref="B310" r:id="rId203" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=104085382152131525" xr:uid="{18144DB4-01F2-2E49-A0AB-4FA7E6C6F314}"/>
-    <hyperlink ref="A313" r:id="rId204" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:08ZZubdj9fEC" xr:uid="{E0146093-3A61-6D4B-8850-1389B7624CE5}"/>
-    <hyperlink ref="B313" r:id="rId205" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2483569933196342945" xr:uid="{C6743B63-7D3E-B346-B775-E230A3362150}"/>
-    <hyperlink ref="A316" r:id="rId206" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:XD-gHx7UXLsC" xr:uid="{11CC09CE-DCAC-BD40-9160-F330932EF4BA}"/>
-    <hyperlink ref="B316" r:id="rId207" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1186113911725416393" xr:uid="{43292DE0-C072-3E44-9530-862C9013B092}"/>
-    <hyperlink ref="A319" r:id="rId208" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:ZfRJV9d4-WMC" xr:uid="{A3B4BD64-79E0-BA44-A1BC-678C5D8805FA}"/>
-    <hyperlink ref="B319" r:id="rId209" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=3144558464421653050" xr:uid="{6E02EB03-5460-A645-968B-0F563C732938}"/>
-    <hyperlink ref="A322" r:id="rId210" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:j8SEvjWlNXcC" xr:uid="{3644EEB0-D8BE-D747-93A3-2FBA2CDA7BBE}"/>
-    <hyperlink ref="B322" r:id="rId211" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8398362486471036782,2570846515687838170" xr:uid="{CB3139D7-208B-2A4E-92E7-2B2D9D7A47BF}"/>
-    <hyperlink ref="A325" r:id="rId212" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:Y5dfb0dijaUC" xr:uid="{99A2C75B-CEA1-184F-82B1-C1646E4FE181}"/>
-    <hyperlink ref="B325" r:id="rId213" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11232548838173255092,12788281159718551455" xr:uid="{0E8B8645-586D-5B4F-A381-317636A87639}"/>
-    <hyperlink ref="A328" r:id="rId214" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:3s1wT3WcHBgC" xr:uid="{F8781559-7FCA-4740-9C4B-F641CC1C9C5C}"/>
-    <hyperlink ref="B328" r:id="rId215" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7495958295445879158" xr:uid="{1D9F6217-15D0-9848-9166-5B598C3CAAF8}"/>
-    <hyperlink ref="A331" r:id="rId216" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:t6usbXjVLHcC" xr:uid="{17298E66-DE3D-1C48-A9F1-178E9D38BCFA}"/>
-    <hyperlink ref="B331" r:id="rId217" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6897121472101981230" xr:uid="{507D40FE-51C1-4A45-837D-15D07BF5355F}"/>
-    <hyperlink ref="A334" r:id="rId218" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:NMxIlDl6LWMC" xr:uid="{3C98138B-E854-B345-A18C-CCF197818B5E}"/>
-    <hyperlink ref="B334" r:id="rId219" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4390993639691727131" xr:uid="{390F23EC-EFCE-0840-8066-A868DC474C3B}"/>
-    <hyperlink ref="A337" r:id="rId220" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:0EnyYjriUFMC" xr:uid="{C6D60941-B7AF-D74A-AD7C-85BE2F7F4564}"/>
-    <hyperlink ref="B337" r:id="rId221" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=396408347637046392" xr:uid="{317E6C92-5CA1-6D49-BE15-80808A2D7FA7}"/>
-    <hyperlink ref="A340" r:id="rId222" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:epqYDVWIO7EC" xr:uid="{603683FA-3EBB-8F4B-8474-DC00DD2A7400}"/>
-    <hyperlink ref="B340" r:id="rId223" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15624479947755182442" xr:uid="{FCBB5B30-D3FF-7A47-8E6F-27ED868E7313}"/>
-    <hyperlink ref="A343" r:id="rId224" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:_kc_bZDykSQC" xr:uid="{BF5DAC43-966E-2C4C-B149-635DF50F5FF7}"/>
-    <hyperlink ref="B343" r:id="rId225" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9970934687604809167" xr:uid="{0334B487-1671-4B40-AEEF-0B4D14B350EB}"/>
-    <hyperlink ref="A346" r:id="rId226" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:BUYA1_V_uYcC" xr:uid="{5F4AAEFA-3188-D649-862C-B85F111DEFA4}"/>
-    <hyperlink ref="B346" r:id="rId227" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13676995628850696864" xr:uid="{4AE5D7C0-8C69-8D4A-BDB5-8845390E3818}"/>
-    <hyperlink ref="A349" r:id="rId228" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:Fu2w8maKXqMC" xr:uid="{A92242D5-A09A-3C45-8CFC-8784AA3F0A44}"/>
-    <hyperlink ref="B349" r:id="rId229" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9691413334368179424" xr:uid="{6BCDD99F-F6CA-EA4C-B442-F402110F2952}"/>
-    <hyperlink ref="A352" r:id="rId230" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:1yQoGdGgb4wC" xr:uid="{8B6E869A-8115-FA45-976A-DD6409ECFADA}"/>
-    <hyperlink ref="B352" r:id="rId231" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11741074295207369761" xr:uid="{30C57573-E4DB-5643-8119-D20D6EC461D4}"/>
-    <hyperlink ref="A355" r:id="rId232" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:70eg2SAEIzsC" xr:uid="{7A2DDF50-05D5-A845-9A47-3C09D64ED40F}"/>
-    <hyperlink ref="B355" r:id="rId233" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9627655095505024530" xr:uid="{FF1CD266-FC6D-D647-9248-154B329BBDBE}"/>
-    <hyperlink ref="A358" r:id="rId234" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:zYLM7Y9cAGgC" xr:uid="{8B62A749-CD49-A14F-9C4D-B29654CCB0FD}"/>
-    <hyperlink ref="B358" r:id="rId235" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2084618667136346817" xr:uid="{D16A9F15-EF10-A44B-9C83-7D75C2154C26}"/>
-    <hyperlink ref="A361" r:id="rId236" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:W7OEmFMy1HYC" xr:uid="{535C18B5-3A87-BB4F-8035-3B773009A57A}"/>
-    <hyperlink ref="B361" r:id="rId237" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4241406062953309350" xr:uid="{D0E924E3-578A-D047-84AF-0519A64927A0}"/>
-    <hyperlink ref="A364" r:id="rId238" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:Wp0gIr-vW9MC" xr:uid="{87B7B193-EB43-764A-B5C0-96476202D45B}"/>
-    <hyperlink ref="B364" r:id="rId239" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12995922977674132301" xr:uid="{99F9F727-6D59-4645-8026-4B27CD6E2D81}"/>
-    <hyperlink ref="A367" r:id="rId240" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:-f6ydRqryjwC" xr:uid="{D1A4E4FE-42CB-184C-80C6-F9467F97C8F2}"/>
-    <hyperlink ref="B367" r:id="rId241" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16149707310901490982" xr:uid="{299FB71C-9368-D04E-A43F-06FC7AA8B6C7}"/>
-    <hyperlink ref="A370" r:id="rId242" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:9ZlFYXVOiuMC" xr:uid="{E6797ECB-8C22-4D46-88DF-1776E75303A6}"/>
-    <hyperlink ref="B370" r:id="rId243" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13615534701347562822" xr:uid="{C8E3F1F0-8785-EE4A-944B-B931BAF4F7DB}"/>
-    <hyperlink ref="A373" r:id="rId244" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:BwyfMAYsbu0C" xr:uid="{BA2AF6B4-5D70-384F-89B3-3E51D983C73B}"/>
-    <hyperlink ref="B373" r:id="rId245" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8557475709729251005" xr:uid="{853BE77A-7801-AE40-BAE3-05D9567478FD}"/>
-    <hyperlink ref="A376" r:id="rId246" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:VLnqNzywnoUC" xr:uid="{B08BD668-BEF5-4E4D-9C2D-CD67F4DD8610}"/>
-    <hyperlink ref="B376" r:id="rId247" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10580436175122826885" xr:uid="{2AB3DA8E-9304-A648-B303-CFC94AF9069A}"/>
-    <hyperlink ref="A379" r:id="rId248" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:tKAzc9rXhukC" xr:uid="{49CC03E9-4EDD-5443-94C9-0B68D880DE56}"/>
-    <hyperlink ref="B379" r:id="rId249" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4390265008156162287" xr:uid="{91BA788E-BC9D-2F42-9B87-F0B1FE439668}"/>
-    <hyperlink ref="A382" r:id="rId250" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:9Nmd_mFXekcC" xr:uid="{55DC44BB-85E8-EA4C-8D45-4A543691E424}"/>
-    <hyperlink ref="B382" r:id="rId251" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1222119398266347402" xr:uid="{7BB3D9AD-DD07-8E41-95A5-37E11441D878}"/>
-    <hyperlink ref="A385" r:id="rId252" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:4JMBOYKVnBMC" xr:uid="{CAA4C2F5-52F3-F64E-8B50-6E8FA5CA1B9E}"/>
-    <hyperlink ref="B385" r:id="rId253" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5208820412855728759" xr:uid="{85F25001-82DD-854F-BA1A-24461A491051}"/>
-    <hyperlink ref="A388" r:id="rId254" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:4TOpqqG69KYC" xr:uid="{F8CE8892-96DC-A644-975B-4E482A36E00F}"/>
-    <hyperlink ref="B388" r:id="rId255" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10138283561733198013" xr:uid="{B18EA425-7482-8247-9DF0-4D3C3DF310FE}"/>
-    <hyperlink ref="A391" r:id="rId256" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:QIV2ME_5wuYC" xr:uid="{E6E783A5-1920-0742-A063-CFB987F765A3}"/>
-    <hyperlink ref="B391" r:id="rId257" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14085698606005378160" xr:uid="{40AB1101-CDDF-734A-8AFE-6186E86367D7}"/>
-    <hyperlink ref="A394" r:id="rId258" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:z_wVstp3MssC" xr:uid="{1DCEE629-EBEE-7743-9862-1B1927EA6433}"/>
-    <hyperlink ref="B394" r:id="rId259" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12225935889853151501" xr:uid="{2BC4B70E-F18C-9048-9979-3804F3B9A8F1}"/>
-    <hyperlink ref="A397" r:id="rId260" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:eQOLeE2rZwMC" xr:uid="{C61073C0-FA08-8445-ABFE-21F07914DB4F}"/>
-    <hyperlink ref="B397" r:id="rId261" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=561364294799986477" xr:uid="{5C14ADE8-1E62-174F-AD06-1AEC61F9271A}"/>
-    <hyperlink ref="A400" r:id="rId262" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:LPZeul_q3PIC" xr:uid="{D3E5F03E-9EF4-D749-8A23-741AEAB50330}"/>
-    <hyperlink ref="B400" r:id="rId263" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12579161765913704817" xr:uid="{F1FFF655-FD0A-EC44-AC75-5F622DD0BE9B}"/>
-    <hyperlink ref="A403" r:id="rId264" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:tYavs44e6CUC" xr:uid="{E3ACCA6E-1A54-2C4F-AA1D-4C5694AD919B}"/>
-    <hyperlink ref="B403" xr:uid="{28B576FE-EB76-DA4C-9240-F535F8A806BA}"/>
-    <hyperlink ref="A406" r:id="rId265" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:KUbvn5osdkgC" xr:uid="{80259885-1853-F048-B304-B5FE6DCCF93D}"/>
-    <hyperlink ref="B406" xr:uid="{918E9187-1775-B742-9650-3C1BB1E2F613}"/>
-    <hyperlink ref="A409" r:id="rId266" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:ML0RJ9NH7IQC" xr:uid="{52EE812F-2863-ED44-AB10-ADE169AFE208}"/>
-    <hyperlink ref="B409" xr:uid="{2F8DC445-0DA9-F64B-B832-B7835AD96FEB}"/>
-    <hyperlink ref="A412" r:id="rId267" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:ILKRHgRFtOwC" xr:uid="{00111C3E-A4BE-8A4D-8437-583278C947AC}"/>
-    <hyperlink ref="B412" xr:uid="{EA41BFB9-F46B-1940-8CAC-5B6062715AA4}"/>
-    <hyperlink ref="A415" r:id="rId268" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:4MWp96NkSFoC" xr:uid="{40F25A51-751B-974A-8126-57AFD0A49F5E}"/>
-    <hyperlink ref="B415" xr:uid="{72D40713-FB05-A04B-ADB1-16801AB7122B}"/>
-    <hyperlink ref="A418" r:id="rId269" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:Z5m8FVwuT1cC" xr:uid="{A8B5E057-AEB3-7B4B-8E45-FD9C9FC3E1D6}"/>
-    <hyperlink ref="B418" xr:uid="{D3DD7CA1-F489-C647-81EF-CC3F5C08073F}"/>
-    <hyperlink ref="A421" r:id="rId270" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:p__nRnzSRKYC" xr:uid="{DEB10365-C2BB-5D47-9F0C-8258FEF96E56}"/>
-    <hyperlink ref="B421" xr:uid="{58B5EAC4-0CA9-5B49-974B-D23BAD691A82}"/>
-    <hyperlink ref="A424" r:id="rId271" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:_Re3VWB3Y0AC" xr:uid="{B6C5CAAC-2982-1846-B3FA-597547F16B2C}"/>
-    <hyperlink ref="B424" xr:uid="{899756CB-8B43-B046-BA19-32DDA505B460}"/>
-    <hyperlink ref="A427" r:id="rId272" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:7T2F9Uy0os0C" xr:uid="{5C4F6789-A16F-4A40-82CA-3FB6EC965CE9}"/>
-    <hyperlink ref="B427" xr:uid="{34B46B5A-958F-DA4E-B6BB-267315BE35CE}"/>
-    <hyperlink ref="A430" r:id="rId273" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:ye4kPcJQO24C" xr:uid="{8AC7762F-7AE2-C540-8A05-F8EAACFCC2D7}"/>
-    <hyperlink ref="B430" xr:uid="{0FC856E8-95B9-3B47-AA33-7355C89EEA2A}"/>
-    <hyperlink ref="A433" r:id="rId274" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:tzM49s52ZIMC" xr:uid="{74F72146-2EB6-C84A-AEA9-F332F0E366EC}"/>
-    <hyperlink ref="B433" xr:uid="{C46845D8-D35B-894C-8203-AC719CEDF326}"/>
-    <hyperlink ref="A436" r:id="rId275" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:eJXPG6dFmWUC" xr:uid="{BD0C8DCB-22D1-794A-8DA2-0D68F3508BE1}"/>
-    <hyperlink ref="B436" xr:uid="{D86A0F30-111D-7146-A6D8-55F179EC8E7B}"/>
-    <hyperlink ref="A439" r:id="rId276" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:738O_yMBCRsC" xr:uid="{9AA92CD9-BA59-CA41-A79C-1B89510981D8}"/>
-    <hyperlink ref="B439" xr:uid="{2005C707-5F12-984D-B5A7-3A1154C11634}"/>
-    <hyperlink ref="A442" r:id="rId277" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:hMsQuOkrut0C" xr:uid="{7A2602FE-61C9-5E46-8ED5-81EE66479CE2}"/>
-    <hyperlink ref="B442" xr:uid="{567848B8-237B-CC4F-BB3E-F7C518C6D531}"/>
-    <hyperlink ref="A445" r:id="rId278" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:zLWjf1WUPmwC" xr:uid="{C7B5BB54-74DD-EB4F-9ADC-238E1A164FB2}"/>
-    <hyperlink ref="B445" xr:uid="{D5D9D6C1-DC55-0045-8BE7-FA3DC13C273C}"/>
-    <hyperlink ref="A448" r:id="rId279" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:L7CI7m0gUJcC" xr:uid="{C462C3AA-DE4B-6C49-8E5F-717E844CD9B8}"/>
-    <hyperlink ref="B448" xr:uid="{32144454-6194-1A4B-B70B-75EC714EECC0}"/>
-    <hyperlink ref="A450" r:id="rId280" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:ipzZ9siozwsC" xr:uid="{67EBA974-7207-7549-9A9B-361111770E72}"/>
-    <hyperlink ref="B450" xr:uid="{36A9F931-F2AA-5740-A4AD-9FEBACC4C336}"/>
-    <hyperlink ref="A453" r:id="rId281" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:tS2w5q8j5-wC" xr:uid="{DAF0593A-C7BA-5942-9B29-2543B08BE981}"/>
-    <hyperlink ref="B453" xr:uid="{1EF2E1C5-3C37-C448-980D-DF44785B68C3}"/>
-    <hyperlink ref="A456" r:id="rId282" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:nrtMV_XWKgEC" xr:uid="{9774FAC1-1972-1145-95C3-E183E5793627}"/>
-    <hyperlink ref="B456" xr:uid="{6DA39E5F-BC06-244D-B24A-10787E8B2418}"/>
-    <hyperlink ref="A459" r:id="rId283" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:vDijr-p_gm4C" xr:uid="{416FDEA8-0F8C-4B4B-8532-D0A339A3C433}"/>
-    <hyperlink ref="B459" xr:uid="{083A7FD3-00F4-4247-A78F-68DDFA5255F6}"/>
-    <hyperlink ref="A462" r:id="rId284" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:fEOibwPWpKIC" xr:uid="{9437CFE9-04F3-5348-A015-576DA74181FF}"/>
-    <hyperlink ref="B462" xr:uid="{3F63EC6A-ABB5-FB49-8B01-2B2E19FD5633}"/>
-    <hyperlink ref="A465" r:id="rId285" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:EkHepimYqZsC" xr:uid="{C3459424-E258-4B49-ACA3-E840E91A1514}"/>
-    <hyperlink ref="B465" xr:uid="{E2D10D39-A95C-2F43-AC82-D5B4902520B6}"/>
-    <hyperlink ref="A468" r:id="rId286" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:0KyAp5RtaNEC" xr:uid="{9AF4652B-5BB4-8D4B-873D-A6F380BC42A3}"/>
-    <hyperlink ref="B468" xr:uid="{CE442259-E329-0740-8882-0476885C01A3}"/>
-    <hyperlink ref="A471" r:id="rId287" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=lotIW94AAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=lotIW94AAAAJ:yB1At4FlUx8C" xr:uid="{D397D54C-6630-144F-A20B-12AC5ABEA260}"/>
-    <hyperlink ref="B471" xr:uid="{D14B02BD-4887-CB4B-A4C0-B3F0AD768A4B}"/>
-    <hyperlink ref="A474" r:id="rId288" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=o7i_Yj4AAAAJ&amp;citation_for_view=o7i_Yj4AAAAJ:u5HHmVD_uO8C" xr:uid="{BEAF70FD-4FE8-6F41-B77B-692ABD9A9CBC}"/>
-    <hyperlink ref="B474" r:id="rId289" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2565420096347388496" xr:uid="{04710E4E-003E-984B-86AC-41555E50EA7E}"/>
-    <hyperlink ref="A477" r:id="rId290" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=o7i_Yj4AAAAJ&amp;citation_for_view=o7i_Yj4AAAAJ:d1gkVwhDpl0C" xr:uid="{0B9480DE-96A7-5B4E-98A7-B740D8887C55}"/>
-    <hyperlink ref="B477" r:id="rId291" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10450486218110735942" xr:uid="{D496274F-C014-124E-81E5-D576229B8C15}"/>
-    <hyperlink ref="A480" r:id="rId292" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=o7i_Yj4AAAAJ&amp;citation_for_view=o7i_Yj4AAAAJ:u-x6o8ySG0sC" xr:uid="{CCE7640C-EB30-6845-A827-C4BE7843D36E}"/>
-    <hyperlink ref="B480" r:id="rId293" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7218974355010000251" xr:uid="{55F8A386-E69A-9E4C-9AF6-CAEDE89E63FA}"/>
-    <hyperlink ref="A483" r:id="rId294" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=o7i_Yj4AAAAJ&amp;citation_for_view=o7i_Yj4AAAAJ:2osOgNQ5qMEC" xr:uid="{87C37765-D1A4-4948-B1B9-2F6DAC5D3386}"/>
-    <hyperlink ref="B483" r:id="rId295" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6370476434195885109" xr:uid="{14182E4F-4E99-E845-8C10-F885222506F3}"/>
-    <hyperlink ref="A485" r:id="rId296" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=o7i_Yj4AAAAJ&amp;citation_for_view=o7i_Yj4AAAAJ:9yKSN-GCB0IC" xr:uid="{4756E31E-63F3-084F-AB19-A819A6B6E421}"/>
-    <hyperlink ref="B485" r:id="rId297" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=3144558464421653050" xr:uid="{54DA91DD-18B3-F745-A944-EC5D5C4E9FD1}"/>
-    <hyperlink ref="A488" r:id="rId298" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:Tyk-4Ss8FVUC" xr:uid="{FD051CC9-6D3B-C643-87C1-D0A48A320407}"/>
-    <hyperlink ref="B488" r:id="rId299" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14114835634948919371" xr:uid="{3FC8E51D-C9D6-CA4D-B84A-E94B871FC975}"/>
-    <hyperlink ref="A491" r:id="rId300" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:2osOgNQ5qMEC" xr:uid="{7218644F-B3E7-0A40-8D4D-0B7CD8D44AD2}"/>
-    <hyperlink ref="B491" r:id="rId301" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8476549231901375126" xr:uid="{8E72ECD7-1FBB-6B4D-8CCF-29D18ECA529D}"/>
-    <hyperlink ref="A494" r:id="rId302" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:u5HHmVD_uO8C" xr:uid="{5ED57ED8-21B7-CB4E-A2EF-A54E3F5BFB13}"/>
-    <hyperlink ref="B494" r:id="rId303" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=3695330541162280238" xr:uid="{3CB79D15-7554-164E-8902-C56E1F403268}"/>
-    <hyperlink ref="A497" r:id="rId304" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:qjMakFHDy7sC" xr:uid="{40A8C408-C3ED-B644-950C-460522A42DE9}"/>
-    <hyperlink ref="B497" r:id="rId305" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=10588644636881881377" xr:uid="{8035F035-3280-9548-AFEB-0271BF679194}"/>
-    <hyperlink ref="A500" r:id="rId306" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:YsMSGLbcyi4C" xr:uid="{9B62D473-5EEB-5441-BB26-E1ED300C2378}"/>
-    <hyperlink ref="B500" r:id="rId307" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=16928041941113515765" xr:uid="{35BC7C5E-5FE8-9045-96AC-D006586F4BB3}"/>
-    <hyperlink ref="A503" r:id="rId308" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:IjCSPb-OGe4C" xr:uid="{9EF6CEC4-98E6-3941-A41E-63771BDF2226}"/>
-    <hyperlink ref="B503" r:id="rId309" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=13112971051610378335" xr:uid="{DF4B710E-E475-DC46-ADD9-EA2F1ECA91C1}"/>
-    <hyperlink ref="A506" r:id="rId310" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:Y0pCki6q_DkC" xr:uid="{4E525DAD-0704-C64B-BAF8-AF20C38F8FFF}"/>
-    <hyperlink ref="B506" r:id="rId311" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=2805744561285583491" xr:uid="{E1C63AB2-A852-434C-9E02-9289A9276D8B}"/>
-    <hyperlink ref="A509" r:id="rId312" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:d1gkVwhDpl0C" xr:uid="{E8706FA4-65C1-EB47-B8AE-CAB7CE5E0CFB}"/>
-    <hyperlink ref="B509" r:id="rId313" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5357841664055392961" xr:uid="{22DF0DFD-78E6-9743-AD74-016AEC580E43}"/>
-    <hyperlink ref="A512" r:id="rId314" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:W7OEmFMy1HYC" xr:uid="{9B83D219-F3B4-2340-96DE-5429B2BDDD35}"/>
-    <hyperlink ref="B512" r:id="rId315" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=16867030307165583130" xr:uid="{05717B36-621E-4C46-AA14-5B20C4D8CC2A}"/>
-    <hyperlink ref="A515" r:id="rId316" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:LkGwnXOMwfcC" xr:uid="{9582F6F7-39D2-C543-91B7-18F6B212F23B}"/>
-    <hyperlink ref="B515" r:id="rId317" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15148502300070183642" xr:uid="{B7748590-E52C-B64E-8923-C2DFE88F1561}"/>
-    <hyperlink ref="A518" r:id="rId318" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:u-x6o8ySG0sC" xr:uid="{B812E83F-27D7-0D48-B297-8AB06FFF556A}"/>
-    <hyperlink ref="B518" r:id="rId319" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5304324652359956834" xr:uid="{CF6DD38C-1DCD-0C44-A451-5C4C21F289D8}"/>
-    <hyperlink ref="A521" r:id="rId320" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:roLk4NBRz8UC" xr:uid="{AF5DDC72-497B-3C49-93E2-F9DD49A3D95E}"/>
-    <hyperlink ref="B521" r:id="rId321" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15830419501735151201" xr:uid="{15122114-01B9-CC4C-8388-4919AF53ED6E}"/>
-    <hyperlink ref="A524" r:id="rId322" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:ufrVoPGSRksC" xr:uid="{00E9CFDB-F978-9A46-9483-CF47E346194C}"/>
-    <hyperlink ref="B524" r:id="rId323" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=7916540758135801985" xr:uid="{E700DB66-C12C-194B-91C7-EAF0831C2EC2}"/>
-    <hyperlink ref="A527" r:id="rId324" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:UebtZRa9Y70C" xr:uid="{F0C58751-230F-0E45-A5FE-ADBD22D10CA2}"/>
-    <hyperlink ref="B527" r:id="rId325" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=588320814757422542" xr:uid="{AD716C94-68EA-0541-96F0-D19AA656C9B8}"/>
-    <hyperlink ref="A530" r:id="rId326" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:zYLM7Y9cAGgC" xr:uid="{4FD6343D-91BC-2946-B410-A60AE17E0972}"/>
-    <hyperlink ref="B530" r:id="rId327" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=10283123087671260165" xr:uid="{BCC78B14-D596-6447-A2EB-04B1A1511320}"/>
-    <hyperlink ref="A533" r:id="rId328" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:0EnyYjriUFMC" xr:uid="{DADE3152-1E5B-9348-BB9C-B7DEA91F0F35}"/>
-    <hyperlink ref="B533" r:id="rId329" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11215469155605238517" xr:uid="{7829CCCB-04AF-4741-89B1-42A2F787E6BE}"/>
-    <hyperlink ref="A536" r:id="rId330" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:9yKSN-GCB0IC" xr:uid="{A83827C2-9D32-D640-B2B2-ED48A7524899}"/>
-    <hyperlink ref="B536" r:id="rId331" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5932007910941363020" xr:uid="{AD449217-3DB0-754A-950C-9636EA33A911}"/>
-    <hyperlink ref="A539" r:id="rId332" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:8k81kl-MbHgC" xr:uid="{40A66B39-E64E-BD4E-9122-62B822F823C7}"/>
-    <hyperlink ref="B539" xr:uid="{4C1EF44E-F0B6-FC47-8B53-B0331D0F399E}"/>
-    <hyperlink ref="A542" r:id="rId333" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:hqOjcs7Dif8C" xr:uid="{C23D0DFC-89E7-B348-8318-ADE5892D1E6F}"/>
-    <hyperlink ref="B542" xr:uid="{87F6DEC3-1FAE-D245-9941-2D8CF49B5FCF}"/>
-    <hyperlink ref="A545" r:id="rId334" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;citation_for_view=Dujw1bYAAAAJ:Se3iqnhoufwC" xr:uid="{A659C087-8FAB-114F-BDCC-B4A271EDD496}"/>
-    <hyperlink ref="B545" xr:uid="{8DFFEE07-D8CF-0F42-8BDF-F8A577AE5D1F}"/>
-    <hyperlink ref="A548" r:id="rId335" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=Dujw1bYAAAAJ:eQOLeE2rZwMC" xr:uid="{AEC23CC8-A73C-A342-B614-18F1D8E67FB4}"/>
-    <hyperlink ref="B548" xr:uid="{3DE06DA6-8702-B648-8DB8-D2C2A27DF304}"/>
-    <hyperlink ref="A551" r:id="rId336" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=Dujw1bYAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=Dujw1bYAAAAJ:5nxA0vEk-isC" xr:uid="{E9FE4531-5A4D-9843-BF0B-66500AAD3F1D}"/>
-    <hyperlink ref="B551" xr:uid="{ACF3A058-9EFE-9449-BBF5-1C5E3F3C7CFD}"/>
-    <hyperlink ref="A553" r:id="rId337" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=gJ4oeJEAAAAJ&amp;citation_for_view=gJ4oeJEAAAAJ:u5HHmVD_uO8C" xr:uid="{1B40A5DF-438A-8749-85FB-771386916169}"/>
-    <hyperlink ref="B553" r:id="rId338" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12514179958636495151" xr:uid="{1EA87DC8-7ED0-0F4E-BB7E-24E576B98039}"/>
-    <hyperlink ref="A556" r:id="rId339" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=gJ4oeJEAAAAJ&amp;citation_for_view=gJ4oeJEAAAAJ:9yKSN-GCB0IC" xr:uid="{CA582E4B-12F0-0E4F-B61F-4956EB680F58}"/>
-    <hyperlink ref="B556" r:id="rId340" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9513485110243366275" xr:uid="{EA64D2E5-0267-F541-A023-B046287144CA}"/>
-    <hyperlink ref="A558" r:id="rId341" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=gJ4oeJEAAAAJ&amp;citation_for_view=gJ4oeJEAAAAJ:d1gkVwhDpl0C" xr:uid="{F20E747C-AD44-374A-A35B-4ED1CFA0451A}"/>
-    <hyperlink ref="B558" r:id="rId342" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13387262746893670169" xr:uid="{BA87B8EC-DE94-344C-9678-0484D3591908}"/>
-    <hyperlink ref="A561" r:id="rId343" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:2osOgNQ5qMEC" xr:uid="{38323CF8-6FB9-A346-9004-9BCCB5D1ADF1}"/>
-    <hyperlink ref="B561" r:id="rId344" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=18438821309036428096" xr:uid="{4D227B07-A2DA-8440-8BF4-F1CD707B6767}"/>
-    <hyperlink ref="A564" r:id="rId345" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:9yKSN-GCB0IC" xr:uid="{7A2429BB-E8D8-1545-9615-C85E07B53FF3}"/>
-    <hyperlink ref="B564" r:id="rId346" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=10199253588006063450" xr:uid="{AB810BA5-DB5E-514C-BB90-946C09DD2DF4}"/>
-    <hyperlink ref="A567" r:id="rId347" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:d1gkVwhDpl0C" xr:uid="{BC7D4E69-C0F1-234F-933A-3421060894AF}"/>
-    <hyperlink ref="B567" r:id="rId348" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5394371955331720451,3464617528505037522" xr:uid="{8D45ADDF-E22F-B745-AB3A-968EFAB5F8F5}"/>
-    <hyperlink ref="A570" r:id="rId349" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:qjMakFHDy7sC" xr:uid="{299A71C5-9CA8-7E4C-A193-5CAC3B7419E5}"/>
-    <hyperlink ref="B570" r:id="rId350" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14682916917507945538" xr:uid="{0B8F4095-47E6-344A-80D8-E2BC1221D175}"/>
-    <hyperlink ref="A573" r:id="rId351" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:3fE2CSJIrl8C" xr:uid="{2A84EDE8-57CD-4749-9B6B-34A80D7BFCA4}"/>
-    <hyperlink ref="B573" r:id="rId352" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14518297721468927072" xr:uid="{A6EA550D-BE52-724E-B0C0-6BA07C8ADADA}"/>
-    <hyperlink ref="A576" r:id="rId353" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:5nxA0vEk-isC" xr:uid="{F7CEF5D7-6E09-924C-AC3E-E116821E97D9}"/>
-    <hyperlink ref="B576" r:id="rId354" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15431931766288051897" xr:uid="{570C1D8E-D822-EC44-9C69-FA8813ECD00B}"/>
-    <hyperlink ref="A579" r:id="rId355" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:W7OEmFMy1HYC" xr:uid="{A9D54770-C7FE-084D-BA80-D4D7137E6CFC}"/>
-    <hyperlink ref="B579" r:id="rId356" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15260255064978446488" xr:uid="{9137A70F-7B78-EC40-BFD7-D09C9C5838AF}"/>
-    <hyperlink ref="A582" r:id="rId357" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:UebtZRa9Y70C" xr:uid="{25C71EDA-279B-9842-8F38-F6E54234D0BD}"/>
-    <hyperlink ref="B582" r:id="rId358" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12384977865030484821" xr:uid="{A8855B04-63B7-8D4A-B15A-BECFEAC1F118}"/>
-    <hyperlink ref="A585" r:id="rId359" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Se3iqnhoufwC" xr:uid="{7737AD4C-2FEE-4544-BC03-6DCDDDA6AE7B}"/>
-    <hyperlink ref="B585" r:id="rId360" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11478491708220273652" xr:uid="{EF67D154-1548-9A42-AF2C-5B7E91B39544}"/>
-    <hyperlink ref="A588" r:id="rId361" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:eQOLeE2rZwMC" xr:uid="{E6865631-5B53-A248-B7FD-6DB49D735DC4}"/>
-    <hyperlink ref="B588" r:id="rId362" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=445594232509227482" xr:uid="{E5B78B03-61C6-1545-B4AF-8D09DC1B8D57}"/>
-    <hyperlink ref="A591" r:id="rId363" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Wp0gIr-vW9MC" xr:uid="{3DCC3FE4-B093-DC4C-9944-FB125D22C2DE}"/>
-    <hyperlink ref="B591" r:id="rId364" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=4599190040013596024" xr:uid="{5128CE87-B13B-2444-A3B6-093E5D21EACD}"/>
-    <hyperlink ref="A594" r:id="rId365" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Zph67rFs4hoC" xr:uid="{03E06999-84A5-5042-952A-CB02E53CB311}"/>
-    <hyperlink ref="B594" r:id="rId366" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=17221536997697496231" xr:uid="{2A15D51D-47B1-8B47-8FA6-869EBFB720E1}"/>
-    <hyperlink ref="A597" r:id="rId367" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:-f6ydRqryjwC" xr:uid="{CDFAD303-BAE2-B64B-9312-16F9EF60DAD9}"/>
-    <hyperlink ref="B597" r:id="rId368" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11247321173341005052" xr:uid="{031503EC-2C69-FF41-9758-8CF954D8D378}"/>
-    <hyperlink ref="A600" r:id="rId369" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:LkGwnXOMwfcC" xr:uid="{B690395B-D125-F44D-A06E-329C3B85D807}"/>
-    <hyperlink ref="B600" r:id="rId370" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11765246759472421603" xr:uid="{D896DEB7-902C-284A-ACB4-0E8683869642}"/>
-    <hyperlink ref="A602" r:id="rId371" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:Y0pCki6q_DkC" xr:uid="{25227F6B-3550-DD46-A023-A96829CFC39E}"/>
-    <hyperlink ref="B602" r:id="rId372" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=17617524555772456740" xr:uid="{CAF87E98-7ADC-454D-8F27-FC97E11DED2E}"/>
-    <hyperlink ref="A605" r:id="rId373" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:4DMP91E08xMC" xr:uid="{A583228E-2B61-6B46-817E-E50216F43AAD}"/>
-    <hyperlink ref="B605" r:id="rId374" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=11258725931960264031" xr:uid="{5AFEE5B4-4986-0648-A588-656828B8B0AB}"/>
-    <hyperlink ref="A608" r:id="rId375" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:mB3voiENLucC" xr:uid="{DA0884F2-9A8E-4243-A737-07050EA84AEA}"/>
-    <hyperlink ref="B608" xr:uid="{92884CA6-7D93-9E48-9499-83EB4E87643C}"/>
-    <hyperlink ref="A610" r:id="rId376" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:hFOr9nPyWt4C" xr:uid="{51180FB2-E55E-3248-9CD0-35C6132512BB}"/>
-    <hyperlink ref="B610" xr:uid="{A411A3D8-449E-E64D-BAC3-8BFB7FA555AF}"/>
-    <hyperlink ref="A613" r:id="rId377" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:YOwf2qJgpHMC" xr:uid="{D35FCF3D-732F-6144-A326-66C013C26801}"/>
-    <hyperlink ref="B613" xr:uid="{8DBF1737-CE95-0241-AF67-31AEF5B4D4FB}"/>
-    <hyperlink ref="A616" r:id="rId378" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MajTI0kAAAAJ&amp;citation_for_view=MajTI0kAAAAJ:M3ejUd6NZC8C" xr:uid="{1AB2FAF2-6599-6744-85E7-0B4CA200039F}"/>
-    <hyperlink ref="B616" xr:uid="{941EF143-70B2-1543-B49C-0A32255D5826}"/>
-    <hyperlink ref="A619" r:id="rId379" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:_FxGoFyzp5QC" xr:uid="{04D3BF3D-AB71-6A43-8D99-C60D207B086A}"/>
-    <hyperlink ref="B619" r:id="rId380" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=14943949718996492241,9295283714574589860" xr:uid="{55107CCA-6BD3-7E41-A5CE-994E76862821}"/>
-    <hyperlink ref="A622" r:id="rId381" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:YsMSGLbcyi4C" xr:uid="{AF42615C-0A8D-984F-AE74-DF10DAAD2273}"/>
-    <hyperlink ref="B622" r:id="rId382" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=13162351343408260130" xr:uid="{F5D734A1-0A7F-6F4C-BE93-0103F3DFDB37}"/>
-    <hyperlink ref="A625" r:id="rId383" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:WF5omc3nYNoC" xr:uid="{7485BA4D-AA5B-CD49-9FDF-7E04AD014BD6}"/>
-    <hyperlink ref="B625" r:id="rId384" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=15445732360366845980,2096223136222651988" xr:uid="{34BBB573-C79F-CA42-AABB-58D30D5C343C}"/>
-    <hyperlink ref="A628" r:id="rId385" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:qjMakFHDy7sC" xr:uid="{99D9321F-A778-A346-A46D-704581189D38}"/>
-    <hyperlink ref="A631" r:id="rId386" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:2osOgNQ5qMEC" xr:uid="{AF0D195D-7C03-6A49-97A8-44E59FBA68D4}"/>
-    <hyperlink ref="B631" r:id="rId387" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=6892275663945815970" xr:uid="{3CC00941-739B-5B43-88C4-7E846ED67E12}"/>
-    <hyperlink ref="A634" r:id="rId388" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:u-x6o8ySG0sC" xr:uid="{6565E707-4911-A442-8AD3-87A69E8BF2FC}"/>
-    <hyperlink ref="B634" r:id="rId389" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=1505539922492679102" xr:uid="{B4FE0E29-BE24-4E4C-AFE2-8203AC8244B7}"/>
-    <hyperlink ref="A637" r:id="rId390" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:u5HHmVD_uO8C" xr:uid="{A1D9B95B-52AC-0945-92B4-2EE2A4A503B9}"/>
-    <hyperlink ref="B637" r:id="rId391" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=1195250452201948679" xr:uid="{B944A079-6782-D247-AC5F-8A2AF69D7DC6}"/>
-    <hyperlink ref="A640" r:id="rId392" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:W7OEmFMy1HYC" xr:uid="{2C3B0EDC-AE81-B945-800F-35ECE5619BB4}"/>
-    <hyperlink ref="B640" r:id="rId393" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12347233027893450893,4081673723780999764" xr:uid="{B221B3C1-375D-4A4D-829A-54E7B330E941}"/>
-    <hyperlink ref="A643" r:id="rId394" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Se3iqnhoufwC" xr:uid="{70A0535D-282F-E148-BA00-906BD07AB97E}"/>
-    <hyperlink ref="B643" r:id="rId395" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=5518562443997509835" xr:uid="{222FC3B5-6B0E-E649-A849-78FFD283A757}"/>
-    <hyperlink ref="A646" r:id="rId396" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:zYLM7Y9cAGgC" xr:uid="{CA351F20-8381-994E-8831-A6E18260BA8A}"/>
-    <hyperlink ref="B646" r:id="rId397" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8639077744506763903" xr:uid="{0510EDE9-AF42-6D4B-8DE4-4E42197AAB05}"/>
-    <hyperlink ref="A649" r:id="rId398" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:UeHWp8X0CEIC" xr:uid="{34C7ED57-A208-2745-8BA4-90F1F2330EDA}"/>
-    <hyperlink ref="B649" r:id="rId399" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8398362486471036782" xr:uid="{57213D3F-1450-E844-BA14-644B833B6092}"/>
-    <hyperlink ref="A652" r:id="rId400" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:hqOjcs7Dif8C" xr:uid="{76528754-7F41-7849-AC1E-C5F99255D85A}"/>
-    <hyperlink ref="B652" r:id="rId401" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=13676995628850696864" xr:uid="{C30E8D6E-4E28-2945-891F-276BB5FB5135}"/>
-    <hyperlink ref="A655" r:id="rId402" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Y0pCki6q_DkC" xr:uid="{3ABE0018-5AB6-E14E-8CBD-F9A884C00A60}"/>
-    <hyperlink ref="B655" r:id="rId403" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12214531268750987377" xr:uid="{4929D805-6EAF-3F49-A4BA-68F0E1B1D0BB}"/>
-    <hyperlink ref="A658" r:id="rId404" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:5nxA0vEk-isC" xr:uid="{90E49A5D-3A85-3540-8EB9-4EADDC127403}"/>
-    <hyperlink ref="B658" r:id="rId405" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=8557475709729251005" xr:uid="{3F327CF0-9A47-B044-A975-3E3FEF0351CE}"/>
-    <hyperlink ref="A661" r:id="rId406" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:UebtZRa9Y70C" xr:uid="{02CAF606-2149-0744-BAA5-8D9347D0968A}"/>
-    <hyperlink ref="B661" r:id="rId407" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=4390265008156162287" xr:uid="{ADE9C1A8-B8E6-4F48-BCD8-C12235519ECA}"/>
-    <hyperlink ref="A664" r:id="rId408" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:3fE2CSJIrl8C" xr:uid="{FD3ABF8A-A9F7-DE43-B440-EC98B0E16F94}"/>
-    <hyperlink ref="B664" xr:uid="{C971C95C-ABCD-8B40-8D81-F740BE830825}"/>
-    <hyperlink ref="A667" r:id="rId409" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:0EnyYjriUFMC" xr:uid="{3A9E737D-1822-464F-9091-E9B7BAF9DC84}"/>
-    <hyperlink ref="B667" xr:uid="{3599401A-8514-E44F-BD51-0451F08CE78E}"/>
-    <hyperlink ref="A670" r:id="rId410" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:8k81kl-MbHgC" xr:uid="{CD38D470-3A80-434D-9F5D-B3D7525E0800}"/>
-    <hyperlink ref="B670" xr:uid="{6C1056B1-5E2F-6D4D-AEE7-0C60A64A5887}"/>
-    <hyperlink ref="A673" r:id="rId411" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:Tyk-4Ss8FVUC" xr:uid="{C78D2281-E55B-C746-A139-425869A51446}"/>
-    <hyperlink ref="B673" xr:uid="{DCF8A146-9B7F-2349-B2D2-5F6EA72D4CA4}"/>
-    <hyperlink ref="A676" r:id="rId412" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;citation_for_view=MhVneNwAAAAJ:IjCSPb-OGe4C" xr:uid="{0D3A73C3-6304-A045-80F5-9105FED4A9D6}"/>
-    <hyperlink ref="B676" xr:uid="{8E4F6276-9FF3-1449-BE25-8AE55ED093A1}"/>
-    <hyperlink ref="A679" r:id="rId413" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=MhVneNwAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=MhVneNwAAAAJ:ufrVoPGSRksC" xr:uid="{ADEAA86B-1406-FC4D-AD92-9B84A4AA5796}"/>
-    <hyperlink ref="B679" xr:uid="{8134520B-D207-1440-BF89-A7125B3B0847}"/>
-    <hyperlink ref="A681" r:id="rId414" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:IjCSPb-OGe4C" xr:uid="{57EBE04C-1694-DE4C-8F3E-541B3015BDB6}"/>
-    <hyperlink ref="B681" r:id="rId415" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12125926802820743093" xr:uid="{D9668CC8-08E4-4942-BA77-2622EEB1CDE1}"/>
-    <hyperlink ref="A684" r:id="rId416" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:9yKSN-GCB0IC" xr:uid="{A367D32F-1923-8040-B461-F8624F16EB4F}"/>
-    <hyperlink ref="B684" r:id="rId417" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=7380889746393990269" xr:uid="{C5170D3E-8E00-F649-B907-168EE34CA7F2}"/>
-    <hyperlink ref="A687" r:id="rId418" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:d1gkVwhDpl0C" xr:uid="{336B9BA8-1FDF-3543-85D8-8ABDB1DBC7EA}"/>
-    <hyperlink ref="B687" r:id="rId419" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=895373070968311813" xr:uid="{F5A0C93E-407D-E945-B079-07A65DA11227}"/>
-    <hyperlink ref="A690" r:id="rId420" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:Y0pCki6q_DkC" xr:uid="{76322B4C-7C8D-6240-8BA6-C4320F2612C0}"/>
-    <hyperlink ref="B690" r:id="rId421" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=16759362408447206514" xr:uid="{04C2EAD0-53D9-5240-921A-A54CFDB8ADBE}"/>
-    <hyperlink ref="A693" r:id="rId422" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:qjMakFHDy7sC" xr:uid="{3B2E40B8-0DC3-BB43-81AA-2C6079D248D2}"/>
-    <hyperlink ref="B693" r:id="rId423" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9327618205908924005" xr:uid="{059B5B34-4E5D-AC45-B735-B4D212FB981B}"/>
-    <hyperlink ref="A696" r:id="rId424" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:YsMSGLbcyi4C" xr:uid="{3101AD4B-BFB6-EC4D-BF89-D1BC73AE0F9A}"/>
-    <hyperlink ref="B696" r:id="rId425" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9572686037325897793" xr:uid="{C5866D2F-76D9-1A4E-A7DA-5A873A5A69D9}"/>
-    <hyperlink ref="A699" r:id="rId426" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:UeHWp8X0CEIC" xr:uid="{D00B9E9E-650E-9C44-AC72-E25A39FE49F2}"/>
-    <hyperlink ref="B699" xr:uid="{12A15543-E927-2749-B30A-99C906709ECF}"/>
-    <hyperlink ref="A702" r:id="rId427" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:u-x6o8ySG0sC" xr:uid="{0CAD1EB8-94D0-9648-9588-39AC16B81326}"/>
-    <hyperlink ref="B702" xr:uid="{934E254C-B7C1-C244-BC93-6F2069D5C9BD}"/>
-    <hyperlink ref="A705" r:id="rId428" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:W7OEmFMy1HYC" xr:uid="{DC91BC4F-630B-A148-8FF6-7D9F2AD5016D}"/>
-    <hyperlink ref="B705" xr:uid="{D13194E0-44A8-554E-B85B-E9CE7EC4F5EF}"/>
-    <hyperlink ref="A708" r:id="rId429" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:zYLM7Y9cAGgC" xr:uid="{4D8C5D73-9BBD-1247-85F2-B4E8476D31C6}"/>
-    <hyperlink ref="B708" xr:uid="{458D8C43-2E67-DC41-80BE-95C73C272E62}"/>
+    <hyperlink ref="A707" r:id="rId1" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:IjCSPb-OGe4C" xr:uid="{BDCC0DA5-215B-7B46-9732-7FC1ED96006D}"/>
+    <hyperlink ref="B707" r:id="rId2" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=12125926802820743093" xr:uid="{E95C55E5-5D61-3647-9995-59A062C58C24}"/>
+    <hyperlink ref="A710" r:id="rId3" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:9yKSN-GCB0IC" xr:uid="{5B226CB5-899A-1140-BF0A-9B2D4A8D10D0}"/>
+    <hyperlink ref="B710" r:id="rId4" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=7380889746393990269" xr:uid="{53BD8FF5-978F-A647-B2C1-5DFAD968AF5E}"/>
+    <hyperlink ref="A713" r:id="rId5" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:d1gkVwhDpl0C" xr:uid="{76BD657E-D3C0-7148-9D5A-52A82A5592E8}"/>
+    <hyperlink ref="B713" r:id="rId6" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=895373070968311813" xr:uid="{A65552D2-56ED-2F4F-A1B7-75EEBAE3154C}"/>
+    <hyperlink ref="A716" r:id="rId7" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:Y0pCki6q_DkC" xr:uid="{7F513542-28E7-7B42-A4C1-4E7C4766F854}"/>
+    <hyperlink ref="B716" r:id="rId8" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=16759362408447206514" xr:uid="{27641C9A-D367-E84E-B9FC-D3A5D2341102}"/>
+    <hyperlink ref="A719" r:id="rId9" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:qjMakFHDy7sC" xr:uid="{BD539A4E-9B1D-C748-A330-71536BAAB9DF}"/>
+    <hyperlink ref="B719" r:id="rId10" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9327618205908924005" xr:uid="{658CF1CC-045F-2741-A223-C40E6FB7F7F6}"/>
+    <hyperlink ref="A722" r:id="rId11" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:YsMSGLbcyi4C" xr:uid="{EFB44CDC-3DAA-D945-8006-E5143C95BF6A}"/>
+    <hyperlink ref="B722" r:id="rId12" display="https://scholar.google.com/scholar?oi=bibs&amp;hl=en&amp;cites=9572686037325897793" xr:uid="{4803CD44-C039-994F-9EA1-7BB77774CFA4}"/>
+    <hyperlink ref="A725" r:id="rId13" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:UeHWp8X0CEIC" xr:uid="{4CB1B01C-09D5-A14F-B696-4A97F0D5B89F}"/>
+    <hyperlink ref="B725" xr:uid="{4D6B5BDE-2657-AF46-895B-31B05CC803A9}"/>
+    <hyperlink ref="A728" r:id="rId14" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:u-x6o8ySG0sC" xr:uid="{28FC0E42-1A11-864E-9A44-E01D969539F0}"/>
+    <hyperlink ref="B728" xr:uid="{C254E882-2F20-DA42-B2B6-64D7201377BA}"/>
+    <hyperlink ref="A731" r:id="rId15" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:W7OEmFMy1HYC" xr:uid="{38635B03-7D5B-4F41-AE09-71BCEB0FE7EE}"/>
+    <hyperlink ref="B731" xr:uid="{E1DBA32B-9365-2749-AA69-9019EB9D639D}"/>
+    <hyperlink ref="A734" r:id="rId16" display="https://scholar.google.com/citations?view_op=view_citation&amp;hl=en&amp;user=dq0JfDcAAAAJ&amp;citation_for_view=dq0JfDcAAAAJ:zYLM7Y9cAGgC" xr:uid="{D9F38FE1-8946-5D45-9CF6-D3465A0D1EBE}"/>
+    <hyperlink ref="B734" xr:uid="{B63FF9B7-7A6D-7D46-B565-4B54AF347562}"/>
+    <hyperlink ref="A736" r:id="rId17" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:UeHWp8X0CEIC" xr:uid="{36C87687-3B33-564B-9D68-9D85257E2CA5}"/>
+    <hyperlink ref="B736" r:id="rId18" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14346273139660196717" xr:uid="{4E7139C7-B6D8-6F4C-BD82-4A208F76DC2F}"/>
+    <hyperlink ref="A739" r:id="rId19" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:J_g5lzvAfSwC" xr:uid="{75DC45AB-2C8F-2D43-97C8-27E7E84782DC}"/>
+    <hyperlink ref="B739" r:id="rId20" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8861674829721771794" xr:uid="{5E915A30-A0AE-7F40-8A04-96F2345B638D}"/>
+    <hyperlink ref="A742" r:id="rId21" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:SeFeTyx0c_EC" xr:uid="{D44CF206-6614-334D-B9E0-AEEEFB7658E2}"/>
+    <hyperlink ref="B742" r:id="rId22" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8568270304914414114" xr:uid="{1F096A8F-FDEA-434C-9173-F88E655F5734}"/>
+    <hyperlink ref="A745" r:id="rId23" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:3s1wT3WcHBgC" xr:uid="{F684C125-1400-CD48-9C2B-E08418AA8C90}"/>
+    <hyperlink ref="B745" r:id="rId24" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11920379147387198776,4783607086043749107" xr:uid="{411F15E8-27F7-B64E-9189-AF010F7E86D2}"/>
+    <hyperlink ref="A748" r:id="rId25" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:g5m5HwL7SMYC" xr:uid="{28AE842E-131D-E04B-AA41-F35A811E6153}"/>
+    <hyperlink ref="B748" r:id="rId26" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13720792361583339973" xr:uid="{C3BD0601-D601-8840-B64A-C5E2F01B2615}"/>
+    <hyperlink ref="A751" r:id="rId27" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:cK4Rrx0J3m0C" xr:uid="{58FEE88C-68EA-2745-8087-4E515483CABE}"/>
+    <hyperlink ref="B751" r:id="rId28" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8475020901310660771" xr:uid="{3CABE934-98F2-A14A-94C7-2756812BB125}"/>
+    <hyperlink ref="A754" r:id="rId29" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:u_35RYKgDlwC" xr:uid="{3927BFE1-AA3A-274B-BA58-51FFB8A2E8A2}"/>
+    <hyperlink ref="B754" r:id="rId30" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=528369404368986234" xr:uid="{B32F2CDF-4869-A54B-ABE7-20C225643AE9}"/>
+    <hyperlink ref="A757" r:id="rId31" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:mNrWkgRL2YcC" xr:uid="{2906E8F1-66D7-7C4F-A3FB-67C0FF856F2D}"/>
+    <hyperlink ref="B757" r:id="rId32" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17801138625187775878" xr:uid="{B3F530B4-7EB5-F44C-A81D-879A6226C062}"/>
+    <hyperlink ref="A760" r:id="rId33" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:maZDTaKrznsC" xr:uid="{BF4E4E59-2FAE-4042-A223-D6FBF1BC0868}"/>
+    <hyperlink ref="B760" r:id="rId34" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1593362075739306399" xr:uid="{901F333B-AF2B-0844-A3A4-3F80DC849110}"/>
+    <hyperlink ref="A763" r:id="rId35" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:eGYfIraVYiQC" xr:uid="{F5648F52-B042-AC4B-8A3C-E91E66020A90}"/>
+    <hyperlink ref="B763" r:id="rId36" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12979649474359891071" xr:uid="{EE31E8CD-01AB-D34E-9B40-5B920A67EF81}"/>
+    <hyperlink ref="A766" r:id="rId37" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:wE-fMHVdjMkC" xr:uid="{3FBF8769-7B22-AB4E-8D27-656095DD3D7E}"/>
+    <hyperlink ref="B766" r:id="rId38" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16761395255968795921" xr:uid="{086850B9-00E0-DF42-8FED-8F25BDBDBB9A}"/>
+    <hyperlink ref="A769" r:id="rId39" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:u5HHmVD_uO8C" xr:uid="{9D8AF86D-1720-9342-B87B-5C71FF1D9259}"/>
+    <hyperlink ref="B769" r:id="rId40" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15054669945519323318" xr:uid="{3FAA5709-532C-6B4D-88AC-AD602ABFBCB0}"/>
+    <hyperlink ref="A772" r:id="rId41" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:YFjsv_pBGBYC" xr:uid="{6B1C30CA-984C-B445-819E-D5B2895A9DC1}"/>
+    <hyperlink ref="B772" r:id="rId42" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9903578772955684746" xr:uid="{8BD57D75-E9CB-9C41-AEF5-F990522CFE8B}"/>
+    <hyperlink ref="A775" r:id="rId43" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:LdasjJ6CEcoC" xr:uid="{E6CCE708-4227-3A48-976C-94BED4497E7B}"/>
+    <hyperlink ref="B775" r:id="rId44" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10554931737733326517" xr:uid="{C80AF427-D772-1443-9350-FCB524AD21DC}"/>
+    <hyperlink ref="A778" r:id="rId45" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:u-x6o8ySG0sC" xr:uid="{B4270926-026B-7C4D-B5B5-6D09D48772F2}"/>
+    <hyperlink ref="B778" r:id="rId46" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4567078381489118229" xr:uid="{077284E5-10C0-1441-B4B2-14BAAE1C23DE}"/>
+    <hyperlink ref="A781" r:id="rId47" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:RGFaLdJalmkC" xr:uid="{1F4A060B-8123-B547-87EB-16EBEC602B0B}"/>
+    <hyperlink ref="B781" r:id="rId48" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6468959405811416805" xr:uid="{153CE29D-84DC-2C44-BECD-E69C6A8F481A}"/>
+    <hyperlink ref="A784" r:id="rId49" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:isC4tDSrTZIC" xr:uid="{1188C693-9D04-9A45-882F-215E6F2A8C41}"/>
+    <hyperlink ref="B784" r:id="rId50" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9845726323955356475" xr:uid="{180F55C8-7A07-E342-8236-7C3D0E53F891}"/>
+    <hyperlink ref="A787" r:id="rId51" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:-DxkuPiZhfEC" xr:uid="{B1F2E2C4-D7E7-6A45-A589-9357D8C87124}"/>
+    <hyperlink ref="B787" r:id="rId52" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8887078801435178458" xr:uid="{574FB332-3B88-DB41-A890-7F8B5C0EF344}"/>
+    <hyperlink ref="A790" r:id="rId53" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:blknAaTinKkC" xr:uid="{50AA3075-331B-0F4B-91C4-B33C9DC47D6D}"/>
+    <hyperlink ref="B790" r:id="rId54" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1163025148350801929" xr:uid="{C5AE9532-0B0D-A94B-A633-63FF46BC46DA}"/>
+    <hyperlink ref="A793" r:id="rId55" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;citation_for_view=_X58b2IAAAAJ:7BrZ7Jt4UNcC" xr:uid="{F2C3002C-AEA0-8B4C-BA22-F614218ED88D}"/>
+    <hyperlink ref="B793" r:id="rId56" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5171643882282870128" xr:uid="{28676383-0E25-C34A-B592-202CF17D2A38}"/>
+    <hyperlink ref="A796" r:id="rId57" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:2P1L_qKh6hAC" xr:uid="{85E0743B-FA07-A847-A67C-C4903146169C}"/>
+    <hyperlink ref="B796" r:id="rId58" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11698323136891879601" xr:uid="{9F30F72D-FA84-D643-8344-CF1C5D9E7E67}"/>
+    <hyperlink ref="A799" r:id="rId59" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:cWzG1nlazyYC" xr:uid="{7C4FC024-EA97-3A40-AA63-A02E70FAED9B}"/>
+    <hyperlink ref="B799" r:id="rId60" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11147637902431611608" xr:uid="{08E77304-13BB-5044-BBB2-1BB0F72C7671}"/>
+    <hyperlink ref="A802" r:id="rId61" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:wKETBy42zhYC" xr:uid="{7DD68450-A4AF-B544-B9AB-B7CEC762847D}"/>
+    <hyperlink ref="B802" r:id="rId62" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8252746229047695479" xr:uid="{1AA3030D-B33D-8E4F-A083-37190E2D0176}"/>
+    <hyperlink ref="A805" r:id="rId63" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:NMxIlDl6LWMC" xr:uid="{0072DF06-95F2-8247-A9B6-F846CCD8E7C6}"/>
+    <hyperlink ref="B805" r:id="rId64" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7959828378339549962" xr:uid="{3663089F-6EBB-D648-8BDD-5B1991AC7C3A}"/>
+    <hyperlink ref="A808" r:id="rId65" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:R3hNpaxXUhUC" xr:uid="{0B84E6E1-D2D3-094F-A31D-6A5191677779}"/>
+    <hyperlink ref="B808" r:id="rId66" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13648668480549103601" xr:uid="{D2677D77-7434-4C42-8B97-8870E065A4F1}"/>
+    <hyperlink ref="A811" r:id="rId67" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:hFOr9nPyWt4C" xr:uid="{EEDFF39A-DFFE-DB41-93F2-059D8DA26DA4}"/>
+    <hyperlink ref="B811" r:id="rId68" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16962343946725353103" xr:uid="{ABBCD265-5F4B-D64B-AC4C-9D0D6CB3E9DD}"/>
+    <hyperlink ref="A814" r:id="rId69" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:HDshCWvjkbEC" xr:uid="{D009B542-8140-764E-8FAA-685EAE020E2C}"/>
+    <hyperlink ref="B814" r:id="rId70" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16410617063730297208" xr:uid="{761D0FE3-99ED-3C40-AD0B-F3E8626878DD}"/>
+    <hyperlink ref="A817" r:id="rId71" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:sA9dB-pw3HoC" xr:uid="{9B8C998C-52AD-0049-9F2E-6A47BCBFFA7B}"/>
+    <hyperlink ref="B817" r:id="rId72" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15501957683774966981" xr:uid="{07BD0492-9B15-C743-AD00-27C946E9FBE1}"/>
+    <hyperlink ref="A820" r:id="rId73" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:silx2ntsSuwC" xr:uid="{D2D6B540-FA90-D644-A8C2-B3BD85A3740D}"/>
+    <hyperlink ref="B820" r:id="rId74" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10326633140154187503" xr:uid="{8B5E5DCA-F143-0D4A-BA55-A9F00C1B5FB1}"/>
+    <hyperlink ref="A823" r:id="rId75" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:d1gkVwhDpl0C" xr:uid="{23B40668-340F-F74C-9BAE-842FE07753AC}"/>
+    <hyperlink ref="B823" r:id="rId76" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17385967802513106675" xr:uid="{75A6C102-8236-274B-942C-8D1D2101DFA2}"/>
+    <hyperlink ref="A826" r:id="rId77" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:RJOyoaXV5v8C" xr:uid="{2985C901-7700-B643-86AB-AFB649D380A0}"/>
+    <hyperlink ref="B826" r:id="rId78" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2056764792287693739" xr:uid="{80CCF3FA-5BDD-AE48-B5BF-A35521B44B60}"/>
+    <hyperlink ref="A829" r:id="rId79" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ghEM2AJqZyQC" xr:uid="{80E36FCB-C4BB-F844-AE91-A6A246118FB2}"/>
+    <hyperlink ref="B829" r:id="rId80" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15042493862497651687" xr:uid="{70ECF4F3-149E-F94E-9B68-A7925AB3DBEB}"/>
+    <hyperlink ref="A832" r:id="rId81" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:iH-uZ7U-co4C" xr:uid="{ADCD6BA1-71AD-C34D-95BD-3DBFA98754B7}"/>
+    <hyperlink ref="B832" r:id="rId82" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12762164665213147032" xr:uid="{AC0849ED-FD60-7745-9645-B051AEF49760}"/>
+    <hyperlink ref="A835" r:id="rId83" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:YsMSGLbcyi4C" xr:uid="{6689CE3A-7235-7341-9EA8-69311B3D7540}"/>
+    <hyperlink ref="B835" r:id="rId84" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=873460391339353105" xr:uid="{C3571D77-44C7-E144-9785-992F793E4E39}"/>
+    <hyperlink ref="A838" r:id="rId85" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:IWHjjKOFINEC" xr:uid="{4C982B17-7DBD-C442-8087-767430F3D02C}"/>
+    <hyperlink ref="B838" r:id="rId86" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16826277865627951468" xr:uid="{52203FA0-840A-DE48-A7EF-8ECBE7CD8F6A}"/>
+    <hyperlink ref="A841" r:id="rId87" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:X9ykpCP0fEIC" xr:uid="{9B2DFA4F-EFA7-D44D-867B-8F578A3A0EC4}"/>
+    <hyperlink ref="B841" r:id="rId88" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13203038051270044811" xr:uid="{310A0437-EB2A-7542-9C63-4C9981BBE2EF}"/>
+    <hyperlink ref="A844" r:id="rId89" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:4vMrXwiscB8C" xr:uid="{79DA3AD8-652C-1846-9FE5-F99E157E6DAC}"/>
+    <hyperlink ref="B844" r:id="rId90" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4250375418489682478" xr:uid="{285506CC-0646-3C48-882D-FDA3115363F7}"/>
+    <hyperlink ref="A847" r:id="rId91" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:Tyk-4Ss8FVUC" xr:uid="{2B1DC51D-89A6-5245-B9C3-26F2C34B8AE6}"/>
+    <hyperlink ref="B847" r:id="rId92" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=633340985551841010" xr:uid="{69D6CFED-ADFF-7145-BE5B-12A51851746A}"/>
+    <hyperlink ref="A850" r:id="rId93" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:4X0JR2_MtJMC" xr:uid="{D3766E5A-1091-0C4E-A7CB-22905F91C689}"/>
+    <hyperlink ref="B850" r:id="rId94" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5434651140522184120" xr:uid="{A0B9A93C-4110-6849-A5DD-F70425EEDE06}"/>
+    <hyperlink ref="A853" r:id="rId95" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:UmS_249rOGwC" xr:uid="{44E2C7EE-C834-AD40-B506-B8F9FAC09336}"/>
+    <hyperlink ref="B853" r:id="rId96" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2288629408403659455" xr:uid="{BA73BAC0-31AF-8740-889E-91960E63A343}"/>
+    <hyperlink ref="A856" r:id="rId97" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:kVjdVfd2voEC" xr:uid="{6FEE2740-A65E-D44B-8A78-4FF307252C26}"/>
+    <hyperlink ref="B856" r:id="rId98" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12123630504927837030" xr:uid="{2E9D8718-5F52-D948-9D34-02202547600D}"/>
+    <hyperlink ref="A859" r:id="rId99" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:FiytvqdAVhgC" xr:uid="{91D6465E-15E0-C64A-AD97-1CA77F0E23A1}"/>
+    <hyperlink ref="B859" r:id="rId100" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7675481433774857377" xr:uid="{BDD86AD6-6371-8B46-A8FB-C57FB84412EC}"/>
+    <hyperlink ref="A862" r:id="rId101" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:hMod-77fHWUC" xr:uid="{A76FDF31-1AF7-284F-A9E8-68C312542D19}"/>
+    <hyperlink ref="B862" r:id="rId102" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15930892928494232983" xr:uid="{5A79359C-2ABA-7B43-B7F3-FED496ADA7C3}"/>
+    <hyperlink ref="A865" r:id="rId103" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:7PzlFSSx8tAC" xr:uid="{C271EC43-EDD2-1646-94BF-94055974FA5F}"/>
+    <hyperlink ref="B865" r:id="rId104" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9674321725953244964" xr:uid="{DF2EBE39-99EA-EE4D-97FF-E0756AA0FDCD}"/>
+    <hyperlink ref="A868" r:id="rId105" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:_Qo2XoVZTnwC" xr:uid="{F3A93642-AA82-5349-99E7-150F72679867}"/>
+    <hyperlink ref="B868" r:id="rId106" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12206336576563425910" xr:uid="{86269A54-DCC8-AB4E-9004-6CB939D8435D}"/>
+    <hyperlink ref="A871" r:id="rId107" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:RHpTSmoSYBkC" xr:uid="{575FBA4A-527E-F24A-A007-E64326C1A35A}"/>
+    <hyperlink ref="B871" r:id="rId108" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14213548540001962428" xr:uid="{A47A2944-EA4E-A942-BB5D-0B7ADBD99B1C}"/>
+    <hyperlink ref="A874" r:id="rId109" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:eAlLMO4JVmQC" xr:uid="{3983A96C-C5B6-724D-95EC-4E66452F0CC5}"/>
+    <hyperlink ref="B874" r:id="rId110" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6737419523760401315" xr:uid="{1B0E28C7-B3F7-BE4E-BE5F-7FA596CE57E0}"/>
+    <hyperlink ref="A877" r:id="rId111" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:WHdLCjDvYFkC" xr:uid="{6975D054-30B6-E94A-9BB9-0A18C16CCB27}"/>
+    <hyperlink ref="B877" r:id="rId112" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15382619314921104697" xr:uid="{0AF6522D-FE50-9C48-9916-7C91C0DDA5D5}"/>
+    <hyperlink ref="A880" r:id="rId113" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:r0BpntZqJG4C" xr:uid="{1D5158FF-B4D7-5548-8498-B138644D9823}"/>
+    <hyperlink ref="B880" r:id="rId114" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=3951794794272948061" xr:uid="{94ADE5BE-E0BC-754D-A438-2C48CC992209}"/>
+    <hyperlink ref="A883" r:id="rId115" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:a0OBvERweLwC" xr:uid="{DBFBFC4D-BB18-494A-8C6D-ED2888235DEC}"/>
+    <hyperlink ref="B883" r:id="rId116" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7911019871609839735" xr:uid="{AF99F9D1-3D59-0D4F-BA57-84DC31305BC1}"/>
+    <hyperlink ref="A886" r:id="rId117" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:4OULZ7Gr8RgC" xr:uid="{4096F95E-CCA9-4A4C-990E-6F5790AF0E7C}"/>
+    <hyperlink ref="B886" r:id="rId118" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5413300862332350814" xr:uid="{F5480B4D-E5F4-784D-9AE3-E749543B1ED5}"/>
+    <hyperlink ref="A889" r:id="rId119" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:9yKSN-GCB0IC" xr:uid="{6E5E5194-0401-B441-933D-5DC2928D84D6}"/>
+    <hyperlink ref="B889" r:id="rId120" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6330768405004824845" xr:uid="{3A0DF290-8B00-E540-83B0-50C64131C789}"/>
+    <hyperlink ref="A892" r:id="rId121" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:qjMakFHDy7sC" xr:uid="{AA3F1B62-0799-7142-967F-69D18BE6B5C5}"/>
+    <hyperlink ref="B892" r:id="rId122" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13404789190346776479" xr:uid="{74185B63-D025-8A4C-A39F-B04937EA8A41}"/>
+    <hyperlink ref="A895" r:id="rId123" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:v6i8RKmR8ToC" xr:uid="{83A841EE-446E-F549-A143-F3C49D2C2E02}"/>
+    <hyperlink ref="B895" r:id="rId124" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10658430876385780017" xr:uid="{3573A43C-972D-614E-B75F-332D8AB0B73B}"/>
+    <hyperlink ref="A898" r:id="rId125" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:IaI1MmNe2tcC" xr:uid="{8ED76FF1-2AB6-2249-A781-9E77649A29B9}"/>
+    <hyperlink ref="B898" r:id="rId126" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7640648223960335092" xr:uid="{8D50F61E-FD3B-6A44-A5EF-721746FEA9CB}"/>
+    <hyperlink ref="A901" r:id="rId127" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:fPk4N6BV_jEC" xr:uid="{CC65670C-0C45-4F4E-B499-54DE0878F37F}"/>
+    <hyperlink ref="B901" r:id="rId128" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12580702505512816191" xr:uid="{06283D20-DC81-2B43-BB15-486339A9C769}"/>
+    <hyperlink ref="A904" r:id="rId129" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:PaBasH6fAo0C" xr:uid="{AE4A5F59-E39C-FD4F-8685-4D83D5B33C0C}"/>
+    <hyperlink ref="B904" r:id="rId130" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1359193106659464272" xr:uid="{BD1DC5EC-29A4-6B49-81F9-05B8C4AF23DC}"/>
+    <hyperlink ref="A907" r:id="rId131" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:4JMBOYKVnBMC" xr:uid="{E2856E5F-54AA-3F45-9C9F-D868F55F7271}"/>
+    <hyperlink ref="B907" r:id="rId132" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=13357762055598599843" xr:uid="{A45D9F83-75FE-4346-8142-F285EA11704E}"/>
+    <hyperlink ref="A910" r:id="rId133" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:MXK_kJrjxJIC" xr:uid="{4D055283-ECCC-C646-960C-5FE0C45B2DD4}"/>
+    <hyperlink ref="B910" r:id="rId134" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16193269676628861260" xr:uid="{09DDC078-D0AB-6044-A3E5-0FA64639108E}"/>
+    <hyperlink ref="A913" r:id="rId135" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:IjCSPb-OGe4C" xr:uid="{5F6D5EA6-AAA7-E54D-A11D-B8033FF91E83}"/>
+    <hyperlink ref="B913" r:id="rId136" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16649567720134657689" xr:uid="{63796E4B-CF33-244D-BB29-10F25C120219}"/>
+    <hyperlink ref="A916" r:id="rId137" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:BJbdYPG6LGMC" xr:uid="{0936362A-651A-EC40-A4CD-97F14EA4DF6F}"/>
+    <hyperlink ref="B916" r:id="rId138" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=853851338433459014" xr:uid="{DDA8501A-85A1-0648-A1AB-D50725521011}"/>
+    <hyperlink ref="A919" r:id="rId139" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:Y0pCki6q_DkC" xr:uid="{630E0C73-12EF-7C49-A480-9078D7E2DCF5}"/>
+    <hyperlink ref="B919" r:id="rId140" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16450128503800122570" xr:uid="{5006F0E8-7C03-BC4F-9A4F-F6AB84A1260D}"/>
+    <hyperlink ref="A922" r:id="rId141" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:kw52XkFRtyQC" xr:uid="{A979755E-DB37-9741-AB30-D650E4A81947}"/>
+    <hyperlink ref="B922" r:id="rId142" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10452413709306838386" xr:uid="{F5D19848-79A9-3944-A36F-0BEDD1A2D8B6}"/>
+    <hyperlink ref="A925" r:id="rId143" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:O3NaXMp0MMsC" xr:uid="{F80E9971-B82C-BC49-B722-BC179A669984}"/>
+    <hyperlink ref="B925" r:id="rId144" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16755274867984387328" xr:uid="{4620F93B-7026-4B4C-9D14-03B4707E1DA6}"/>
+    <hyperlink ref="A928" r:id="rId145" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ULOm3_A8WrAC" xr:uid="{7EAAE6EE-1719-3044-B075-8F1404425B16}"/>
+    <hyperlink ref="B928" r:id="rId146" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6531674985469644878" xr:uid="{4C65FB83-AA47-0149-9DD1-6690C2290863}"/>
+    <hyperlink ref="A931" r:id="rId147" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:2osOgNQ5qMEC" xr:uid="{BB5038BC-9A48-2B42-8898-82E249680BCD}"/>
+    <hyperlink ref="B931" r:id="rId148" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12450036236199483570" xr:uid="{1F962CF5-E751-FD48-A840-06463304C631}"/>
+    <hyperlink ref="A934" r:id="rId149" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:43bX7VzcjpAC" xr:uid="{30C638E7-8221-6F43-8507-427D66EA37EC}"/>
+    <hyperlink ref="B934" r:id="rId150" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11651978174989726105" xr:uid="{D6CF4DB2-CD18-6A46-B17C-2422B8187B5E}"/>
+    <hyperlink ref="A937" r:id="rId151" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:-yGd096yOn8C" xr:uid="{BB9010D6-B5C2-8C4E-B14F-2EC6CB597065}"/>
+    <hyperlink ref="B937" r:id="rId152" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10975155642223770124" xr:uid="{AE116437-7949-4D40-BF91-E620C2C6A20C}"/>
+    <hyperlink ref="A939" r:id="rId153" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:zA6iFVUQeVQC" xr:uid="{74CED968-B1BE-6543-8905-67076ED34D61}"/>
+    <hyperlink ref="B939" r:id="rId154" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=74169188519875563" xr:uid="{45B7CB2C-A0E2-DC42-890E-5606E1A1DC50}"/>
+    <hyperlink ref="A942" r:id="rId155" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:hC7cP41nSMkC" xr:uid="{1E06951E-4100-6845-B7D6-21D5FD5842FD}"/>
+    <hyperlink ref="B942" r:id="rId156" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1167897155425622534" xr:uid="{E5C2CD73-FB02-E344-920D-221583E7B406}"/>
+    <hyperlink ref="A945" r:id="rId157" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:Wq2b2clWBLsC" xr:uid="{E6210DB3-84B8-B346-AED6-C173FDB276E5}"/>
+    <hyperlink ref="B945" r:id="rId158" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9812454237493124908" xr:uid="{3168586C-E1D3-FA46-9198-9647C1BCF783}"/>
+    <hyperlink ref="A948" r:id="rId159" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:SIv7DqKytYAC" xr:uid="{DFE411E7-B147-8D4C-80CE-506B4F3E9772}"/>
+    <hyperlink ref="B948" r:id="rId160" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9490953511622729624" xr:uid="{6F5FA01E-B6D3-A649-AC6C-D6EB369AD1FD}"/>
+    <hyperlink ref="A951" r:id="rId161" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:v1_lew4L6wgC" xr:uid="{476602D3-2ED3-1E44-990C-AD9C33637355}"/>
+    <hyperlink ref="B951" r:id="rId162" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16570582394777815723" xr:uid="{4570BE8D-F3DC-214A-9B1B-50C803CEC0A7}"/>
+    <hyperlink ref="A954" r:id="rId163" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ubry08Y2EpUC" xr:uid="{AA5825B4-BF2C-E14D-94C4-826A8DD108EF}"/>
+    <hyperlink ref="B954" r:id="rId164" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17718037247525400985" xr:uid="{E548B928-B2CD-DD4F-9531-D9C9EF324BD2}"/>
+    <hyperlink ref="A957" r:id="rId165" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ldfaerwXgEUC" xr:uid="{EAE71D4E-2C2E-904A-9EFE-E54DEAF0837B}"/>
+    <hyperlink ref="B957" r:id="rId166" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10852074020263000126" xr:uid="{A6135B4D-0C60-9A40-8B9A-D6D315A7FD1D}"/>
+    <hyperlink ref="A960" r:id="rId167" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:BqipwSGYUEgC" xr:uid="{A4FAC6EA-6518-854D-A4BB-49C172D6F1C6}"/>
+    <hyperlink ref="B960" r:id="rId168" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15609067858908144696" xr:uid="{CA545D69-2FE5-154D-A743-D38F32E4078D}"/>
+    <hyperlink ref="A963" r:id="rId169" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:35N4QoGY0k4C" xr:uid="{E7E281A1-BC34-264F-9BD7-9A14DC0EB607}"/>
+    <hyperlink ref="B963" r:id="rId170" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5265550754138841709" xr:uid="{7BBBA3BB-F76A-7A40-8254-271F8E6A833C}"/>
+    <hyperlink ref="A966" r:id="rId171" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:KlAtU1dfN6UC" xr:uid="{94F995B4-F088-A746-A802-985C0C4E6775}"/>
+    <hyperlink ref="B966" r:id="rId172" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16711332403309855524" xr:uid="{40711613-2F7A-7B46-AF1E-ADAAC9445059}"/>
+    <hyperlink ref="A969" r:id="rId173" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:hqOjcs7Dif8C" xr:uid="{4A55098A-09AD-DE45-87E3-770B8D2ED3C5}"/>
+    <hyperlink ref="B969" r:id="rId174" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8862902440761712271" xr:uid="{DACE1ABF-7641-B24C-9BA6-EFEF52963539}"/>
+    <hyperlink ref="A972" r:id="rId175" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:HoB7MX3m0LUC" xr:uid="{9A8B7D2E-34B2-D14E-ADFE-D79A49EBDFE3}"/>
+    <hyperlink ref="B972" r:id="rId176" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=11519887475692966358" xr:uid="{4E9A26DD-E64D-044A-96B2-501A48DC3E5F}"/>
+    <hyperlink ref="A975" r:id="rId177" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:LkGwnXOMwfcC" xr:uid="{07B678E8-C474-D94A-A877-D560517648EE}"/>
+    <hyperlink ref="B975" r:id="rId178" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4658247653475435372" xr:uid="{735941D3-9C80-1C43-9727-0AE28C154A07}"/>
+    <hyperlink ref="A978" r:id="rId179" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:TQgYirikUcIC" xr:uid="{7702EDA7-D665-F948-81B0-6DF1C288E867}"/>
+    <hyperlink ref="B978" r:id="rId180" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8452246908995767711" xr:uid="{C3FBB638-810D-5C4A-A768-0C49C37FF49E}"/>
+    <hyperlink ref="A981" r:id="rId181" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:qE4H1tSSYIIC" xr:uid="{81BFED73-2C3C-D04D-BE03-AB7FEC1CF745}"/>
+    <hyperlink ref="B981" r:id="rId182" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7939219207341910813" xr:uid="{230E0F9A-1DF3-8B40-9A47-8D6B9C8C71D9}"/>
+    <hyperlink ref="A984" r:id="rId183" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:27LrP4qxOz0C" xr:uid="{1CA3266C-0E44-1F4C-8A89-6BEDB7FEB375}"/>
+    <hyperlink ref="B984" r:id="rId184" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1460459474485297673" xr:uid="{0EC68AEE-2D01-A54B-B0A7-9BE6E127F2DA}"/>
+    <hyperlink ref="A987" r:id="rId185" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:KWzIFqRkAKkC" xr:uid="{4B7E3363-BB0D-DA4F-9966-368E4592F317}"/>
+    <hyperlink ref="B987" r:id="rId186" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7502328843225623091" xr:uid="{373BA29F-09C8-224B-950E-D89D9C121009}"/>
+    <hyperlink ref="A990" r:id="rId187" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:DyXnQzXoVgIC" xr:uid="{B6614801-EE59-E34E-BBFB-D856A8F57CB8}"/>
+    <hyperlink ref="B990" r:id="rId188" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=405676590358495528" xr:uid="{6A2F087C-9190-7E4C-B1E4-E38CCB9BF7C2}"/>
+    <hyperlink ref="A993" r:id="rId189" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:nRpfm8aw39MC" xr:uid="{86301F67-DF6F-884B-A5AE-0639867C98CC}"/>
+    <hyperlink ref="B993" r:id="rId190" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4541519868271063963" xr:uid="{E69F31D3-C022-5A49-8810-2D763091BCD2}"/>
+    <hyperlink ref="A996" r:id="rId191" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ns9cj8rnVeAC" xr:uid="{840AC949-81A4-D14D-AB39-050B8DFD406D}"/>
+    <hyperlink ref="B996" r:id="rId192" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=4107548390674171379" xr:uid="{51D8FE20-A92B-5941-ADC2-D7CC7233E1AE}"/>
+    <hyperlink ref="A999" r:id="rId193" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:g5Ck-dwhA_QC" xr:uid="{1C8FFE1A-2FF3-7747-AAD8-A1329AA2FAC5}"/>
+    <hyperlink ref="B999" r:id="rId194" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17357024887053200817" xr:uid="{C13D4C6E-4D7C-8C4B-A73F-03A324AB47E9}"/>
+    <hyperlink ref="A1002" r:id="rId195" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:_FxGoFyzp5QC" xr:uid="{B52A1C6B-0294-964E-998C-9BE3633B9742}"/>
+    <hyperlink ref="B1002" r:id="rId196" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2497077256023576348" xr:uid="{F7BF2A83-9FA9-0A42-A1F3-5C9FE6089FA3}"/>
+    <hyperlink ref="A1005" r:id="rId197" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:isU91gLudPYC" xr:uid="{CD92281A-8A3E-9244-9A59-9E6CBF1D0E7B}"/>
+    <hyperlink ref="B1005" r:id="rId198" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5403258321659285635" xr:uid="{4B2555D7-5ECC-3546-B607-6B59EC423598}"/>
+    <hyperlink ref="A1008" r:id="rId199" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:2ywjKiB__4kC" xr:uid="{925992E3-2D04-5549-AEE2-DF5A7C667AAA}"/>
+    <hyperlink ref="B1008" r:id="rId200" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2138826916776572496" xr:uid="{171A9103-8A5F-5546-8E79-34854BE05776}"/>
+    <hyperlink ref="A1011" r:id="rId201" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:zdjWy_NXXwUC" xr:uid="{42238AEC-BBC2-4D44-944F-FC57576A0332}"/>
+    <hyperlink ref="B1011" r:id="rId202" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6281004857986417296,169981167384169630" xr:uid="{CA836190-8BEA-C440-A6A1-20A082C80827}"/>
+    <hyperlink ref="A1014" r:id="rId203" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:j7_hQOaDUrUC" xr:uid="{E0D32A31-A068-C043-8AFB-9DF48EE71308}"/>
+    <hyperlink ref="B1014" r:id="rId204" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=7309967024547229019" xr:uid="{27D7C322-EAFC-B049-98DD-5CE4ED7CB2AA}"/>
+    <hyperlink ref="A1017" r:id="rId205" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:MpfHP-DdYjUC" xr:uid="{8BC97E08-F6C9-E946-8276-DA49B79C5552}"/>
+    <hyperlink ref="B1017" r:id="rId206" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14239192859345500946" xr:uid="{7CB4AEA9-9B30-5F47-8EEE-06E567CF1820}"/>
+    <hyperlink ref="A1020" r:id="rId207" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:ALROH1vI_8AC" xr:uid="{4117F211-998D-4744-9FE0-09ADE98E1438}"/>
+    <hyperlink ref="B1020" r:id="rId208" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10498387806931523115" xr:uid="{910F225A-8400-5047-BADC-89CC5F5BFA0E}"/>
+    <hyperlink ref="A1023" r:id="rId209" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:NaGl4SEjCO4C" xr:uid="{902D0E43-AA0D-0348-8C2F-59CCA2F394DC}"/>
+    <hyperlink ref="B1023" r:id="rId210" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=3385369039261659135" xr:uid="{6AE2F88B-5F6C-E543-99DA-4E81B8076CB0}"/>
+    <hyperlink ref="A1026" r:id="rId211" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:qUcmZB5y_30C" xr:uid="{9A0FBCAB-3C64-614D-8EA4-FF4E754D1EDB}"/>
+    <hyperlink ref="B1026" r:id="rId212" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=1918759025826596299" xr:uid="{B158D9FC-DF89-9645-81A8-0C85FA49CA65}"/>
+    <hyperlink ref="A1029" r:id="rId213" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:eQOLeE2rZwMC" xr:uid="{C00101C6-82D8-0C4F-8A02-E2624A5C99AD}"/>
+    <hyperlink ref="B1029" r:id="rId214" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9320757173065556192" xr:uid="{5004C938-3C5C-FC41-AB54-E0901B43D3D0}"/>
+    <hyperlink ref="A1032" r:id="rId215" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=20&amp;pagesize=80&amp;citation_for_view=_X58b2IAAAAJ:UebtZRa9Y70C" xr:uid="{EFBF10ED-6685-6146-A283-E45004DFB287}"/>
+    <hyperlink ref="B1032" r:id="rId216" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=8420335358698098783" xr:uid="{C8DE9856-D55A-7849-AA1C-CD7DACE90784}"/>
+    <hyperlink ref="A1035" r:id="rId217" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:4DMP91E08xMC" xr:uid="{97245730-7280-C54C-A122-8ABAB0B426EF}"/>
+    <hyperlink ref="B1035" r:id="rId218" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=14875805729269045987" xr:uid="{22DBDAC9-3700-794E-967C-D1676AA8E3FD}"/>
+    <hyperlink ref="A1038" r:id="rId219" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:8Xgff_V0N9gC" xr:uid="{298F65E4-5E1F-894D-84CA-E8040F771A76}"/>
+    <hyperlink ref="B1038" r:id="rId220" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=2288671527192286620" xr:uid="{CDD34BBF-CD0B-A34D-A46C-3CED40F94CED}"/>
+    <hyperlink ref="A1041" r:id="rId221" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:ZqE1mSdD_DYC" xr:uid="{BC9B1473-9FC0-A944-8A72-B359D90B1A29}"/>
+    <hyperlink ref="B1041" r:id="rId222" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=12164359272944469088" xr:uid="{E4C4E713-D43B-D54A-8D68-1639BF16220B}"/>
+    <hyperlink ref="A1044" r:id="rId223" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:hvmnpdAuIbkC" xr:uid="{0DEDCFF5-4AD1-144D-B068-7C2660D20AE2}"/>
+    <hyperlink ref="B1044" r:id="rId224" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15990090884763296202" xr:uid="{A9E5DA9D-0E22-B242-8BC2-CD166DC6F2D9}"/>
+    <hyperlink ref="A1047" r:id="rId225" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:NxmKEeNBbOMC" xr:uid="{B3D4F71D-5150-4C47-8ADE-2E7290C50B00}"/>
+    <hyperlink ref="B1047" r:id="rId226" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=18070680073078193793" xr:uid="{35458C05-0E4E-3C46-B678-2E511B78DEB6}"/>
+    <hyperlink ref="A1050" r:id="rId227" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:C33y2ycGS3YC" xr:uid="{75D9F5B4-32C5-8A48-BE0E-EA57534A2572}"/>
+    <hyperlink ref="B1050" r:id="rId228" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10580436175122826885" xr:uid="{C93346A4-D49A-0842-A2CE-A8B9DC200633}"/>
+    <hyperlink ref="A1053" r:id="rId229" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:kJDgFkosVoMC" xr:uid="{7B68D2D8-47A5-0846-8366-6AD8B436D9EA}"/>
+    <hyperlink ref="B1053" r:id="rId230" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=9606018611033260159" xr:uid="{7592118C-4EA5-A14A-8824-D64139D30ED9}"/>
+    <hyperlink ref="A1056" r:id="rId231" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:7H_MAutzIkAC" xr:uid="{59F350B0-C907-A94C-A22F-319B0C364587}"/>
+    <hyperlink ref="B1056" r:id="rId232" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=17865693966492255378" xr:uid="{B01ED936-B56E-A74E-B78F-44B3675F2D57}"/>
+    <hyperlink ref="A1059" r:id="rId233" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:WC23djZS0W4C" xr:uid="{2F5DD241-F2DA-A14B-850A-DEE3A2853327}"/>
+    <hyperlink ref="B1059" r:id="rId234" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=16180336133057077838" xr:uid="{4D826B23-B9D1-EB4C-B0D5-DBF466FE8C50}"/>
+    <hyperlink ref="A1062" r:id="rId235" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:7wO8s98CvbsC" xr:uid="{96B6650D-B901-1B40-B906-0FF5A34B842A}"/>
+    <hyperlink ref="B1062" r:id="rId236" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=15689466142094465660" xr:uid="{8CC97C80-0F30-C646-95F6-AE1676914873}"/>
+    <hyperlink ref="A1065" r:id="rId237" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:8dzOF9BpDQoC" xr:uid="{120C7BA5-6FFD-AD4B-BAB1-88AA706CC737}"/>
+    <hyperlink ref="B1065" r:id="rId238" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=5088169649003989203" xr:uid="{AF4EC739-652D-6742-9811-DE36EBA2F839}"/>
+    <hyperlink ref="A1068" r:id="rId239" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:4TOpqqG69KYC" xr:uid="{70BDF1EC-E913-CA40-9906-F381C1FB3A28}"/>
+    <hyperlink ref="B1068" r:id="rId240" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=10441650011535093115" xr:uid="{2923D22D-0512-C54F-B6FE-A94076BD0AB6}"/>
+    <hyperlink ref="A1071" r:id="rId241" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:Se3iqnhoufwC" xr:uid="{62861377-DD2A-A54F-BC5C-A61CA08A646A}"/>
+    <hyperlink ref="B1071" r:id="rId242" display="https://scholar.google.ca/scholar?oi=bibs&amp;hl=en&amp;cites=6522716868345772210" xr:uid="{F9328336-09E4-7F4C-B736-291D2F0CAD71}"/>
+    <hyperlink ref="A1074" r:id="rId243" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:4aZ_i-5WJEQC" xr:uid="{225955CB-149F-C746-88F5-24E886F683AD}"/>
+    <hyperlink ref="B1074" xr:uid="{B45E7B1F-9EFF-0A46-9F7D-262A6FAC6E77}"/>
+    <hyperlink ref="A1077" r:id="rId244" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:zwpXiJ37cpgC" xr:uid="{35AAD33B-3ED9-B04F-9D8B-73C9C8A9B23E}"/>
+    <hyperlink ref="B1077" xr:uid="{B019BBAC-8047-F448-BED0-6AE6854013B7}"/>
+    <hyperlink ref="A1080" r:id="rId245" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:SxCCDk4iOpsC" xr:uid="{DB8C9021-7561-4D4A-9D30-3BABAEB93488}"/>
+    <hyperlink ref="B1080" xr:uid="{69CAF036-3028-C74C-B5BE-BDE656DBEDC8}"/>
+    <hyperlink ref="A1083" r:id="rId246" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:RtRctb2lSbAC" xr:uid="{178F11D4-5C9A-6842-9234-72C625F6EABF}"/>
+    <hyperlink ref="B1083" xr:uid="{20F37994-2E53-A44A-9E46-7998E85807FE}"/>
+    <hyperlink ref="A1086" r:id="rId247" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:s9ia6_kGH2AC" xr:uid="{100F73D3-D4AF-B945-97D3-6294CF89F1C7}"/>
+    <hyperlink ref="B1086" xr:uid="{75264778-976D-2147-83EA-20A8B29EEAB8}"/>
+    <hyperlink ref="A1089" r:id="rId248" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:mel-f30kHHgC" xr:uid="{816DCE4D-F54C-EB4A-82AD-B8C0CF8D030D}"/>
+    <hyperlink ref="B1089" xr:uid="{F993A30E-F9E7-6641-A4C0-56261C42C784}"/>
+    <hyperlink ref="A1092" r:id="rId249" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:G1UMdFYMoxkC" xr:uid="{99ECA48E-7308-C64A-ADFC-F5D075592FDC}"/>
+    <hyperlink ref="B1092" xr:uid="{C04F9B40-5DD4-E24C-BA13-FBE51A71FB6B}"/>
+    <hyperlink ref="A1095" r:id="rId250" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:unp9ATQDT5gC" xr:uid="{8E0D8837-C15F-A14D-8C8D-045DDC8A5EEC}"/>
+    <hyperlink ref="B1095" xr:uid="{7634159B-9BC7-0340-B705-4F01C6C63B24}"/>
+    <hyperlink ref="A1098" r:id="rId251" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:lYAcb2jw7qUC" xr:uid="{2EFE761E-06DD-5E46-BD19-7B1F43D1DEC7}"/>
+    <hyperlink ref="B1098" xr:uid="{4EAB1B4F-0571-1842-BD5A-848AF7B9F874}"/>
+    <hyperlink ref="A1100" r:id="rId252" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:nqdriD65xNoC" xr:uid="{F41ACA70-8AC1-B049-A695-562F89525C55}"/>
+    <hyperlink ref="B1100" xr:uid="{47D90971-0EE2-F244-A4CB-D5B9DB38DFA9}"/>
+    <hyperlink ref="A1102" r:id="rId253" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:z8nqeaKD1nsC" xr:uid="{0B7B717C-0E15-A041-A19C-3E0AF1EE2972}"/>
+    <hyperlink ref="B1102" xr:uid="{C3E4F573-1EAD-5C45-A7F4-34AED06FC785}"/>
+    <hyperlink ref="A1104" r:id="rId254" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:X0DADzN9RKwC" xr:uid="{EAEFAEA6-AA59-174D-BF10-0119031CCB8C}"/>
+    <hyperlink ref="B1104" xr:uid="{165859AE-DEA2-8A4A-9C30-D9D44220937B}"/>
+    <hyperlink ref="A1106" r:id="rId255" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:jtI9f0ekYq0C" xr:uid="{4A834AF9-6A5C-9442-A42E-4FF6DED8611A}"/>
+    <hyperlink ref="B1106" xr:uid="{6ABD69F4-0335-E84F-8BB9-67942DABC87E}"/>
+    <hyperlink ref="A1108" r:id="rId256" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:TaaCk18tZOkC" xr:uid="{A03AF4A8-7614-EF4D-ABAF-7A438DCE3A99}"/>
+    <hyperlink ref="B1108" xr:uid="{9E4028DB-F4CA-AE4B-A6CA-5A7E85EA2549}"/>
+    <hyperlink ref="A1110" r:id="rId257" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:_AeoHAGD03cC" xr:uid="{CEC994D3-22E2-BD49-93E4-E58E9007D9AE}"/>
+    <hyperlink ref="B1110" xr:uid="{17B76034-EAA0-B24C-A6E6-EA9FA701AA26}"/>
+    <hyperlink ref="A1112" r:id="rId258" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:s85pQhAUCrAC" xr:uid="{BAE154B1-9D44-A847-A756-42C441AEF234}"/>
+    <hyperlink ref="B1112" xr:uid="{01646529-131A-074F-8086-2D6AF2D75331}"/>
+    <hyperlink ref="A1114" r:id="rId259" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:LK8CI43ZvvMC" xr:uid="{7EA447FA-13A1-9440-8198-C2990D4D4F76}"/>
+    <hyperlink ref="B1114" xr:uid="{AAF52DC0-FAB0-754B-9E65-30360A15D14E}"/>
+    <hyperlink ref="A1116" r:id="rId260" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:zUl2_INMlC4C" xr:uid="{6A64D542-C93A-AC46-AC49-022B1904F824}"/>
+    <hyperlink ref="B1116" xr:uid="{EBFDD03F-BB0D-1545-8F4A-3C4F737F8B33}"/>
+    <hyperlink ref="A1118" r:id="rId261" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:nPT8s1NX_-sC" xr:uid="{7EB94EAE-AE83-C645-8427-1DEA8336FBCB}"/>
+    <hyperlink ref="B1118" xr:uid="{0DD8D714-A6DA-564E-B1C2-7F0C0100E954}"/>
+    <hyperlink ref="A1120" r:id="rId262" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:hQUaER0FWQ4C" xr:uid="{D1DE909A-BBFA-B440-A23B-1F50F5984FC4}"/>
+    <hyperlink ref="B1120" xr:uid="{BCD3261E-75DC-734B-801B-8981A339AA78}"/>
+    <hyperlink ref="A1122" r:id="rId263" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:oPLKW5k6eA4C" xr:uid="{B767F7C2-BC6F-B646-BA05-C41E49DF4E51}"/>
+    <hyperlink ref="B1122" xr:uid="{91177AEE-3949-2A4D-9173-DE3BFE465816}"/>
+    <hyperlink ref="A1124" r:id="rId264" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:LGlY6t8CeOMC" xr:uid="{20824D09-6EB3-A14C-A729-356C7E250D96}"/>
+    <hyperlink ref="B1124" xr:uid="{1AC8A4D1-0685-184A-9EF4-67EFDE5886DC}"/>
+    <hyperlink ref="A1126" r:id="rId265" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:YTuZlYwrTOUC" xr:uid="{96EAA814-EA4F-984D-924F-529C049A60FC}"/>
+    <hyperlink ref="B1126" xr:uid="{B6FEC758-9C58-A94A-9F21-C4A1CEA8B849}"/>
+    <hyperlink ref="A1129" r:id="rId266" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:t-hv7AR41mYC" xr:uid="{38F7AC31-9683-3540-B70A-C48C7FA549A7}"/>
+    <hyperlink ref="B1129" xr:uid="{60F2A798-B3E9-BF41-B35B-939BD05FBC76}"/>
+    <hyperlink ref="A1131" r:id="rId267" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:BmWJbWwHJAwC" xr:uid="{8642CBB8-7526-E04A-8595-A229676C81CF}"/>
+    <hyperlink ref="B1131" xr:uid="{0ED0DDC0-A0D9-5B48-9CA4-69B5E783FC40}"/>
+    <hyperlink ref="A1133" r:id="rId268" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:hGdtkIFZdKAC" xr:uid="{F5EE2AF7-B209-2E42-BDBB-653D059FCCCB}"/>
+    <hyperlink ref="B1133" xr:uid="{17DC4C4F-48A9-684E-9EB3-9253106E4EE9}"/>
+    <hyperlink ref="A1135" r:id="rId269" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:BJrgspguQaEC" xr:uid="{EA901BC1-0D3B-3948-8586-202EC709F707}"/>
+    <hyperlink ref="B1135" xr:uid="{DED0CC8F-8A14-4246-B7FC-00A3B6E34129}"/>
+    <hyperlink ref="A1137" r:id="rId270" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:T_ojBgVMvoEC" xr:uid="{5ACA896B-ED92-EF40-B825-690A37FB1CF7}"/>
+    <hyperlink ref="B1137" xr:uid="{088E6455-C9DF-084D-9249-7C9E49B2381D}"/>
+    <hyperlink ref="A1140" r:id="rId271" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:D_tqNUsBuKoC" xr:uid="{62963D4E-AB75-9E48-9054-CD1E927A6F14}"/>
+    <hyperlink ref="B1140" xr:uid="{C26B92D5-3017-7F4D-998D-7657983D5B32}"/>
+    <hyperlink ref="A1143" r:id="rId272" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:c1e4I3QdEKYC" xr:uid="{4505F37D-AD0A-8446-B52A-BF5E04B5702B}"/>
+    <hyperlink ref="B1143" xr:uid="{A830E3CE-754B-DA49-AFF7-0CCFF338945B}"/>
+    <hyperlink ref="A1146" r:id="rId273" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:AYInfyleIOsC" xr:uid="{CB1EA637-B7B4-4743-94CD-229103DFEB66}"/>
+    <hyperlink ref="B1146" xr:uid="{66C9FFF6-85EB-C546-9CD6-AB725DEEA1E6}"/>
+    <hyperlink ref="A1149" r:id="rId274" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:0aBXIfxlw9sC" xr:uid="{BF2579FB-FE1F-7A45-B834-D27324637A9E}"/>
+    <hyperlink ref="B1149" xr:uid="{EFDDA555-7438-4D48-AAFB-10A7D3C8B772}"/>
+    <hyperlink ref="A1151" r:id="rId275" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:MhiOAD_qIWkC" xr:uid="{DD0F04F0-0758-4340-8A34-8801D7203E23}"/>
+    <hyperlink ref="B1151" xr:uid="{C526846A-8EDD-E743-B3BA-293A41A1AE32}"/>
+    <hyperlink ref="A1154" r:id="rId276" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:1taIhTC69MYC" xr:uid="{6F43A497-F5BB-4045-BE78-05859FAE0CCD}"/>
+    <hyperlink ref="B1154" xr:uid="{1B130693-371E-474F-8D39-6E039D7634A1}"/>
+    <hyperlink ref="A1157" r:id="rId277" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:tHtfpZlB6tUC" xr:uid="{CB7C10DB-6528-6644-AA65-55D14E3094C1}"/>
+    <hyperlink ref="B1157" xr:uid="{A1D2BE3D-A7F5-0743-BF71-556BDF44161B}"/>
+    <hyperlink ref="A1160" r:id="rId278" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:Zh0EY9V9P6UC" xr:uid="{6339C602-1EB1-7C45-95B3-B92D9040530F}"/>
+    <hyperlink ref="B1160" xr:uid="{65A2C050-B93A-724B-A23E-8E445B305F1A}"/>
+    <hyperlink ref="A1162" r:id="rId279" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:M3NEmzRMIkIC" xr:uid="{1401C59B-14DA-ED42-866D-D98F7F836C33}"/>
+    <hyperlink ref="B1162" xr:uid="{D6F857DB-C357-4A4C-9EB0-401C0CD3DA51}"/>
+    <hyperlink ref="A1164" r:id="rId280" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:k_IJM867U9cC" xr:uid="{E6AF58A0-9022-0C40-9049-71DB320A2C43}"/>
+    <hyperlink ref="B1164" xr:uid="{5E327361-09B6-314B-B454-B31974A6745A}"/>
+    <hyperlink ref="A1167" r:id="rId281" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:TFP_iSt0sucC" xr:uid="{AF56A507-EE58-6448-BBDE-44E64B91FC82}"/>
+    <hyperlink ref="B1167" xr:uid="{C08D66ED-5EA4-A94A-A9DB-3DE7987AD427}"/>
+    <hyperlink ref="A1170" r:id="rId282" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:ufrVoPGSRksC" xr:uid="{FAEE18DE-EBC3-0240-A2ED-3F29D9627AFF}"/>
+    <hyperlink ref="B1170" xr:uid="{CBD15EBE-BAB5-3E46-BE4F-B4A58A86902D}"/>
+    <hyperlink ref="A1173" r:id="rId283" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:WF5omc3nYNoC" xr:uid="{F91E0BA3-07CE-3B4C-8E52-DEF4F2CE0EFD}"/>
+    <hyperlink ref="B1173" xr:uid="{4EE4B57F-B481-CF4B-B680-DF2595736AAB}"/>
+    <hyperlink ref="A1176" r:id="rId284" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:kNdYIx-mwKoC" xr:uid="{B8DE264F-C1F7-8548-A90E-FB44C04B9C0D}"/>
+    <hyperlink ref="B1176" xr:uid="{F28C077B-69AA-9D4D-BB4C-3364B9156409}"/>
+    <hyperlink ref="A1179" r:id="rId285" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:5nxA0vEk-isC" xr:uid="{E38FF296-D97E-964B-9AAD-1C730A4E8FEB}"/>
+    <hyperlink ref="B1179" xr:uid="{FC1E0053-968C-9140-9DC9-CB6BDEE48A66}"/>
+    <hyperlink ref="A1182" r:id="rId286" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:JV2RwH3_ST0C" xr:uid="{28FB1F82-0613-5547-B399-3C835F954D20}"/>
+    <hyperlink ref="B1182" xr:uid="{E3353E6D-B77D-9C45-910A-B99C140EE807}"/>
+    <hyperlink ref="A1185" r:id="rId287" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:roLk4NBRz8UC" xr:uid="{F2A88A3C-2256-864D-A301-9E4838F17528}"/>
+    <hyperlink ref="B1185" xr:uid="{DBE2F30E-975A-174C-B0F0-68752C2ED69D}"/>
+    <hyperlink ref="A1188" r:id="rId288" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:RuPIJ_LgqDgC" xr:uid="{1FAC8C37-F5E8-2D43-B06B-866BB8C22FBB}"/>
+    <hyperlink ref="B1188" xr:uid="{74C79B6F-4FCD-FE43-A4F0-3244051701F9}"/>
+    <hyperlink ref="A1190" r:id="rId289" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:L8Ckcad2t8MC" xr:uid="{F9983521-A85E-434B-83BD-0870599C31FA}"/>
+    <hyperlink ref="B1190" xr:uid="{BFA1CB1A-4CC5-A44D-88AD-6089C4F967DC}"/>
+    <hyperlink ref="A1192" r:id="rId290" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:_kc_bZDykSQC" xr:uid="{9E967FF9-CA04-8A41-8C13-4EE821BCC788}"/>
+    <hyperlink ref="B1192" xr:uid="{349E462D-ADE6-DC43-8720-38450A25A630}"/>
+    <hyperlink ref="A1194" r:id="rId291" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:YOwf2qJgpHMC" xr:uid="{87D00495-671E-AF40-A151-B180E732E184}"/>
+    <hyperlink ref="B1194" xr:uid="{6BD1116F-CA35-D143-BE18-415BBA713B06}"/>
+    <hyperlink ref="A1196" r:id="rId292" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:3fE2CSJIrl8C" xr:uid="{765E5645-848E-D447-8E26-E154895470BC}"/>
+    <hyperlink ref="B1196" xr:uid="{7207CFD5-5167-214B-8BE7-B37203F9F2BC}"/>
+    <hyperlink ref="A1199" r:id="rId293" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:e5wmG9Sq2KIC" xr:uid="{C70B7439-4F43-1847-8B2F-09EF96FF4C03}"/>
+    <hyperlink ref="B1199" xr:uid="{54D17505-32ED-5B48-A16F-21B3B2BEE8D7}"/>
+    <hyperlink ref="A1202" r:id="rId294" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:aqlVkmm33-oC" xr:uid="{76A31334-9ECD-134E-BA5D-31959FD2B50C}"/>
+    <hyperlink ref="B1202" xr:uid="{C6217E9F-003C-4641-8E9D-1F44981E7B4D}"/>
+    <hyperlink ref="A1205" r:id="rId295" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:8k81kl-MbHgC" xr:uid="{7969E932-4803-1548-A5B3-E2B32438AB51}"/>
+    <hyperlink ref="B1205" xr:uid="{E9DB7856-8733-9344-AE82-4789F5A4CF3E}"/>
+    <hyperlink ref="A1208" r:id="rId296" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:mVmsd5A6BfQC" xr:uid="{FDCF971C-D954-574C-A802-99DB657ABD5F}"/>
+    <hyperlink ref="B1208" xr:uid="{8D96BFDE-36E6-8744-BC20-588979E944C2}"/>
+    <hyperlink ref="A1211" r:id="rId297" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:Wp0gIr-vW9MC" xr:uid="{DA4AD69B-008C-9E4E-852B-F86530FCF1EB}"/>
+    <hyperlink ref="B1211" xr:uid="{B82CB31C-91AB-C440-8A08-ED36C4649373}"/>
+    <hyperlink ref="A1214" r:id="rId298" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:-f6ydRqryjwC" xr:uid="{AF15C701-D92F-B94D-A79A-BD84CCDF25DB}"/>
+    <hyperlink ref="B1214" xr:uid="{E47A355E-A815-3342-9657-39B1A3C9031D}"/>
+    <hyperlink ref="A1217" r:id="rId299" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:9ZlFYXVOiuMC" xr:uid="{FE479163-5120-3D49-BB0D-DA35949E2BA9}"/>
+    <hyperlink ref="B1217" xr:uid="{4655467E-4A78-B54D-B5D3-65FE052BE5EB}"/>
+    <hyperlink ref="A1220" r:id="rId300" display="https://scholar.google.ca/citations?view_op=view_citation&amp;hl=en&amp;user=_X58b2IAAAAJ&amp;cstart=100&amp;pagesize=100&amp;citation_for_view=_X58b2IAAAAJ:hSRAE-fF4OAC" xr:uid="{6780E506-BA74-2C46-AD9B-F64CFCE941D8}"/>
+    <hyperlink ref="B1220" xr:uid="{A34817AC-0BA6-8D4E-838C-D9DFD3370A2E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
